--- a/TUCUMAN 1061/Octubre/tucuman Octubre.xlsx
+++ b/TUCUMAN 1061/Octubre/tucuman Octubre.xlsx
@@ -5,22 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03015B6-014B-4F87-9ED0-BB6385034CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816A58D0-C282-48E0-9D29-040335E83956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Gastos" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilla" sheetId="2" r:id="rId2"/>
+    <sheet name="Planilla" sheetId="2" r:id="rId1"/>
+    <sheet name="Gastos" sheetId="1" r:id="rId2"/>
     <sheet name="Calculo Servicios  (2)" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$52</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$R$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$R$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
     <definedName name="PaseMateriales" localSheetId="2">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="172">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -257,9 +257,6 @@
     <t>4- GASTO DE ADMINISTRACION</t>
   </si>
   <si>
-    <t>5- SEGURO OBLIGATORIO</t>
-  </si>
-  <si>
     <t xml:space="preserve">General </t>
   </si>
   <si>
@@ -549,29 +546,44 @@
   </si>
   <si>
     <t>subidos en juli 2025</t>
-  </si>
-  <si>
-    <t>Luz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERIODO: SEPTIEMBRE </t>
-  </si>
-  <si>
-    <t>Poliza Sr. De Luca Carlos Hernan - La holando SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Administraciòn SEPTIEMBRE 2025:</t>
-  </si>
-  <si>
-    <t>Digitalizacion acta - Escribania Narosky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adelanto Sr. Leo trabajo en medianera </t>
   </si>
   <si>
     <t xml:space="preserve">Banco santander - C DE P TUCUMAN 1061 1063 - Nro. De cuenta : 39-022068/6
 CBU: 0720039720000002206868
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERIODO: OCTUBRE </t>
+  </si>
+  <si>
+    <t>Poliza Sr. De Luca Carlos Hernan - La holando OCTUBRE</t>
+  </si>
+  <si>
+    <t>Administraciòn OCTUBRE 2025:</t>
+  </si>
+  <si>
+    <t>Articulios de limpieza</t>
+  </si>
+  <si>
+    <t>Gustavo padron - Contador - Honorarios inscripcion ARCA</t>
+  </si>
+  <si>
+    <t>Honorarios - Inscripcion consorcio</t>
+  </si>
+  <si>
+    <t>Kromacolor compra RECUPLAS y Duralba - Muros</t>
+  </si>
+  <si>
+    <t>Sr. Leonardo Balcazza trabajo en medianera (Altura)</t>
+  </si>
+  <si>
+    <t>5 - GASTOS BANCARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gastos bancarios </t>
+  </si>
+  <si>
+    <t>Luz / Martin</t>
   </si>
 </sst>
 </file>
@@ -1390,7 +1402,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1398,7 +1409,6 @@
     <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1815,6 +1825,8 @@
     <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="6" fontId="35" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1841,6 +1853,61 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>62513</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>676215</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3558188" y="447675"/>
+          <a:ext cx="2804452" cy="1143000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1884,61 +1951,6 @@
         <a:xfrm>
           <a:off x="0" y="168275"/>
           <a:ext cx="2325158" cy="1127125"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>62513</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>676215</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3558188" y="447675"/>
-          <a:ext cx="2804452" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2212,839 +2224,180 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="3"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="D2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="192">
-        <v>1153202676</v>
-      </c>
-      <c r="F2" s="192"/>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="D3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="J4" s="191"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="D5" s="193" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="193"/>
-      <c r="F5" s="193"/>
-      <c r="G5" s="193"/>
-      <c r="H5" s="194"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="D6" s="193"/>
-      <c r="E6" s="193"/>
-      <c r="F6" s="193"/>
-      <c r="G6" s="193"/>
-      <c r="H6" s="194"/>
-    </row>
-    <row r="7" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="D7" s="193"/>
-      <c r="E7" s="193"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="194"/>
-    </row>
-    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="206" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="206"/>
-      <c r="C13" s="206"/>
-      <c r="D13" s="206"/>
-      <c r="E13" s="206"/>
-      <c r="F13" s="206"/>
-      <c r="G13" s="206"/>
-      <c r="H13" s="206"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="188">
-        <f>392270+392270*2%</f>
-        <v>400115.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="188">
-        <v>4030.28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="180">
-        <f>SUM(H14:H16)</f>
-        <v>404145.68000000005</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="42"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="207" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="208"/>
-      <c r="C19" s="208"/>
-      <c r="D19" s="208"/>
-      <c r="E19" s="208"/>
-      <c r="F19" s="208"/>
-      <c r="G19" s="208"/>
-      <c r="H19" s="209"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="26">
-        <v>364854.17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="26">
-        <v>533528.86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="27">
-        <f>SUM(H20:H21)</f>
-        <v>898383.03</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="210" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="210"/>
-      <c r="C23" s="210"/>
-      <c r="D23" s="210"/>
-      <c r="E23" s="210"/>
-      <c r="F23" s="210"/>
-      <c r="G23" s="210"/>
-      <c r="H23" s="210"/>
-      <c r="J23" s="26"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="97" t="s">
-        <v>142</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="26">
-        <v>46638</v>
-      </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="97" t="s">
-        <v>144</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="26">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="27">
-        <f>SUM(H24:H25)</f>
-        <v>121638</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="207" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="208"/>
-      <c r="C27" s="208"/>
-      <c r="D27" s="208"/>
-      <c r="E27" s="208"/>
-      <c r="F27" s="208"/>
-      <c r="G27" s="208"/>
-      <c r="H27" s="209"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="43"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="189">
-        <v>66600</v>
-      </c>
-      <c r="I29" s="43"/>
-      <c r="N29" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="29"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="207" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="208"/>
-      <c r="C31" s="208"/>
-      <c r="D31" s="208"/>
-      <c r="E31" s="208"/>
-      <c r="F31" s="208"/>
-      <c r="G31" s="208"/>
-      <c r="H31" s="209"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="49"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="51"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32">
-        <f>H17+H22+H26+H29+H32</f>
-        <v>1490766.71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A34" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="47"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="197" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="198"/>
-      <c r="C35" s="198"/>
-      <c r="D35" s="198"/>
-      <c r="E35" s="198"/>
-      <c r="F35" s="198"/>
-      <c r="G35" s="198"/>
-      <c r="H35" s="199"/>
-      <c r="I35" s="166"/>
-      <c r="K35" s="166"/>
-    </row>
-    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="200"/>
-      <c r="B36" s="201"/>
-      <c r="C36" s="201"/>
-      <c r="D36" s="201"/>
-      <c r="E36" s="201"/>
-      <c r="F36" s="201"/>
-      <c r="G36" s="201"/>
-      <c r="H36" s="202"/>
-    </row>
-    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="211" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="212"/>
-      <c r="C37" s="212"/>
-      <c r="D37" s="212"/>
-      <c r="E37" s="212"/>
-      <c r="F37" s="212"/>
-      <c r="G37" s="213"/>
-      <c r="H37" s="190">
-        <v>45500</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="211" t="s">
-        <v>166</v>
-      </c>
-      <c r="B38" s="212"/>
-      <c r="C38" s="212"/>
-      <c r="D38" s="212"/>
-      <c r="E38" s="212"/>
-      <c r="F38" s="212"/>
-      <c r="G38" s="213"/>
-      <c r="H38" s="190">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="214"/>
-      <c r="B39" s="215"/>
-      <c r="C39" s="215"/>
-      <c r="D39" s="215"/>
-      <c r="E39" s="215"/>
-      <c r="F39" s="215"/>
-      <c r="G39" s="216"/>
-      <c r="H39" s="33"/>
-    </row>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="217" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" s="218"/>
-      <c r="C40" s="218"/>
-      <c r="D40" s="218"/>
-      <c r="E40" s="218"/>
-      <c r="F40" s="218"/>
-      <c r="G40" s="219"/>
-      <c r="H40" s="34">
-        <f>SUM(H37:H39)</f>
-        <v>445500</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="186"/>
-      <c r="B41" s="186"/>
-      <c r="C41" s="186"/>
-      <c r="D41" s="186"/>
-      <c r="E41" s="186"/>
-      <c r="F41" s="186"/>
-      <c r="G41" s="186"/>
-      <c r="H41" s="187"/>
-    </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H42" s="19"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="195" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" s="195"/>
-      <c r="C43" s="195"/>
-      <c r="D43" s="195"/>
-      <c r="E43" s="195"/>
-      <c r="F43" s="195"/>
-      <c r="G43" s="195"/>
-      <c r="H43" s="32">
-        <f>+H33+H34</f>
-        <v>1490766.71</v>
-      </c>
-      <c r="J43" s="166"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="35">
-        <f>H40</f>
-        <v>445500</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-    </row>
-    <row r="47" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="203" t="s">
-        <v>13</v>
-      </c>
-      <c r="B47" s="204"/>
-      <c r="C47" s="204"/>
-      <c r="D47" s="204"/>
-      <c r="E47" s="204"/>
-      <c r="F47" s="204"/>
-      <c r="G47" s="204"/>
-      <c r="H47" s="205"/>
-    </row>
-    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="196" t="s">
-        <v>152</v>
-      </c>
-      <c r="B48" s="196"/>
-      <c r="C48" s="196"/>
-      <c r="D48" s="196"/>
-      <c r="E48" s="196"/>
-      <c r="F48" s="196"/>
-      <c r="G48" s="196"/>
-      <c r="H48" s="41">
-        <v>2237684.7725573108</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="44">
-        <f>Planilla!I31</f>
-        <v>1986523.3583134203</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="38">
-        <f>-(H33+H40)</f>
-        <v>-1936266.71</v>
-      </c>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A51" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="48">
-        <f>SUM(H48:H50)</f>
-        <v>2287941.4208707316</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="D5:H7"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A35:H36"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A38:G38"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" style="52" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="54" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="53" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" style="53" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" style="53" customWidth="1"/>
-    <col min="10" max="10" width="0.109375" style="53" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" style="53" customWidth="1"/>
-    <col min="12" max="12" width="0.109375" style="53" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="12.109375" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="50" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="52" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="51" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="51" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="51" customWidth="1"/>
+    <col min="10" max="10" width="0.140625" style="51" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="51" customWidth="1"/>
+    <col min="12" max="12" width="0.140625" style="51" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.109375" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="222" t="str">
+    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="220" t="str">
         <f>Gastos!E8</f>
-        <v xml:space="preserve">PERIODO: SEPTIEMBRE </v>
-      </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
-      <c r="N1" s="223"/>
-      <c r="O1" s="223"/>
-      <c r="P1" s="223"/>
-      <c r="Q1" s="223"/>
-      <c r="R1" s="224"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="91"/>
-      <c r="C2" s="182">
-        <v>1490766.71</v>
-      </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
+        <v xml:space="preserve">PERIODO: OCTUBRE </v>
+      </c>
+      <c r="B1" s="221"/>
+      <c r="C1" s="221"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
+      <c r="M1" s="221"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="221"/>
+      <c r="P1" s="221"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="222"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="89"/>
+      <c r="C2" s="180">
+        <v>1554753.9300000002</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
       <c r="L2" s="13"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="87"/>
-      <c r="D3" s="182">
-        <v>533528.66</v>
-      </c>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="L3" s="89"/>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="85"/>
+      <c r="D3" s="180">
+        <v>472904.04</v>
+      </c>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="L3" s="87"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="87"/>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="85"/>
       <c r="C4" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="192"/>
-      <c r="N4" s="192"/>
-      <c r="O4" s="192"/>
-      <c r="P4" s="192"/>
-      <c r="Q4" s="192"/>
-      <c r="R4" s="221"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="87"/>
-      <c r="B5" s="90"/>
-      <c r="C5" s="230">
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="190"/>
+      <c r="N4" s="190"/>
+      <c r="O4" s="190"/>
+      <c r="P4" s="190"/>
+      <c r="Q4" s="190"/>
+      <c r="R4" s="219"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="85"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="228">
         <f>D3</f>
-        <v>533528.66</v>
-      </c>
-      <c r="D5" s="230"/>
+        <v>472904.04</v>
+      </c>
+      <c r="D5" s="228"/>
       <c r="E5" s="13"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="L5" s="89"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="L5" s="87"/>
       <c r="M5" s="17"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="87"/>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="85"/>
       <c r="C6" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="87"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="230">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="85"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="228">
         <f>C2-D3</f>
-        <v>957238.04999999993</v>
-      </c>
-      <c r="D7" s="230"/>
-      <c r="E7" s="88"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
+        <v>1081849.8900000001</v>
+      </c>
+      <c r="D7" s="228"/>
+      <c r="E7" s="86"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="87"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86" t="s">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="85"/>
+      <c r="B8" s="84"/>
+      <c r="C8" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="85"/>
-      <c r="B9" s="84"/>
-      <c r="C9" s="231">
-        <v>445500</v>
-      </c>
-      <c r="D9" s="231"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-      <c r="L9" s="80"/>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="83"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="229">
+        <v>350000</v>
+      </c>
+      <c r="D9" s="229"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="78"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3052,1410 +2405,1386 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="79" t="s">
+    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="78" t="s">
+      <c r="C10" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="78" t="s">
+      <c r="D10" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="78" t="s">
+      <c r="E10" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="76" t="s">
-        <v>109</v>
-      </c>
-      <c r="H10" s="76" t="s">
+      <c r="G10" s="74" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="76" t="s">
+      <c r="I10" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="76" t="s">
+      <c r="J10" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="76" t="s">
+      <c r="K10" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="76" t="s">
+      <c r="L10" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="75" t="s">
-        <v>141</v>
-      </c>
-      <c r="N10" s="75" t="s">
+      <c r="M10" s="73" t="s">
+        <v>140</v>
+      </c>
+      <c r="N10" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="75" t="s">
-        <v>156</v>
-      </c>
-      <c r="P10" s="75" t="s">
+      <c r="O10" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="P10" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="75" t="s">
+      <c r="Q10" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="75" t="s">
+      <c r="R10" s="73" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="173" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="174"/>
-      <c r="C11" s="175" t="s">
+    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="171" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="172"/>
+      <c r="C11" s="173" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="176" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="162"/>
-      <c r="F11" s="177">
+      <c r="D11" s="174" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="160"/>
+      <c r="F11" s="175">
         <v>7.9</v>
       </c>
-      <c r="G11" s="66">
-        <v>125031.62204000002</v>
-      </c>
-      <c r="H11" s="66">
-        <v>0</v>
-      </c>
-      <c r="I11" s="66">
+      <c r="G11" s="64">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="H11" s="64">
+        <v>0</v>
+      </c>
+      <c r="I11" s="64">
         <f t="shared" ref="I11:I24" si="0">G11</f>
-        <v>125031.62204000002</v>
-      </c>
-      <c r="J11" s="66" t="e">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="J11" s="64" t="e">
         <f>C8*F11/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="66">
+      <c r="K11" s="64">
         <f t="shared" ref="K11:K18" si="1">G11-H11-I11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="66"/>
-      <c r="M11" s="178">
+      <c r="L11" s="64"/>
+      <c r="M11" s="176">
         <f>(K11+L11)*3%</f>
         <v>0</v>
       </c>
-      <c r="N11" s="178">
+      <c r="N11" s="176">
         <f t="shared" ref="N11:N19" si="2">K11+M11+L11</f>
         <v>0</v>
       </c>
-      <c r="O11" s="66">
+      <c r="O11" s="64">
         <f>C$7*F11/100</f>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P11" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P11" s="64">
         <f>C$9*F11/100</f>
-        <v>35194.5</v>
-      </c>
-      <c r="Q11" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q11" s="64">
         <f>C$5*F11/100</f>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R11" s="178">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R11" s="176">
         <f t="shared" ref="R11:R29" si="3">O11+N11+P11+Q11</f>
+        <v>150475.56047000003</v>
+      </c>
+      <c r="U11" s="90" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="165" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="158"/>
+      <c r="C12" s="166" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="167" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="168"/>
+      <c r="F12" s="169">
+        <v>7.9</v>
+      </c>
+      <c r="G12" s="156">
         <v>152965.07008999999</v>
       </c>
-      <c r="U11" s="92" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="167" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="160"/>
-      <c r="C12" s="168" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="169" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="170"/>
-      <c r="F12" s="171">
-        <v>7.9</v>
-      </c>
-      <c r="G12" s="158">
-        <v>125031.62204000002</v>
-      </c>
-      <c r="H12" s="158">
-        <v>0</v>
-      </c>
-      <c r="I12" s="66">
+      <c r="H12" s="156">
+        <v>0</v>
+      </c>
+      <c r="I12" s="64">
         <f t="shared" si="0"/>
-        <v>125031.62204000002</v>
-      </c>
-      <c r="J12" s="158" t="e">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="J12" s="156" t="e">
         <f>C8*F12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K12" s="158">
+      <c r="K12" s="156">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L12" s="158"/>
-      <c r="M12" s="164">
+      <c r="L12" s="156"/>
+      <c r="M12" s="162">
         <f t="shared" ref="M12:M29" si="4">(K12+L12)*3%</f>
         <v>0</v>
       </c>
-      <c r="N12" s="164">
+      <c r="N12" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O12" s="158">
+      <c r="O12" s="156">
         <f t="shared" ref="O12:O29" si="5">C$7*F12/100</f>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P12" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P12" s="64">
         <f t="shared" ref="P12:P29" si="6">C$9*F12/100</f>
-        <v>35194.5</v>
-      </c>
-      <c r="Q12" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q12" s="64">
         <f t="shared" ref="Q12:Q22" si="7">C$5*F12/100</f>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R12" s="164">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R12" s="162">
         <f t="shared" si="3"/>
+        <v>150475.56047000003</v>
+      </c>
+      <c r="U12" s="91" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="157" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="158"/>
+      <c r="C13" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="159" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="160" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="161">
+        <v>7.9</v>
+      </c>
+      <c r="G13" s="64">
         <v>152965.07008999999</v>
       </c>
-      <c r="U12" s="93" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="160"/>
-      <c r="C13" s="94" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="161" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="162" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="163">
-        <v>7.9</v>
-      </c>
-      <c r="G13" s="66">
-        <v>255645.23380710077</v>
-      </c>
-      <c r="H13" s="158">
-        <v>0</v>
-      </c>
-      <c r="I13" s="66">
+      <c r="H13" s="156">
+        <v>0</v>
+      </c>
+      <c r="I13" s="64">
         <f t="shared" si="0"/>
-        <v>255645.23380710077</v>
-      </c>
-      <c r="J13" s="158" t="e">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="J13" s="156" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="158">
+      <c r="K13" s="156">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L13" s="158"/>
-      <c r="M13" s="164">
+      <c r="L13" s="156"/>
+      <c r="M13" s="162">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N13" s="164">
+      <c r="N13" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O13" s="158">
+      <c r="O13" s="156">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P13" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P13" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q13" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q13" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R13" s="164">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R13" s="162">
         <f t="shared" si="3"/>
+        <v>150475.56047000003</v>
+      </c>
+      <c r="U13" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="107" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="72"/>
+      <c r="C14" s="91" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="110"/>
+      <c r="F14" s="93">
+        <v>7.9</v>
+      </c>
+      <c r="G14" s="155">
         <v>152965.07008999999</v>
       </c>
-      <c r="U13" s="93" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="109" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="93" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="155" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="112"/>
-      <c r="F14" s="95">
-        <v>7.9</v>
-      </c>
-      <c r="G14" s="157">
-        <v>125031.62204000002</v>
-      </c>
-      <c r="H14" s="73"/>
-      <c r="I14" s="66">
+      <c r="H14" s="71"/>
+      <c r="I14" s="64">
         <f t="shared" si="0"/>
-        <v>125031.62204000002</v>
-      </c>
-      <c r="J14" s="64" t="e">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="J14" s="62" t="e">
         <f>C8*F14/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K14" s="64">
+      <c r="K14" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L14" s="65"/>
-      <c r="M14" s="63">
+      <c r="L14" s="63"/>
+      <c r="M14" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N14" s="63">
+      <c r="N14" s="61">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O14" s="64">
+      <c r="O14" s="62">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P14" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P14" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q14" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q14" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R14" s="63">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R14" s="61">
         <f t="shared" si="3"/>
+        <v>150475.56047000003</v>
+      </c>
+      <c r="U14" s="91" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="107" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="68"/>
+      <c r="C15" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="108" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="110"/>
+      <c r="F15" s="93">
+        <v>7.9</v>
+      </c>
+      <c r="G15" s="69">
         <v>152965.07008999999</v>
       </c>
-      <c r="U14" s="93" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="109" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="110" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="112"/>
-      <c r="F15" s="95">
-        <v>7.9</v>
-      </c>
-      <c r="G15" s="71">
-        <v>408427.27100467531</v>
-      </c>
-      <c r="H15" s="73">
-        <v>0</v>
-      </c>
-      <c r="I15" s="66">
-        <f t="shared" si="0"/>
-        <v>408427.27100467531</v>
-      </c>
-      <c r="J15" s="64" t="e">
+      <c r="H15" s="71">
+        <v>0</v>
+      </c>
+      <c r="I15" s="64">
+        <f>163345-I27</f>
+        <v>152964.73843</v>
+      </c>
+      <c r="J15" s="62" t="e">
         <f>C8*F15/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K15" s="64">
+      <c r="K15" s="62">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="64"/>
-      <c r="M15" s="63">
+        <v>0.33165999999619089</v>
+      </c>
+      <c r="L15" s="62"/>
+      <c r="M15" s="61">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="63">
+        <v>9.9497999998857268E-3</v>
+      </c>
+      <c r="N15" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="64">
+        <v>0.3416097999960766</v>
+      </c>
+      <c r="O15" s="62">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P15" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P15" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q15" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q15" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R15" s="63">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R15" s="61">
         <f t="shared" si="3"/>
+        <v>150475.90207980003</v>
+      </c>
+      <c r="U15" s="91" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="157" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="158"/>
+      <c r="C16" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="159" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="160" t="s">
+        <v>171</v>
+      </c>
+      <c r="F16" s="161">
+        <v>7.9</v>
+      </c>
+      <c r="G16" s="64">
         <v>152965.07008999999</v>
       </c>
-      <c r="U15" s="93" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="159" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="160"/>
-      <c r="C16" s="94" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="161" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16" s="162" t="s">
-        <v>161</v>
-      </c>
-      <c r="F16" s="163">
-        <v>7.9</v>
-      </c>
-      <c r="G16" s="66">
-        <v>125031.34985144658</v>
-      </c>
-      <c r="H16" s="158">
-        <v>0</v>
-      </c>
-      <c r="I16" s="66">
-        <f t="shared" si="0"/>
-        <v>125031.34985144658</v>
-      </c>
-      <c r="J16" s="158" t="e">
+      <c r="H16" s="156">
+        <v>0</v>
+      </c>
+      <c r="I16" s="64">
+        <f>163345-I28</f>
+        <v>152964.73843</v>
+      </c>
+      <c r="J16" s="156" t="e">
         <f>C8*F16/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="158">
+      <c r="K16" s="156">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="158"/>
-      <c r="M16" s="164">
+        <v>0.33165999999619089</v>
+      </c>
+      <c r="L16" s="156"/>
+      <c r="M16" s="162">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="164">
+        <v>9.9497999998857268E-3</v>
+      </c>
+      <c r="N16" s="162">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="158">
+        <v>0.3416097999960766</v>
+      </c>
+      <c r="O16" s="156">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P16" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P16" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q16" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q16" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R16" s="164">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R16" s="162">
         <f t="shared" si="3"/>
+        <v>150475.90207980003</v>
+      </c>
+      <c r="U16" s="91" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="107" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="68"/>
+      <c r="C17" s="91" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="108" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="110" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="93">
+        <v>7.9</v>
+      </c>
+      <c r="G17" s="69">
         <v>152965.07008999999</v>
       </c>
-      <c r="U16" s="93" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="109" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="70"/>
-      <c r="C17" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="110" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="112" t="s">
-        <v>146</v>
-      </c>
-      <c r="F17" s="95">
-        <v>7.9</v>
-      </c>
-      <c r="G17" s="71">
-        <v>125031.43807345279</v>
-      </c>
-      <c r="H17" s="64">
-        <v>0</v>
-      </c>
-      <c r="I17" s="66">
-        <f t="shared" si="0"/>
-        <v>125031.43807345279</v>
-      </c>
-      <c r="J17" s="64" t="e">
+      <c r="H17" s="62">
+        <v>0</v>
+      </c>
+      <c r="I17" s="64">
+        <f>152965-I23</f>
+        <v>142584.73843</v>
+      </c>
+      <c r="J17" s="62" t="e">
         <f>C8*F17/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="64">
+      <c r="K17" s="62">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="64"/>
-      <c r="M17" s="63">
+        <v>10380.331659999996</v>
+      </c>
+      <c r="L17" s="62"/>
+      <c r="M17" s="61">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="63">
+        <v>311.40994979999988</v>
+      </c>
+      <c r="N17" s="61">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="64">
+        <v>10691.741609799996</v>
+      </c>
+      <c r="O17" s="62">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P17" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P17" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q17" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q17" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R17" s="63">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R17" s="61">
         <f t="shared" si="3"/>
+        <v>161167.30207979999</v>
+      </c>
+      <c r="U17" s="91" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="157" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="158"/>
+      <c r="C18" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="159" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="160" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" s="161">
+        <v>7.9</v>
+      </c>
+      <c r="G18" s="64">
         <v>152965.07008999999</v>
       </c>
-      <c r="U17" s="93" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="159" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="160"/>
-      <c r="C18" s="94" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="161" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="162" t="s">
-        <v>147</v>
-      </c>
-      <c r="F18" s="163">
-        <v>7.9</v>
-      </c>
-      <c r="G18" s="66">
-        <v>124838.38386877713</v>
-      </c>
-      <c r="H18" s="158">
-        <v>0</v>
-      </c>
-      <c r="I18" s="66">
-        <f t="shared" si="0"/>
-        <v>124838.38386877713</v>
-      </c>
-      <c r="J18" s="158" t="e">
+      <c r="H18" s="156">
+        <v>0</v>
+      </c>
+      <c r="I18" s="64"/>
+      <c r="J18" s="156" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="158">
+      <c r="K18" s="156">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="158"/>
-      <c r="M18" s="164">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="L18" s="156"/>
+      <c r="M18" s="162">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="164">
+        <v>4588.9521027000001</v>
+      </c>
+      <c r="N18" s="162">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="158">
+        <v>157554.02219269998</v>
+      </c>
+      <c r="O18" s="156">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P18" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P18" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q18" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q18" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R18" s="164">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R18" s="162">
         <f t="shared" si="3"/>
+        <v>308029.58266269998</v>
+      </c>
+      <c r="U18" s="91" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="157" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="158"/>
+      <c r="C19" s="92" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="159" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="160"/>
+      <c r="F19" s="161">
+        <v>7.9</v>
+      </c>
+      <c r="G19" s="64">
         <v>152965.07008999999</v>
       </c>
-      <c r="U18" s="93" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="159" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="160"/>
-      <c r="C19" s="94" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="161" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="162"/>
-      <c r="F19" s="163">
-        <v>7.9</v>
-      </c>
-      <c r="G19" s="66">
-        <v>125025.47008393914</v>
-      </c>
-      <c r="H19" s="158">
-        <v>0</v>
-      </c>
-      <c r="I19" s="66">
+      <c r="H19" s="156">
+        <v>0</v>
+      </c>
+      <c r="I19" s="64">
         <f t="shared" si="0"/>
-        <v>125025.47008393914</v>
-      </c>
-      <c r="J19" s="158" t="e">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="J19" s="156" t="e">
         <f>C8*F19/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="158">
+      <c r="K19" s="156">
         <f t="shared" ref="K19:K29" si="8">G19-H19-I19</f>
         <v>0</v>
       </c>
-      <c r="L19" s="158">
+      <c r="L19" s="156">
         <f>G19-I19</f>
         <v>0</v>
       </c>
-      <c r="M19" s="164">
+      <c r="M19" s="162">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N19" s="164">
+      <c r="N19" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O19" s="158">
+      <c r="O19" s="156">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P19" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P19" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q19" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q19" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R19" s="164">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R19" s="162">
         <f t="shared" si="3"/>
+        <v>150475.56047000003</v>
+      </c>
+      <c r="U19" s="91" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="107" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="68"/>
+      <c r="C20" s="91" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="108" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="110"/>
+      <c r="F20" s="93">
+        <v>7.9</v>
+      </c>
+      <c r="G20" s="69">
         <v>152965.07008999999</v>
       </c>
-      <c r="U19" s="93" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="109" t="s">
+      <c r="H20" s="62"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62">
+        <f t="shared" si="8"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="L20" s="62"/>
+      <c r="M20" s="61">
+        <f t="shared" si="4"/>
+        <v>4588.9521027000001</v>
+      </c>
+      <c r="N20" s="61">
+        <f t="shared" ref="N20:N29" si="9">K20+M20+L20</f>
+        <v>157554.02219269998</v>
+      </c>
+      <c r="O20" s="62">
+        <f t="shared" si="5"/>
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P20" s="64">
+        <f t="shared" si="6"/>
+        <v>27650</v>
+      </c>
+      <c r="Q20" s="64">
+        <f t="shared" si="7"/>
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R20" s="61">
+        <f t="shared" si="3"/>
+        <v>308029.58266269998</v>
+      </c>
+      <c r="U20" s="91" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="157" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="93" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="110" t="s">
+      <c r="B21" s="158"/>
+      <c r="C21" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="159" t="s">
         <v>107</v>
       </c>
-      <c r="E20" s="112"/>
-      <c r="F20" s="95">
+      <c r="E21" s="160" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="161">
         <v>7.9</v>
       </c>
-      <c r="G20" s="71">
-        <v>125031.62204000002</v>
-      </c>
-      <c r="H20" s="64"/>
-      <c r="I20" s="66">
-        <f t="shared" si="0"/>
-        <v>125031.62204000002</v>
-      </c>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64">
+      <c r="G21" s="64">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="H21" s="156"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="156"/>
+      <c r="K21" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="64"/>
-      <c r="M20" s="63">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="L21" s="156"/>
+      <c r="M21" s="162">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="63">
-        <f t="shared" ref="N20:N29" si="9">K20+M20+L20</f>
-        <v>0</v>
-      </c>
-      <c r="O20" s="64">
+        <v>4588.9521027000001</v>
+      </c>
+      <c r="N21" s="162">
+        <f t="shared" si="9"/>
+        <v>157554.02219269998</v>
+      </c>
+      <c r="O21" s="156">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P20" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P21" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q20" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q21" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R20" s="63">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R21" s="162">
         <f t="shared" si="3"/>
+        <v>308029.58266269998</v>
+      </c>
+      <c r="U21" s="91" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="157" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="158"/>
+      <c r="C22" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="159" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="160" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22" s="161">
+        <v>7.9</v>
+      </c>
+      <c r="G22" s="64">
         <v>152965.07008999999</v>
       </c>
-      <c r="U20" s="93" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="159" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="160"/>
-      <c r="C21" s="94" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="161" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" s="162" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="163">
-        <v>7.9</v>
-      </c>
-      <c r="G21" s="66">
-        <v>120968.14931198064</v>
-      </c>
-      <c r="H21" s="158"/>
-      <c r="I21" s="66">
-        <f t="shared" si="0"/>
-        <v>120968.14931198064</v>
-      </c>
-      <c r="J21" s="158"/>
-      <c r="K21" s="158">
+      <c r="H22" s="156"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="156"/>
+      <c r="K22" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="158"/>
-      <c r="M21" s="164">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="L22" s="156"/>
+      <c r="M22" s="162">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="164">
+        <v>4588.9521027000001</v>
+      </c>
+      <c r="N22" s="162">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="158">
+        <v>157554.02219269998</v>
+      </c>
+      <c r="O22" s="156">
         <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P21" s="66">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P22" s="64">
         <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q21" s="66">
+        <v>27650</v>
+      </c>
+      <c r="Q22" s="64">
         <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R21" s="164">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R22" s="162">
         <f t="shared" si="3"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="U21" s="93" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="159" t="s">
+        <v>308029.58266269998</v>
+      </c>
+      <c r="S22" s="177"/>
+      <c r="U22" s="91" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="107"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="160"/>
-      <c r="C22" s="94" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="161" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" s="162" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="163">
-        <v>7.9</v>
-      </c>
-      <c r="G22" s="66">
-        <v>125031.53639642705</v>
-      </c>
-      <c r="H22" s="158"/>
-      <c r="I22" s="66">
-        <f t="shared" si="0"/>
-        <v>125031.53639642705</v>
-      </c>
-      <c r="J22" s="158"/>
-      <c r="K22" s="158">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="158"/>
-      <c r="M22" s="164">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="164">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="158">
-        <f t="shared" si="5"/>
-        <v>75621.805949999994</v>
-      </c>
-      <c r="P22" s="66">
-        <f t="shared" si="6"/>
-        <v>35194.5</v>
-      </c>
-      <c r="Q22" s="66">
-        <f t="shared" si="7"/>
-        <v>42148.764140000007</v>
-      </c>
-      <c r="R22" s="164">
-        <f t="shared" si="3"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="S22" s="179"/>
-      <c r="U22" s="93" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="109"/>
-      <c r="B23" s="70"/>
-      <c r="C23" s="93" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="111" t="str">
+      <c r="D23" s="109" t="str">
         <f>D17</f>
         <v>Estevez Norberto Omar</v>
       </c>
-      <c r="E23" s="112" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="95">
+      <c r="E23" s="110" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23" s="93">
         <v>0.74</v>
       </c>
-      <c r="G23" s="71">
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="H23" s="64"/>
-      <c r="I23" s="66">
-        <f t="shared" si="0"/>
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64">
+      <c r="G23" s="69">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="H23" s="62"/>
+      <c r="I23" s="64">
+        <f>G23</f>
+        <v>10380.261569999999</v>
+      </c>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L23" s="64"/>
-      <c r="M23" s="63">
+      <c r="L23" s="62"/>
+      <c r="M23" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N23" s="63">
+      <c r="N23" s="61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O23" s="64">
+      <c r="O23" s="62">
         <f t="shared" si="5"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P23" s="66">
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P23" s="64">
         <f t="shared" si="6"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="63">
+        <v>2590</v>
+      </c>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="61">
         <f t="shared" si="3"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="U23" s="93" t="s">
+        <v>10595.689186</v>
+      </c>
+      <c r="U23" s="91" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="159"/>
-      <c r="B24" s="160"/>
-      <c r="C24" s="94" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="165" t="str">
+    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="157"/>
+      <c r="B24" s="158"/>
+      <c r="C24" s="92" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="163" t="str">
         <f>D21</f>
         <v>Moro Vanesa Yania / Juan Carlos Moro</v>
       </c>
-      <c r="E24" s="162" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" s="163">
+      <c r="E24" s="160" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="161">
         <v>0.74</v>
       </c>
-      <c r="G24" s="66">
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="H24" s="158"/>
-      <c r="I24" s="66">
-        <f t="shared" si="0"/>
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="J24" s="158"/>
-      <c r="K24" s="158">
+      <c r="G24" s="64">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="H24" s="156"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="156"/>
+      <c r="K24" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="158"/>
-      <c r="M24" s="164">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="L24" s="156"/>
+      <c r="M24" s="162">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="164">
+        <v>311.40784709999997</v>
+      </c>
+      <c r="N24" s="162">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="158">
+        <v>10691.669417099998</v>
+      </c>
+      <c r="O24" s="156">
         <f t="shared" si="5"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P24" s="66">
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P24" s="64">
         <f t="shared" si="6"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q24" s="158">
+        <v>2590</v>
+      </c>
+      <c r="Q24" s="156">
         <f>'Calculo Servicios  (2)'!H22</f>
         <v>0</v>
       </c>
-      <c r="R24" s="164">
+      <c r="R24" s="162">
         <f t="shared" si="3"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="U24" s="93" t="s">
+        <v>21287.358603099998</v>
+      </c>
+      <c r="U24" s="91" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="109"/>
-      <c r="B25" s="70"/>
-      <c r="C25" s="93" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="111" t="str">
+    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="107"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="91" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="109" t="str">
         <f>D20</f>
         <v>Scarlercio Jorge Omar</v>
       </c>
-      <c r="E25" s="111"/>
-      <c r="F25" s="95">
+      <c r="E25" s="109"/>
+      <c r="F25" s="93">
         <v>0.74</v>
       </c>
-      <c r="G25" s="71">
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="H25" s="64"/>
-      <c r="I25" s="66">
-        <f t="shared" ref="I25" si="10">G25</f>
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64">
+      <c r="G25" s="69">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="H25" s="62"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="64"/>
-      <c r="M25" s="63">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="L25" s="62"/>
+      <c r="M25" s="61">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="63">
+        <v>311.40784709999997</v>
+      </c>
+      <c r="N25" s="61">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="64">
+        <v>10691.669417099998</v>
+      </c>
+      <c r="O25" s="62">
         <f t="shared" si="5"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P25" s="66">
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P25" s="64">
         <f t="shared" si="6"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q25" s="64">
+        <v>2590</v>
+      </c>
+      <c r="Q25" s="62">
         <f>'Calculo Servicios  (2)'!H23</f>
         <v>0</v>
       </c>
-      <c r="R25" s="63">
+      <c r="R25" s="61">
         <f t="shared" si="3"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="U25" s="93" t="s">
+        <v>21287.358603099998</v>
+      </c>
+      <c r="U25" s="91" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="159"/>
-      <c r="B26" s="156"/>
-      <c r="C26" s="94" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="165" t="str">
+    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="157"/>
+      <c r="B26" s="154"/>
+      <c r="C26" s="92" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="163" t="str">
         <f>D18</f>
         <v>Lopez Gabriela</v>
       </c>
-      <c r="E26" s="162" t="s">
-        <v>147</v>
-      </c>
-      <c r="F26" s="163">
+      <c r="E26" s="160" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="161">
         <v>0.74</v>
       </c>
-      <c r="G26" s="66">
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="H26" s="158">
-        <v>0</v>
-      </c>
-      <c r="I26" s="66">
-        <f>G26</f>
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="J26" s="158" t="e">
+      <c r="G26" s="64">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="H26" s="156">
+        <v>0</v>
+      </c>
+      <c r="I26" s="64"/>
+      <c r="J26" s="156" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="158">
+      <c r="K26" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="158"/>
-      <c r="M26" s="164">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="L26" s="156"/>
+      <c r="M26" s="162">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="164">
+        <v>311.40784709999997</v>
+      </c>
+      <c r="N26" s="162">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="158">
+        <v>10691.669417099998</v>
+      </c>
+      <c r="O26" s="156">
         <f t="shared" si="5"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P26" s="66">
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P26" s="64">
         <f t="shared" si="6"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q26" s="158">
+        <v>2590</v>
+      </c>
+      <c r="Q26" s="156">
         <f>'Calculo Servicios  (2)'!H24</f>
         <v>0</v>
       </c>
-      <c r="R26" s="164">
+      <c r="R26" s="162">
         <f t="shared" si="3"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="U26" s="93" t="s">
+        <v>21287.358603099998</v>
+      </c>
+      <c r="U26" s="91" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="109"/>
-      <c r="B27" s="70"/>
-      <c r="C27" s="93" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="111" t="str">
+    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="107"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="109" t="str">
         <f>D15</f>
         <v>Cecilia Mariel Cassettari</v>
       </c>
-      <c r="E27" s="111"/>
-      <c r="F27" s="95">
+      <c r="E27" s="109"/>
+      <c r="F27" s="93">
         <v>0.74</v>
       </c>
-      <c r="G27" s="71">
-        <v>28929.782859621002</v>
-      </c>
-      <c r="H27" s="64">
-        <v>0</v>
-      </c>
-      <c r="I27" s="66">
+      <c r="G27" s="69">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="H27" s="62">
+        <v>0</v>
+      </c>
+      <c r="I27" s="64">
         <f>G27</f>
-        <v>28929.782859621002</v>
-      </c>
-      <c r="J27" s="64" t="e">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="J27" s="62" t="e">
         <f>C8*F27/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K27" s="64">
+      <c r="K27" s="62">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L27" s="64"/>
-      <c r="M27" s="63">
+      <c r="L27" s="62"/>
+      <c r="M27" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N27" s="63">
+      <c r="N27" s="61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O27" s="64">
+      <c r="O27" s="62">
         <f t="shared" si="5"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P27" s="66">
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P27" s="64">
         <f t="shared" si="6"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q27" s="64">
+        <v>2590</v>
+      </c>
+      <c r="Q27" s="62">
         <f>'Calculo Servicios  (2)'!H25</f>
         <v>0</v>
       </c>
-      <c r="R27" s="63">
+      <c r="R27" s="61">
         <f t="shared" si="3"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="U27" s="93" t="s">
+        <v>10595.689186</v>
+      </c>
+      <c r="U27" s="91" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="183"/>
-      <c r="B28" s="184"/>
-      <c r="C28" s="94" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" s="165" t="str">
+    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="181"/>
+      <c r="B28" s="182"/>
+      <c r="C28" s="92" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="163" t="str">
         <f>D16</f>
         <v>Perez Sebastian</v>
       </c>
-      <c r="E28" s="162" t="s">
-        <v>161</v>
-      </c>
-      <c r="F28" s="185">
+      <c r="E28" s="160" t="s">
+        <v>171</v>
+      </c>
+      <c r="F28" s="183">
         <v>0.74</v>
       </c>
-      <c r="G28" s="66">
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="H28" s="66">
-        <v>0</v>
-      </c>
-      <c r="I28" s="66">
+      <c r="G28" s="64">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="H28" s="64">
+        <v>0</v>
+      </c>
+      <c r="I28" s="64">
         <f>G28</f>
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="J28" s="66">
-        <v>0</v>
-      </c>
-      <c r="K28" s="66">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="J28" s="64">
+        <v>0</v>
+      </c>
+      <c r="K28" s="64">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L28" s="66"/>
-      <c r="M28" s="178">
+      <c r="L28" s="64"/>
+      <c r="M28" s="176">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N28" s="178">
+      <c r="N28" s="176">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O28" s="66">
+      <c r="O28" s="64">
         <f t="shared" si="5"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P28" s="66">
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P28" s="64">
         <f t="shared" si="6"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q28" s="66">
+        <v>2590</v>
+      </c>
+      <c r="Q28" s="64">
         <f>'Calculo Servicios  (2)'!H26</f>
         <v>0</v>
       </c>
-      <c r="R28" s="178">
+      <c r="R28" s="176">
         <f t="shared" si="3"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="U28" s="93" t="s">
+        <v>10595.689186</v>
+      </c>
+      <c r="U28" s="91" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="159"/>
-      <c r="B29" s="172"/>
-      <c r="C29" s="94" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" s="165" t="str">
+    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="157"/>
+      <c r="B29" s="170"/>
+      <c r="C29" s="92" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="163" t="str">
         <f>D22</f>
         <v>Rodriguez Flavio/Rodriguez Mauro</v>
       </c>
-      <c r="E29" s="162" t="s">
-        <v>153</v>
-      </c>
-      <c r="F29" s="181">
+      <c r="E29" s="160" t="s">
+        <v>152</v>
+      </c>
+      <c r="F29" s="179">
         <v>0.74</v>
       </c>
-      <c r="G29" s="66">
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="H29" s="158">
-        <v>0</v>
-      </c>
-      <c r="I29" s="66">
-        <f>G29</f>
-        <v>7911.3758160000007</v>
-      </c>
-      <c r="J29" s="158" t="e">
+      <c r="G29" s="64">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="H29" s="156">
+        <v>0</v>
+      </c>
+      <c r="I29" s="64"/>
+      <c r="J29" s="156" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="158">
+      <c r="K29" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="158"/>
-      <c r="M29" s="164">
+        <v>10380.261569999999</v>
+      </c>
+      <c r="L29" s="156"/>
+      <c r="M29" s="162">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="164">
+        <v>311.40784709999997</v>
+      </c>
+      <c r="N29" s="162">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="158">
+        <v>10691.669417099998</v>
+      </c>
+      <c r="O29" s="156">
         <f t="shared" si="5"/>
-        <v>7083.5615699999989</v>
-      </c>
-      <c r="P29" s="66">
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P29" s="64">
         <f t="shared" si="6"/>
-        <v>3296.7</v>
-      </c>
-      <c r="Q29" s="158">
+        <v>2590</v>
+      </c>
+      <c r="Q29" s="156">
         <f>'Calculo Servicios  (2)'!H27</f>
         <v>0</v>
       </c>
-      <c r="R29" s="164">
+      <c r="R29" s="162">
         <f t="shared" si="3"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="U29" s="94" t="s">
+        <v>21287.358603099998</v>
+      </c>
+      <c r="U29" s="92" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="72"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="64">
-        <v>0</v>
-      </c>
-      <c r="I30" s="66"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="63"/>
-      <c r="N30" s="63"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64" t="e">
+    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="70"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="62">
+        <v>0</v>
+      </c>
+      <c r="I30" s="64"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="63"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62" t="e">
         <f>#REF!*F30/100</f>
         <v>#REF!</v>
       </c>
-      <c r="Q30" s="64"/>
-      <c r="R30" s="108"/>
-      <c r="U30" s="93" t="s">
+      <c r="Q30" s="62"/>
+      <c r="R30" s="106"/>
+      <c r="U30" s="91" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="57" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="228"/>
-      <c r="B31" s="229"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="60">
+    <row r="31" spans="1:21" s="55" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="226"/>
+      <c r="B31" s="227"/>
+      <c r="C31" s="227"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="58">
         <f>SUM(G11:G30)</f>
-        <v>1986523.3583134203</v>
-      </c>
-      <c r="H31" s="60">
+        <v>1908242.672070001</v>
+      </c>
+      <c r="H31" s="58">
         <f>SUM(H11:H30)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="61">
+      <c r="I31" s="59">
         <f>SUM(I11:I30)</f>
-        <v>1986523.3583134203</v>
-      </c>
-      <c r="J31" s="60"/>
-      <c r="K31" s="61">
+        <v>1244480.3504500003</v>
+      </c>
+      <c r="J31" s="58"/>
+      <c r="K31" s="59">
         <f>SUM(K11:K30)</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="60"/>
-      <c r="M31" s="59"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="61">
+        <v>663762.32161999983</v>
+      </c>
+      <c r="L31" s="58"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="59">
         <f>SUM(O11:O30)</f>
-        <v>957046.6023899999</v>
-      </c>
-      <c r="P31" s="61">
+        <v>1081633.520022</v>
+      </c>
+      <c r="P31" s="59">
         <f>SUM(P11:P29)</f>
-        <v>445410.90000000008</v>
-      </c>
-      <c r="Q31" s="61">
+        <v>349930</v>
+      </c>
+      <c r="Q31" s="59">
         <f>SUM(Q11:Q29)</f>
-        <v>505785.16967999999</v>
-      </c>
-      <c r="R31" s="61">
+        <v>448313.02991999994</v>
+      </c>
+      <c r="R31" s="59">
         <f>SUM(R11:R29)</f>
-        <v>1908242.672070001</v>
-      </c>
-      <c r="U31" s="93" t="s">
+        <v>2563551.741210599</v>
+      </c>
+      <c r="U31" s="91" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="225" t="s">
+    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="223" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="226"/>
-      <c r="D32" s="226"/>
-      <c r="E32" s="226"/>
-      <c r="F32" s="226"/>
-      <c r="G32" s="226"/>
-      <c r="H32" s="226"/>
-      <c r="I32" s="226"/>
-      <c r="J32" s="226"/>
-      <c r="K32" s="226"/>
-      <c r="L32" s="226"/>
-      <c r="M32" s="226"/>
-      <c r="N32" s="226"/>
-      <c r="O32" s="226"/>
-      <c r="P32" s="226"/>
-      <c r="Q32" s="226"/>
-      <c r="R32" s="227"/>
-      <c r="U32" s="93" t="s">
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="224"/>
+      <c r="J32" s="224"/>
+      <c r="K32" s="224"/>
+      <c r="L32" s="224"/>
+      <c r="M32" s="224"/>
+      <c r="N32" s="224"/>
+      <c r="O32" s="224"/>
+      <c r="P32" s="224"/>
+      <c r="Q32" s="224"/>
+      <c r="R32" s="225"/>
+      <c r="U32" s="91" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="F33" s="56"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55" t="s">
+    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="F33" s="54"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="L33" s="55"/>
-      <c r="U33" s="93" t="s">
+      <c r="L33" s="53"/>
+      <c r="U33" s="91" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C34" s="220"/>
-      <c r="D34" s="220"/>
-      <c r="E34" s="220"/>
-      <c r="F34" s="220"/>
-      <c r="G34" s="220"/>
-      <c r="H34" s="220"/>
-      <c r="I34" s="220"/>
-      <c r="J34" s="220"/>
-      <c r="K34" s="220"/>
-      <c r="L34" s="220"/>
-      <c r="M34" s="220"/>
-      <c r="N34" s="220"/>
-      <c r="O34" s="220"/>
-    </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C35" s="220"/>
-      <c r="D35" s="220"/>
-      <c r="E35" s="220"/>
-      <c r="F35" s="220"/>
-      <c r="G35" s="220"/>
-      <c r="H35" s="220"/>
-      <c r="I35" s="220"/>
-      <c r="J35" s="220"/>
-      <c r="K35" s="220"/>
-      <c r="L35" s="220"/>
-      <c r="M35" s="220"/>
-      <c r="N35" s="220"/>
-      <c r="O35" s="220"/>
-    </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C36" s="220"/>
-      <c r="D36" s="220"/>
-      <c r="E36" s="220"/>
-      <c r="F36" s="220"/>
-      <c r="G36" s="220"/>
-      <c r="H36" s="220"/>
-      <c r="I36" s="220"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="220"/>
-      <c r="L36" s="220"/>
-      <c r="M36" s="220"/>
-      <c r="N36" s="220"/>
-      <c r="O36" s="220"/>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C37" s="220"/>
-      <c r="D37" s="220"/>
-      <c r="E37" s="220"/>
-      <c r="F37" s="220"/>
-      <c r="G37" s="220"/>
-      <c r="H37" s="220"/>
-      <c r="I37" s="220"/>
-      <c r="J37" s="220"/>
-      <c r="K37" s="220"/>
-      <c r="L37" s="220"/>
-      <c r="M37" s="220"/>
-      <c r="N37" s="220"/>
-      <c r="O37" s="220"/>
-    </row>
-    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="220"/>
-      <c r="D38" s="220"/>
-      <c r="E38" s="220"/>
-      <c r="F38" s="220"/>
-      <c r="G38" s="220"/>
-      <c r="H38" s="220"/>
-      <c r="I38" s="220"/>
-      <c r="J38" s="220"/>
-      <c r="K38" s="220"/>
-      <c r="L38" s="220"/>
-      <c r="M38" s="220"/>
-      <c r="N38" s="220"/>
-      <c r="O38" s="220"/>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C34" s="218"/>
+      <c r="D34" s="218"/>
+      <c r="E34" s="218"/>
+      <c r="F34" s="218"/>
+      <c r="G34" s="218"/>
+      <c r="H34" s="218"/>
+      <c r="I34" s="218"/>
+      <c r="J34" s="218"/>
+      <c r="K34" s="218"/>
+      <c r="L34" s="218"/>
+      <c r="M34" s="218"/>
+      <c r="N34" s="218"/>
+      <c r="O34" s="218"/>
+    </row>
+    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C35" s="218"/>
+      <c r="D35" s="218"/>
+      <c r="E35" s="218"/>
+      <c r="F35" s="218"/>
+      <c r="G35" s="218"/>
+      <c r="H35" s="218"/>
+      <c r="I35" s="218"/>
+      <c r="J35" s="218"/>
+      <c r="K35" s="218"/>
+      <c r="L35" s="218"/>
+      <c r="M35" s="218"/>
+      <c r="N35" s="218"/>
+      <c r="O35" s="218"/>
+    </row>
+    <row r="36" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C36" s="218"/>
+      <c r="D36" s="218"/>
+      <c r="E36" s="218"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="218"/>
+      <c r="H36" s="218"/>
+      <c r="I36" s="218"/>
+      <c r="J36" s="218"/>
+      <c r="K36" s="218"/>
+      <c r="L36" s="218"/>
+      <c r="M36" s="218"/>
+      <c r="N36" s="218"/>
+      <c r="O36" s="218"/>
+    </row>
+    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C37" s="218"/>
+      <c r="D37" s="218"/>
+      <c r="E37" s="218"/>
+      <c r="F37" s="218"/>
+      <c r="G37" s="218"/>
+      <c r="H37" s="218"/>
+      <c r="I37" s="218"/>
+      <c r="J37" s="218"/>
+      <c r="K37" s="218"/>
+      <c r="L37" s="218"/>
+      <c r="M37" s="218"/>
+      <c r="N37" s="218"/>
+      <c r="O37" s="218"/>
+    </row>
+    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="218"/>
+      <c r="D38" s="218"/>
+      <c r="E38" s="218"/>
+      <c r="F38" s="218"/>
+      <c r="G38" s="218"/>
+      <c r="H38" s="218"/>
+      <c r="I38" s="218"/>
+      <c r="J38" s="218"/>
+      <c r="K38" s="218"/>
+      <c r="L38" s="218"/>
+      <c r="M38" s="218"/>
+      <c r="N38" s="218"/>
+      <c r="O38" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4474,1012 +3803,1726 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="190">
+        <v>1153202676</v>
+      </c>
+      <c r="F2" s="190"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="D3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="J4" s="189"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="D5" s="191" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" s="191"/>
+      <c r="F5" s="191"/>
+      <c r="G5" s="191"/>
+      <c r="H5" s="192"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="D6" s="191"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="192"/>
+    </row>
+    <row r="7" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="D7" s="191"/>
+      <c r="E7" s="191"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="191"/>
+      <c r="H7" s="192"/>
+    </row>
+    <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="204" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="204"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="204"/>
+      <c r="F13" s="204"/>
+      <c r="G13" s="204"/>
+      <c r="H13" s="204"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="239"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="186">
+        <f>392270+392270*2%</f>
+        <v>400115.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="95" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="186">
+        <v>4030.28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="178">
+        <f>SUM(H14:H16)</f>
+        <v>404145.68000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="40"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="205" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="206"/>
+      <c r="C19" s="206"/>
+      <c r="D19" s="206"/>
+      <c r="E19" s="206"/>
+      <c r="F19" s="206"/>
+      <c r="G19" s="206"/>
+      <c r="H19" s="207"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="25">
+        <f>17878.5*2</f>
+        <v>35757</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="25">
+        <v>472904.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="26">
+        <f>SUM(H20:H21)</f>
+        <v>508661.04</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="208" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="208"/>
+      <c r="C23" s="208"/>
+      <c r="D23" s="208"/>
+      <c r="E23" s="208"/>
+      <c r="F23" s="208"/>
+      <c r="G23" s="208"/>
+      <c r="H23" s="208"/>
+      <c r="J23" s="25"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="95" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="25">
+        <v>46638</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="95" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="25">
+        <v>26600</v>
+      </c>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="95" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="25">
+        <v>224969.09</v>
+      </c>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="95" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="25">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="26">
+        <f>SUM(H24:H27)</f>
+        <v>373207.08999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="205" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="206"/>
+      <c r="C29" s="206"/>
+      <c r="D29" s="206"/>
+      <c r="E29" s="206"/>
+      <c r="F29" s="206"/>
+      <c r="G29" s="206"/>
+      <c r="H29" s="207"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="240">
+        <v>90000</v>
+      </c>
+      <c r="I30" s="41"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="240">
+        <v>45000</v>
+      </c>
+      <c r="I31" s="41"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="240">
+        <v>120000</v>
+      </c>
+      <c r="I32" s="41"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="187">
+        <f>SUM(H30:H32)</f>
+        <v>255000</v>
+      </c>
+      <c r="I33" s="41"/>
+      <c r="N33" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="18"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="27"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="205" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" s="206"/>
+      <c r="C35" s="206"/>
+      <c r="D35" s="206"/>
+      <c r="E35" s="206"/>
+      <c r="F35" s="206"/>
+      <c r="G35" s="206"/>
+      <c r="H35" s="207"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="49">
+        <v>13740.12</v>
+      </c>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="37" spans="1:14" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="30">
+        <f>H17+H22+H28+H33+H36</f>
+        <v>1554753.9300000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="45"/>
+    </row>
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="195" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="196"/>
+      <c r="C39" s="196"/>
+      <c r="D39" s="196"/>
+      <c r="E39" s="196"/>
+      <c r="F39" s="196"/>
+      <c r="G39" s="196"/>
+      <c r="H39" s="197"/>
+      <c r="I39" s="164"/>
+      <c r="K39" s="164"/>
+    </row>
+    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="198"/>
+      <c r="B40" s="199"/>
+      <c r="C40" s="199"/>
+      <c r="D40" s="199"/>
+      <c r="E40" s="199"/>
+      <c r="F40" s="199"/>
+      <c r="G40" s="199"/>
+      <c r="H40" s="200"/>
+    </row>
+    <row r="41" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="209" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" s="210"/>
+      <c r="C41" s="210"/>
+      <c r="D41" s="210"/>
+      <c r="E41" s="210"/>
+      <c r="F41" s="210"/>
+      <c r="G41" s="211"/>
+      <c r="H41" s="188">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="212"/>
+      <c r="B42" s="213"/>
+      <c r="C42" s="213"/>
+      <c r="D42" s="213"/>
+      <c r="E42" s="213"/>
+      <c r="F42" s="213"/>
+      <c r="G42" s="214"/>
+      <c r="H42" s="31"/>
+    </row>
+    <row r="43" spans="1:14" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="215" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="216"/>
+      <c r="C43" s="216"/>
+      <c r="D43" s="216"/>
+      <c r="E43" s="216"/>
+      <c r="F43" s="216"/>
+      <c r="G43" s="217"/>
+      <c r="H43" s="32">
+        <f>SUM(H41:H42)</f>
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="184"/>
+      <c r="B44" s="184"/>
+      <c r="C44" s="184"/>
+      <c r="D44" s="184"/>
+      <c r="E44" s="184"/>
+      <c r="F44" s="184"/>
+      <c r="G44" s="184"/>
+      <c r="H44" s="185"/>
+    </row>
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H45" s="19"/>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="193" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="193"/>
+      <c r="C46" s="193"/>
+      <c r="D46" s="193"/>
+      <c r="E46" s="193"/>
+      <c r="F46" s="193"/>
+      <c r="G46" s="193"/>
+      <c r="H46" s="30">
+        <f>+H37+H38</f>
+        <v>1554753.9300000002</v>
+      </c>
+      <c r="J46" s="164"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+    </row>
+    <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="33">
+        <f>H43</f>
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="19"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+    </row>
+    <row r="50" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="201" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" s="202"/>
+      <c r="C50" s="202"/>
+      <c r="D50" s="202"/>
+      <c r="E50" s="202"/>
+      <c r="F50" s="202"/>
+      <c r="G50" s="202"/>
+      <c r="H50" s="203"/>
+    </row>
+    <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="194" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="194"/>
+      <c r="C51" s="194"/>
+      <c r="D51" s="194"/>
+      <c r="E51" s="194"/>
+      <c r="F51" s="194"/>
+      <c r="G51" s="194"/>
+      <c r="H51" s="39">
+        <v>2287941.4208707316</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="35"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="42">
+        <f>Planilla!I31</f>
+        <v>1244480.3504500003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="36">
+        <f>-(H37+H43)</f>
+        <v>-1904753.9300000002</v>
+      </c>
+      <c r="J53" s="15"/>
+    </row>
+    <row r="54" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A54" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="46">
+        <f>SUM(H51:H53)</f>
+        <v>1627667.8413207317</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D5:H7"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A39:H40"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A41:G41"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="113" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="113" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="113" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="113" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="113" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.44140625" style="113" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="113" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.44140625" style="113"/>
-    <col min="13" max="13" width="14.6640625" style="113" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="113" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.44140625" style="113"/>
+    <col min="1" max="1" width="12.140625" style="111" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="111" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="111" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="111" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="111" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="111" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="111" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.42578125" style="111"/>
+    <col min="13" max="13" width="14.7109375" style="111" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="111" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="111"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="232" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="234"/>
-    </row>
-    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="154"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="153" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="230" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="150"/>
-    </row>
-    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="152">
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="232"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="152"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="151" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="148"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="150">
         <f>13+28+19</f>
         <v>60</v>
       </c>
-      <c r="B3" s="107">
+      <c r="B3" s="105">
         <v>10531.71</v>
       </c>
-      <c r="C3" s="151">
+      <c r="C3" s="149">
         <f>+B3/A3</f>
         <v>175.52849999999998</v>
       </c>
-      <c r="D3" s="151">
+      <c r="D3" s="149">
         <v>4863.8999999999996</v>
       </c>
-      <c r="E3" s="150" t="s">
-        <v>140</v>
-      </c>
-      <c r="I3" s="113" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="149"/>
-      <c r="B4" s="148"/>
-      <c r="C4" s="148"/>
-      <c r="D4" s="148"/>
-      <c r="E4" s="147"/>
-    </row>
-    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="146"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="146"/>
-      <c r="E5" s="146"/>
-    </row>
-    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="146"/>
-      <c r="B6" s="146"/>
-      <c r="C6" s="146"/>
-      <c r="D6" s="146"/>
-      <c r="E6" s="146"/>
-    </row>
-    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="235" t="s">
+      <c r="E3" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="I3" s="111" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="236"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="237"/>
-      <c r="L7" s="113" t="s">
+    </row>
+    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="147"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="145"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="144"/>
+      <c r="B5" s="144"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+    </row>
+    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="144"/>
+      <c r="B6" s="144"/>
+      <c r="C6" s="144"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="144"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="233" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="234"/>
+      <c r="C7" s="234"/>
+      <c r="D7" s="234"/>
+      <c r="E7" s="234"/>
+      <c r="F7" s="234"/>
+      <c r="G7" s="234"/>
+      <c r="H7" s="235"/>
+      <c r="L7" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="111" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="104">
+        <v>400523.88</v>
+      </c>
+      <c r="B8" s="142" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="142" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="142" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="113" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="106">
-        <v>400523.88</v>
-      </c>
-      <c r="B8" s="144" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="144" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="144" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="145">
+      <c r="E8" s="143">
         <f>3935/2</f>
         <v>1967.5</v>
       </c>
-      <c r="F8" s="144" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="144" t="s">
+      <c r="F8" s="142" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="143" t="s">
+      <c r="G8" s="142" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="139">
+      <c r="H8" s="141" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="137">
         <v>19</v>
       </c>
-      <c r="L8" s="125">
+      <c r="L8" s="123">
         <v>7502.93</v>
       </c>
-      <c r="M8" s="125">
+      <c r="M8" s="123">
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="142" t="s">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="139">
+      <c r="B9" s="137">
         <v>1617</v>
       </c>
-      <c r="C9" s="139">
+      <c r="C9" s="137">
         <f>B9+J25</f>
         <v>1689</v>
       </c>
-      <c r="D9" s="139">
+      <c r="D9" s="137">
         <f t="shared" ref="D9:D20" si="0">+C9-B9</f>
         <v>72</v>
       </c>
-      <c r="E9" s="103">
+      <c r="E9" s="101">
         <f>+D9/E8</f>
         <v>3.6594663278271919E-2</v>
       </c>
-      <c r="F9" s="102">
+      <c r="F9" s="100">
         <f>+A8*E9</f>
         <v>14657.036523506989</v>
       </c>
-      <c r="G9" s="102">
+      <c r="G9" s="100">
         <f>+(A8*A23)/12</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H9" s="101">
+      <c r="H9" s="99">
         <f>+G9+F9</f>
         <v>24606.517913595933</v>
       </c>
-      <c r="K9" s="113">
+      <c r="K9" s="111">
         <v>106</v>
       </c>
-      <c r="L9" s="125">
+      <c r="L9" s="123">
         <f>+L8*O9</f>
         <v>1575.6152999999999</v>
       </c>
-      <c r="M9" s="113">
+      <c r="M9" s="111">
         <f>M8*21%</f>
         <v>496.70460000000003</v>
       </c>
-      <c r="N9" s="113" t="s">
-        <v>69</v>
-      </c>
-      <c r="O9" s="105">
+      <c r="N9" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="O9" s="103">
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="140" t="s">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="139">
+      <c r="B10" s="137">
         <v>4104</v>
       </c>
-      <c r="C10" s="139">
+      <c r="C10" s="137">
         <f t="shared" ref="C10:C20" si="1">B10+J26</f>
         <v>4195</v>
       </c>
-      <c r="D10" s="139">
+      <c r="D10" s="137">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="E10" s="103">
+      <c r="E10" s="101">
         <f>+D10/E8</f>
         <v>4.6251588310038116E-2</v>
       </c>
-      <c r="F10" s="102">
+      <c r="F10" s="100">
         <f>+A8*E10</f>
         <v>18524.865606099109</v>
       </c>
-      <c r="G10" s="102">
+      <c r="G10" s="100">
         <f>+G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H10" s="101">
+      <c r="H10" s="99">
         <f>+G10+F10</f>
         <v>28474.346996188055</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="111">
         <v>60</v>
       </c>
-      <c r="L10" s="125">
+      <c r="L10" s="123">
         <f>+L8*O10</f>
         <v>481.98822320000005</v>
       </c>
-      <c r="M10" s="113">
+      <c r="M10" s="111">
         <f>+M8*6.424%</f>
         <v>151.94430240000003</v>
       </c>
-      <c r="N10" s="113" t="s">
-        <v>68</v>
-      </c>
-      <c r="O10" s="104">
+      <c r="N10" s="111" t="s">
+        <v>67</v>
+      </c>
+      <c r="O10" s="102">
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="140" t="s">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="139">
+      <c r="B11" s="137">
         <v>7644</v>
       </c>
-      <c r="C11" s="139">
+      <c r="C11" s="137">
         <f t="shared" si="1"/>
         <v>7807</v>
       </c>
-      <c r="D11" s="139">
+      <c r="D11" s="137">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="E11" s="103">
+      <c r="E11" s="101">
         <f>+D11/E8</f>
         <v>8.2846251588310035E-2</v>
       </c>
-      <c r="F11" s="102">
+      <c r="F11" s="100">
         <f>+A8*E11</f>
         <v>33181.902129606096</v>
       </c>
-      <c r="G11" s="102">
+      <c r="G11" s="100">
         <f>G10</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H11" s="101">
+      <c r="H11" s="99">
         <f>+G11+F11</f>
         <v>43131.383519695039</v>
       </c>
-      <c r="K11" s="113">
+      <c r="K11" s="111">
         <v>79</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="123">
         <f>+L8*0.001%</f>
         <v>7.5029300000000007E-2</v>
       </c>
-      <c r="M11" s="113">
+      <c r="M11" s="111">
         <v>0.03</v>
       </c>
-      <c r="N11" s="113" t="s">
-        <v>67</v>
-      </c>
-      <c r="O11" s="125">
+      <c r="N11" s="111" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="123">
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="140" t="s">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="139">
+      <c r="B12" s="137">
         <v>6554</v>
       </c>
-      <c r="C12" s="139">
+      <c r="C12" s="137">
         <f t="shared" si="1"/>
         <v>6730</v>
       </c>
-      <c r="D12" s="139">
+      <c r="D12" s="137">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="E12" s="103">
+      <c r="E12" s="101">
         <f>+D12/E8</f>
         <v>8.9453621346886919E-2</v>
       </c>
-      <c r="F12" s="102">
+      <c r="F12" s="100">
         <f>+A8*E12</f>
         <v>35828.311501905977</v>
       </c>
-      <c r="G12" s="102">
+      <c r="G12" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H12" s="101">
+      <c r="H12" s="99">
         <f t="shared" ref="H12:H20" si="2">SUM(F12:G12)</f>
         <v>45777.792891994919</v>
       </c>
-      <c r="K12" s="113">
+      <c r="K12" s="111">
         <v>89</v>
       </c>
-      <c r="L12" s="125">
+      <c r="L12" s="123">
         <v>400</v>
       </c>
-      <c r="M12" s="113">
+      <c r="M12" s="111">
         <v>253</v>
       </c>
-      <c r="N12" s="113" t="s">
-        <v>66</v>
-      </c>
-      <c r="O12" s="113">
+      <c r="N12" s="111" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="111">
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="140" t="s">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="139">
+      <c r="B13" s="137">
         <v>7564</v>
       </c>
-      <c r="C13" s="139">
+      <c r="C13" s="137">
         <f t="shared" si="1"/>
         <v>7767</v>
       </c>
-      <c r="D13" s="139">
+      <c r="D13" s="137">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="E13" s="103">
+      <c r="E13" s="101">
         <f>+D13/E8</f>
         <v>0.10317662007623889</v>
       </c>
-      <c r="F13" s="102">
+      <c r="F13" s="100">
         <f>+A8*E13</f>
         <v>41324.700198221093</v>
       </c>
-      <c r="G13" s="102">
+      <c r="G13" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H13" s="101">
+      <c r="H13" s="99">
         <f t="shared" si="2"/>
         <v>51274.181588310035</v>
       </c>
-      <c r="K13" s="113">
+      <c r="K13" s="111">
         <v>140</v>
       </c>
-      <c r="L13" s="141">
+      <c r="L13" s="139">
         <f>SUM(L8:L12)-0.45</f>
         <v>9960.1585524999991</v>
       </c>
-      <c r="M13" s="113">
+      <c r="M13" s="111">
         <f>SUM(M8:M12)</f>
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="140" t="s">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="139">
+      <c r="B14" s="137">
         <v>10119</v>
       </c>
-      <c r="C14" s="139">
+      <c r="C14" s="137">
         <f t="shared" si="1"/>
         <v>10334</v>
       </c>
-      <c r="D14" s="139">
+      <c r="D14" s="137">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
-      <c r="E14" s="103">
+      <c r="E14" s="101">
         <f>+D14/E8</f>
         <v>0.10927573062261753</v>
       </c>
-      <c r="F14" s="102">
+      <c r="F14" s="100">
         <f>+A8*E14</f>
         <v>43767.539618805589</v>
       </c>
-      <c r="G14" s="102">
+      <c r="G14" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H14" s="101">
+      <c r="H14" s="99">
         <f t="shared" si="2"/>
         <v>53717.021008894531</v>
       </c>
-      <c r="K14" s="113">
+      <c r="K14" s="111">
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="140" t="s">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="139">
+      <c r="B15" s="137">
         <v>8986</v>
       </c>
-      <c r="C15" s="139">
+      <c r="C15" s="137">
         <f t="shared" si="1"/>
         <v>9068</v>
       </c>
-      <c r="D15" s="139">
+      <c r="D15" s="137">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="E15" s="103">
+      <c r="E15" s="101">
         <f>+D15/E8</f>
         <v>4.1677255400254132E-2</v>
       </c>
-      <c r="F15" s="102">
+      <c r="F15" s="100">
         <f>+A8*E15</f>
         <v>16692.736040660737</v>
       </c>
-      <c r="G15" s="102">
+      <c r="G15" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H15" s="101">
+      <c r="H15" s="99">
         <f t="shared" si="2"/>
         <v>26642.217430749683</v>
       </c>
-      <c r="K15" s="113">
+      <c r="K15" s="111">
         <v>221</v>
       </c>
-      <c r="L15" s="113">
+      <c r="L15" s="111">
         <f>+L13+M13</f>
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="140" t="s">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="138" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="139">
+      <c r="B16" s="137">
         <v>7032</v>
       </c>
-      <c r="C16" s="139">
+      <c r="C16" s="137">
         <f t="shared" si="1"/>
         <v>7034</v>
       </c>
-      <c r="D16" s="139">
+      <c r="D16" s="137">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E16" s="103">
+      <c r="E16" s="101">
         <f>+D16/E8</f>
         <v>1.0165184243964421E-3</v>
       </c>
-      <c r="F16" s="102">
+      <c r="F16" s="100">
         <f>+A8*E16</f>
         <v>407.13990343074965</v>
       </c>
-      <c r="G16" s="102">
+      <c r="G16" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H16" s="101">
+      <c r="H16" s="99">
         <f t="shared" si="2"/>
         <v>10356.621293519693</v>
       </c>
-      <c r="K16" s="113">
+      <c r="K16" s="111">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="140" t="s">
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="139">
+      <c r="B17" s="137">
         <v>1623</v>
       </c>
-      <c r="C17" s="139">
+      <c r="C17" s="137">
         <f t="shared" si="1"/>
         <v>1668</v>
       </c>
-      <c r="D17" s="139">
+      <c r="D17" s="137">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="E17" s="103">
+      <c r="E17" s="101">
         <f>+D17/E8</f>
         <v>2.2871664548919948E-2</v>
       </c>
-      <c r="F17" s="102">
+      <c r="F17" s="100">
         <f>+A8*E17</f>
         <v>9160.6478271918677</v>
       </c>
-      <c r="G17" s="102">
+      <c r="G17" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H17" s="101">
+      <c r="H17" s="99">
         <f t="shared" si="2"/>
         <v>19110.12921728081</v>
       </c>
-      <c r="K17" s="113">
+      <c r="K17" s="111">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="140" t="s">
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="138" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="139">
+      <c r="B18" s="137">
         <v>3932</v>
       </c>
-      <c r="C18" s="139">
+      <c r="C18" s="137">
         <f t="shared" si="1"/>
         <v>4021</v>
       </c>
-      <c r="D18" s="139">
+      <c r="D18" s="137">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="E18" s="103">
+      <c r="E18" s="101">
         <f>+D18/E8</f>
         <v>4.5235069885641674E-2</v>
       </c>
-      <c r="F18" s="102">
+      <c r="F18" s="100">
         <f>+A8*E18</f>
         <v>18117.725702668358</v>
       </c>
-      <c r="G18" s="102">
+      <c r="G18" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H18" s="101">
+      <c r="H18" s="99">
         <f t="shared" si="2"/>
         <v>28067.2070927573</v>
       </c>
-      <c r="K18" s="113">
+      <c r="K18" s="111">
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="140" t="s">
+    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="138" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="139">
+      <c r="B19" s="137">
         <v>6887</v>
       </c>
-      <c r="C19" s="139">
+      <c r="C19" s="137">
         <f t="shared" si="1"/>
         <v>6994</v>
       </c>
-      <c r="D19" s="139">
+      <c r="D19" s="137">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="E19" s="103">
+      <c r="E19" s="101">
         <f>+D19/E8</f>
         <v>5.4383735705209657E-2</v>
       </c>
-      <c r="F19" s="102">
+      <c r="F19" s="100">
         <f>+A8*E19</f>
         <v>21781.98483354511</v>
       </c>
-      <c r="G19" s="102">
+      <c r="G19" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H19" s="101">
+      <c r="H19" s="99">
         <f t="shared" si="2"/>
         <v>31731.466223634052</v>
       </c>
-      <c r="K19" s="113">
+      <c r="K19" s="111">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="140" t="s">
+    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="139">
+      <c r="B20" s="137">
         <v>1884</v>
       </c>
-      <c r="C20" s="139">
+      <c r="C20" s="137">
         <f t="shared" si="1"/>
         <v>2020</v>
       </c>
-      <c r="D20" s="139">
+      <c r="D20" s="137">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="E20" s="103">
+      <c r="E20" s="101">
         <f>+D20/E8</f>
         <v>6.9123252858958067E-2</v>
       </c>
-      <c r="F20" s="102">
+      <c r="F20" s="100">
         <f>+A8*E20</f>
         <v>27685.513433290977</v>
       </c>
-      <c r="G20" s="102">
+      <c r="G20" s="100">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H20" s="101">
+      <c r="H20" s="99">
         <f t="shared" si="2"/>
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="138" t="s">
-        <v>139</v>
-      </c>
-      <c r="B21" s="137"/>
-      <c r="C21" s="137"/>
-      <c r="D21" s="136">
+    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="136" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="135"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="134">
         <f>SUM(D9:D20)</f>
         <v>1381</v>
       </c>
-      <c r="E21" s="135"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="100">
+      <c r="E21" s="133"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="98">
         <f>SUM(H9:H20)</f>
         <v>400523.88</v>
       </c>
-      <c r="J21" s="125">
+      <c r="J21" s="123">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="99">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="97">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
       </c>
-      <c r="B22" s="134" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" s="133"/>
-    </row>
-    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98">
+      <c r="B22" s="132" t="s">
+        <v>64</v>
+      </c>
+      <c r="L22" s="131"/>
+    </row>
+    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="96">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
       </c>
-      <c r="B23" s="132" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="131"/>
-      <c r="J25" s="113">
+      <c r="B23" s="130" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="129"/>
+      <c r="J25" s="111">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J26" s="113">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J26" s="111">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J27" s="113">
+    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="111">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="238" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="239"/>
-      <c r="D28" s="239"/>
-      <c r="E28" s="239"/>
-      <c r="F28" s="240"/>
-      <c r="J28" s="113">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B28" s="236" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="237"/>
+      <c r="D28" s="237"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="238"/>
+      <c r="J28" s="111">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="130" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="129" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B29" s="128" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="129" t="s">
+      <c r="C29" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="E29" s="129" t="s">
+      <c r="D29" s="127" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="128" t="s">
+      <c r="E29" s="127" t="s">
         <v>133</v>
       </c>
-      <c r="J29" s="113">
+      <c r="F29" s="126" t="s">
+        <v>132</v>
+      </c>
+      <c r="J29" s="111">
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B30" s="124" t="s">
-        <v>132</v>
-      </c>
-      <c r="C30" s="102">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B30" s="122" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="100">
         <v>4000</v>
       </c>
-      <c r="D30" s="102">
-        <v>0</v>
-      </c>
-      <c r="E30" s="122"/>
-      <c r="F30" s="101">
+      <c r="D30" s="100">
+        <v>0</v>
+      </c>
+      <c r="E30" s="120"/>
+      <c r="F30" s="99">
         <f>+C30</f>
         <v>4000</v>
       </c>
-      <c r="J30" s="127">
+      <c r="J30" s="125">
         <v>215</v>
       </c>
-      <c r="M30" s="113">
+      <c r="M30" s="111">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B31" s="124" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="102">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B31" s="122" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" s="100">
         <v>4000</v>
       </c>
-      <c r="D31" s="102">
-        <v>0</v>
-      </c>
-      <c r="E31" s="122"/>
-      <c r="F31" s="101">
+      <c r="D31" s="100">
+        <v>0</v>
+      </c>
+      <c r="E31" s="120"/>
+      <c r="F31" s="99">
         <f t="shared" ref="F31:F44" si="3">+F30+C31-D31</f>
         <v>8000</v>
       </c>
-      <c r="J31" s="113">
+      <c r="J31" s="111">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="124" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="102">
+    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B32" s="122" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="100">
         <v>4000</v>
       </c>
-      <c r="D32" s="102">
-        <v>0</v>
-      </c>
-      <c r="E32" s="122"/>
-      <c r="F32" s="101">
+      <c r="D32" s="100">
+        <v>0</v>
+      </c>
+      <c r="E32" s="120"/>
+      <c r="F32" s="99">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="J32" s="113">
+      <c r="J32" s="111">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B33" s="124" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="102">
+    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B33" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" s="100">
         <v>4000</v>
       </c>
-      <c r="D33" s="102">
-        <v>0</v>
-      </c>
-      <c r="E33" s="122"/>
-      <c r="F33" s="101">
+      <c r="D33" s="100">
+        <v>0</v>
+      </c>
+      <c r="E33" s="120"/>
+      <c r="F33" s="99">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="J33" s="113">
+      <c r="J33" s="111">
         <v>45</v>
       </c>
-      <c r="K33" s="126">
+      <c r="K33" s="124">
         <f>11934.02-11933.71</f>
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B34" s="124" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="102">
+    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B34" s="122" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="100">
         <v>4000</v>
       </c>
-      <c r="D34" s="102">
-        <v>0</v>
-      </c>
-      <c r="E34" s="122"/>
-      <c r="F34" s="101">
+      <c r="D34" s="100">
+        <v>0</v>
+      </c>
+      <c r="E34" s="120"/>
+      <c r="F34" s="99">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="J34" s="113">
+      <c r="J34" s="111">
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B35" s="124" t="s">
-        <v>127</v>
-      </c>
-      <c r="C35" s="102">
+    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B35" s="122" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" s="100">
         <v>4000</v>
       </c>
-      <c r="D35" s="102">
-        <v>0</v>
-      </c>
-      <c r="E35" s="122"/>
-      <c r="F35" s="101">
+      <c r="D35" s="100">
+        <v>0</v>
+      </c>
+      <c r="E35" s="120"/>
+      <c r="F35" s="99">
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="J35" s="113">
+      <c r="J35" s="111">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B36" s="124" t="s">
-        <v>126</v>
-      </c>
-      <c r="C36" s="102">
+    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B36" s="122" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="100">
         <v>4000</v>
       </c>
-      <c r="D36" s="102">
-        <v>0</v>
-      </c>
-      <c r="E36" s="122"/>
-      <c r="F36" s="101">
+      <c r="D36" s="100">
+        <v>0</v>
+      </c>
+      <c r="E36" s="120"/>
+      <c r="F36" s="99">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
-      <c r="J36" s="113">
+      <c r="J36" s="111">
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="124" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="123">
+    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B37" s="122" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="121">
         <v>4000</v>
       </c>
-      <c r="D37" s="102">
-        <v>0</v>
-      </c>
-      <c r="E37" s="122"/>
-      <c r="F37" s="101">
+      <c r="D37" s="100">
+        <v>0</v>
+      </c>
+      <c r="E37" s="120"/>
+      <c r="F37" s="99">
         <f t="shared" si="3"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="124" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="123">
+    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B38" s="122" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="121">
         <v>4000</v>
       </c>
-      <c r="D38" s="123">
+      <c r="D38" s="121">
         <v>3500</v>
       </c>
-      <c r="E38" s="122" t="s">
-        <v>123</v>
-      </c>
-      <c r="F38" s="101">
+      <c r="E38" s="120" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="99">
         <f t="shared" si="3"/>
         <v>32500</v>
       </c>
-      <c r="M38" s="125">
+      <c r="M38" s="123">
         <f>88.05-100</f>
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B39" s="124" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="123">
+    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B39" s="122" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="121">
         <v>4000</v>
       </c>
-      <c r="D39" s="122"/>
-      <c r="E39" s="122"/>
-      <c r="F39" s="101">
+      <c r="D39" s="120"/>
+      <c r="E39" s="120"/>
+      <c r="F39" s="99">
         <f t="shared" si="3"/>
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B40" s="124" t="s">
-        <v>121</v>
-      </c>
-      <c r="C40" s="123">
+    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B40" s="122" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="121">
         <v>4000</v>
       </c>
-      <c r="D40" s="122"/>
-      <c r="E40" s="122"/>
-      <c r="F40" s="101">
+      <c r="D40" s="120"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="99">
         <f t="shared" si="3"/>
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="124" t="s">
-        <v>120</v>
-      </c>
-      <c r="C41" s="123">
+    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B41" s="122" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="121">
         <v>4000</v>
       </c>
-      <c r="D41" s="122"/>
-      <c r="E41" s="122"/>
-      <c r="F41" s="101">
+      <c r="D41" s="120"/>
+      <c r="E41" s="120"/>
+      <c r="F41" s="99">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="124" t="s">
-        <v>119</v>
-      </c>
-      <c r="C42" s="123">
-        <v>0</v>
-      </c>
-      <c r="D42" s="122"/>
-      <c r="E42" s="122"/>
-      <c r="F42" s="101">
+    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B42" s="122" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="121">
+        <v>0</v>
+      </c>
+      <c r="D42" s="120"/>
+      <c r="E42" s="120"/>
+      <c r="F42" s="99">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="124" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" s="123">
-        <v>0</v>
-      </c>
-      <c r="D43" s="122"/>
-      <c r="E43" s="122"/>
-      <c r="F43" s="101">
+    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B43" s="122" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="121">
+        <v>0</v>
+      </c>
+      <c r="D43" s="120"/>
+      <c r="E43" s="120"/>
+      <c r="F43" s="99">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="121" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" s="120">
-        <v>0</v>
-      </c>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="118">
+    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B44" s="119" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" s="118">
+        <v>0</v>
+      </c>
+      <c r="D44" s="117"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="116">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B45" s="121" t="s">
-        <v>116</v>
-      </c>
-      <c r="C45" s="120">
-        <v>0</v>
-      </c>
-      <c r="D45" s="119"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="118">
+    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B45" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="118">
+        <v>0</v>
+      </c>
+      <c r="D45" s="117"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="116">
         <f>+F43+C45-D45</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B46" s="121" t="s">
-        <v>115</v>
-      </c>
-      <c r="C46" s="120">
-        <v>0</v>
-      </c>
-      <c r="D46" s="119"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="118">
+    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B46" s="119" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="118">
+        <v>0</v>
+      </c>
+      <c r="D46" s="117"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="116">
         <f>+F44+C46-D46</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="117" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47" s="116">
+    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="114">
         <f>-A47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="115"/>
-      <c r="E47" s="115"/>
-      <c r="F47" s="114">
+      <c r="D47" s="113"/>
+      <c r="E47" s="113"/>
+      <c r="F47" s="112">
         <f>+F45+C47-D47</f>
         <v>44500</v>
       </c>

--- a/TUCUMAN 1061/Octubre/tucuman Octubre.xlsx
+++ b/TUCUMAN 1061/Octubre/tucuman Octubre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816A58D0-C282-48E0-9D29-040335E83956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DDA536-A67F-442B-BF0C-B17FB27757C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$55</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$R$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$S$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
     <definedName name="PaseMateriales" localSheetId="2">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="175">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -584,6 +584,19 @@
   </si>
   <si>
     <t>Luz / Martin</t>
+  </si>
+  <si>
+    <t>IMPORTANTE
+⚠️ Al abonar, respetar los centavos que figuran en la columna “Total a pagar”.
+Respetar los centavos facilita la correcta identificación de los pagos y las unidades funcionales.
+Si poseen departamento y cochera, les pedimos —en la medida de lo posible— que realicen dos pagos separados, respetando los centavos correspondientes a cada uno.
+¡Muchas gracias por la colaboración! 🙌</t>
+  </si>
+  <si>
+    <t>1 er vto</t>
+  </si>
+  <si>
+    <t>VTO: 14/11</t>
   </si>
 </sst>
 </file>
@@ -910,7 +923,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1367,6 +1380,43 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1381,7 +1431,7 @@
     <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1394,7 +1444,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1495,7 +1544,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1651,7 +1699,6 @@
     </xf>
     <xf numFmtId="2" fontId="21" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="6" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1678,6 +1725,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="6" fontId="35" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1735,6 +1845,24 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1744,60 +1872,6 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="1" fontId="27" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1825,8 +1899,20 @@
     <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="6" fontId="35" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1856,16 +1942,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>62513</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>508283</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>156210</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>676215</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>611445</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>156210</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1894,8 +1980,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3558188" y="447675"/>
-          <a:ext cx="2804452" cy="1143000"/>
+          <a:off x="3156233" y="489585"/>
+          <a:ext cx="2779687" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2228,1574 +2314,1779 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="50" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="49" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" customWidth="1"/>
     <col min="4" max="4" width="22.140625" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="52" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="51" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="51" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="51" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" style="51" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="51" customWidth="1"/>
-    <col min="12" max="12" width="0.140625" style="51" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="51" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="50" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="50" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="50" customWidth="1"/>
+    <col min="10" max="10" width="0.140625" style="50" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="50" customWidth="1"/>
+    <col min="12" max="12" width="0.140625" style="50" customWidth="1"/>
     <col min="13" max="13" width="10.28515625" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" customWidth="1"/>
     <col min="15" max="15" width="12.140625" customWidth="1"/>
     <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="220" t="str">
+    <row r="1" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="191" t="str">
         <f>Gastos!E8</f>
         <v xml:space="preserve">PERIODO: OCTUBRE </v>
       </c>
-      <c r="B1" s="221"/>
-      <c r="C1" s="221"/>
-      <c r="D1" s="221"/>
-      <c r="E1" s="221"/>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="221"/>
-      <c r="M1" s="221"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="221"/>
-      <c r="P1" s="221"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="222"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="89"/>
-      <c r="C2" s="180">
+      <c r="B1" s="192"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
+      <c r="G1" s="192"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="192"/>
+      <c r="J1" s="192"/>
+      <c r="K1" s="192"/>
+      <c r="L1" s="192"/>
+      <c r="M1" s="192"/>
+      <c r="N1" s="192"/>
+      <c r="O1" s="192"/>
+      <c r="P1" s="192"/>
+      <c r="Q1" s="192"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="193"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="87"/>
+      <c r="C2" s="177">
         <v>1554753.9300000002</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="13"/>
-      <c r="R2" s="6"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="85"/>
-      <c r="D3" s="180">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="201" t="s">
+        <v>172</v>
+      </c>
+      <c r="N2" s="202"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="202"/>
+      <c r="Q2" s="202"/>
+      <c r="R2" s="202"/>
+      <c r="S2" s="203"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="83"/>
+      <c r="D3" s="177">
         <v>472904.04</v>
       </c>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="L3" s="87"/>
-      <c r="R3" s="6"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
-      <c r="C4" s="13" t="s">
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="204"/>
+      <c r="N3" s="205"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="205"/>
+      <c r="R3" s="205"/>
+      <c r="S3" s="206"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="83"/>
+      <c r="C4" s="252" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="190"/>
-      <c r="N4" s="190"/>
-      <c r="O4" s="190"/>
-      <c r="P4" s="190"/>
-      <c r="Q4" s="190"/>
-      <c r="R4" s="219"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="85"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="228">
+      <c r="D4" s="252"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="204"/>
+      <c r="N4" s="205"/>
+      <c r="O4" s="205"/>
+      <c r="P4" s="205"/>
+      <c r="Q4" s="205"/>
+      <c r="R4" s="205"/>
+      <c r="S4" s="206"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="83"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="199">
         <f>D3</f>
         <v>472904.04</v>
       </c>
-      <c r="D5" s="228"/>
-      <c r="E5" s="13"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="17"/>
-      <c r="R5" s="6"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="85"/>
-      <c r="C6" s="13" t="s">
+      <c r="D5" s="199"/>
+      <c r="E5" s="12"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="204"/>
+      <c r="N5" s="205"/>
+      <c r="O5" s="205"/>
+      <c r="P5" s="205"/>
+      <c r="Q5" s="205"/>
+      <c r="R5" s="205"/>
+      <c r="S5" s="206"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="83"/>
+      <c r="C6" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="R6" s="6"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="85"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="228">
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="204"/>
+      <c r="N6" s="205"/>
+      <c r="O6" s="205"/>
+      <c r="P6" s="205"/>
+      <c r="Q6" s="205"/>
+      <c r="R6" s="205"/>
+      <c r="S6" s="206"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="83"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="199">
         <f>C2-D3</f>
         <v>1081849.8900000001</v>
       </c>
-      <c r="D7" s="228"/>
-      <c r="E7" s="86"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="R7" s="6"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="85"/>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84" t="s">
+      <c r="D7" s="199"/>
+      <c r="E7" s="84"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="204"/>
+      <c r="N7" s="205"/>
+      <c r="O7" s="205"/>
+      <c r="P7" s="205"/>
+      <c r="Q7" s="205"/>
+      <c r="R7" s="205"/>
+      <c r="S7" s="206"/>
+    </row>
+    <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="83"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="R8" s="6"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="229">
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="204"/>
+      <c r="N8" s="205"/>
+      <c r="O8" s="205"/>
+      <c r="P8" s="205"/>
+      <c r="Q8" s="205"/>
+      <c r="R8" s="205"/>
+      <c r="S8" s="206"/>
+    </row>
+    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="81"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="200">
         <v>350000</v>
       </c>
-      <c r="D9" s="229"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="78"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="8"/>
-    </row>
-    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="77" t="s">
+      <c r="D9" s="200"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="249" t="str">
+        <f>Gastos!H8</f>
+        <v>VTO: 14/11</v>
+      </c>
+      <c r="H9" s="250"/>
+      <c r="I9" s="250"/>
+      <c r="J9" s="250"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="207"/>
+      <c r="N9" s="208"/>
+      <c r="O9" s="208"/>
+      <c r="P9" s="208"/>
+      <c r="Q9" s="208"/>
+      <c r="R9" s="208"/>
+      <c r="S9" s="209"/>
+    </row>
+    <row r="10" spans="1:22" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="75" t="s">
+      <c r="F10" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="74" t="s">
+      <c r="G10" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="74" t="s">
+      <c r="H10" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="74" t="s">
+      <c r="I10" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="74" t="s">
+      <c r="J10" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="74" t="s">
+      <c r="K10" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="74" t="s">
+      <c r="L10" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="73" t="s">
+      <c r="M10" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="N10" s="73" t="s">
+      <c r="N10" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="73" t="s">
+      <c r="O10" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="P10" s="73" t="s">
+      <c r="P10" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="73" t="s">
+      <c r="Q10" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="73" t="s">
+      <c r="R10" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="S10" s="72" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="171" t="s">
+    <row r="11" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="169" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="172"/>
-      <c r="C11" s="173" t="s">
+      <c r="B11" s="170"/>
+      <c r="C11" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="174" t="s">
+      <c r="D11" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="160"/>
-      <c r="F11" s="175">
+      <c r="E11" s="158"/>
+      <c r="F11" s="173">
         <v>7.9</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="63">
         <v>152965.07008999999</v>
       </c>
-      <c r="H11" s="64">
-        <v>0</v>
-      </c>
-      <c r="I11" s="64">
-        <f t="shared" ref="I11:I24" si="0">G11</f>
+      <c r="H11" s="63">
+        <v>0</v>
+      </c>
+      <c r="I11" s="63">
+        <f t="shared" ref="I11:I19" si="0">G11</f>
         <v>152965.07008999999</v>
       </c>
-      <c r="J11" s="64" t="e">
+      <c r="J11" s="63" t="e">
         <f>C8*F11/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="64">
+      <c r="K11" s="63">
         <f t="shared" ref="K11:K18" si="1">G11-H11-I11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="64"/>
-      <c r="M11" s="176">
+      <c r="L11" s="63"/>
+      <c r="M11" s="174">
         <f>(K11+L11)*3%</f>
         <v>0</v>
       </c>
-      <c r="N11" s="176">
+      <c r="N11" s="174">
         <f t="shared" ref="N11:N19" si="2">K11+M11+L11</f>
         <v>0</v>
       </c>
-      <c r="O11" s="64">
+      <c r="O11" s="63">
         <f>C$7*F11/100</f>
         <v>85466.141310000006</v>
       </c>
-      <c r="P11" s="64">
+      <c r="P11" s="63">
         <f>C$9*F11/100</f>
         <v>27650</v>
       </c>
-      <c r="Q11" s="64">
+      <c r="Q11" s="63">
         <f>C$5*F11/100</f>
         <v>37359.419160000005</v>
       </c>
-      <c r="R11" s="176">
-        <f t="shared" ref="R11:R29" si="3">O11+N11+P11+Q11</f>
-        <v>150475.56047000003</v>
-      </c>
-      <c r="U11" s="90" t="s">
+      <c r="R11" s="247">
+        <f>ROUND(O11+N11+P11+Q11,0) + T11</f>
+        <v>150476.01</v>
+      </c>
+      <c r="S11" s="189">
+        <f>ROUND(R11+R11*3%,0) + T11</f>
+        <v>154990.01</v>
+      </c>
+      <c r="T11" s="40">
+        <v>0.01</v>
+      </c>
+      <c r="V11" s="88" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="165" t="s">
+    <row r="12" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="163" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="158"/>
-      <c r="C12" s="166" t="s">
+      <c r="B12" s="156"/>
+      <c r="C12" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="167" t="s">
+      <c r="D12" s="165" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="168"/>
-      <c r="F12" s="169">
+      <c r="E12" s="166"/>
+      <c r="F12" s="167">
         <v>7.9</v>
       </c>
-      <c r="G12" s="156">
+      <c r="G12" s="154">
         <v>152965.07008999999</v>
       </c>
-      <c r="H12" s="156">
-        <v>0</v>
-      </c>
-      <c r="I12" s="64">
+      <c r="H12" s="154">
+        <v>0</v>
+      </c>
+      <c r="I12" s="63">
         <f t="shared" si="0"/>
         <v>152965.07008999999</v>
       </c>
-      <c r="J12" s="156" t="e">
+      <c r="J12" s="154" t="e">
         <f>C8*F12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K12" s="156">
+      <c r="K12" s="154">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L12" s="156"/>
-      <c r="M12" s="162">
-        <f t="shared" ref="M12:M29" si="4">(K12+L12)*3%</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="162">
+      <c r="L12" s="154"/>
+      <c r="M12" s="160">
+        <f t="shared" ref="M12:M29" si="3">(K12+L12)*3%</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="160">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O12" s="156">
-        <f t="shared" ref="O12:O29" si="5">C$7*F12/100</f>
+      <c r="O12" s="154">
+        <f t="shared" ref="O12:O29" si="4">C$7*F12/100</f>
         <v>85466.141310000006</v>
       </c>
-      <c r="P12" s="64">
-        <f t="shared" ref="P12:P29" si="6">C$9*F12/100</f>
+      <c r="P12" s="63">
+        <f t="shared" ref="P12:P29" si="5">C$9*F12/100</f>
         <v>27650</v>
       </c>
-      <c r="Q12" s="64">
-        <f t="shared" ref="Q12:Q22" si="7">C$5*F12/100</f>
+      <c r="Q12" s="63">
+        <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
         <v>37359.419160000005</v>
       </c>
-      <c r="R12" s="162">
-        <f t="shared" si="3"/>
-        <v>150475.56047000003</v>
-      </c>
-      <c r="U12" s="91" t="s">
+      <c r="R12" s="247">
+        <f t="shared" ref="R12:R29" si="7">ROUND(O12+N12+P12+Q12,0) + T12</f>
+        <v>150476.01999999999</v>
+      </c>
+      <c r="S12" s="189">
+        <f t="shared" ref="S12:S29" si="8">ROUND(R12+R12*3%,0) + T12</f>
+        <v>154990.01999999999</v>
+      </c>
+      <c r="T12" s="40">
+        <f t="shared" ref="T12:T29" si="9">T11+0.01</f>
+        <v>0.02</v>
+      </c>
+      <c r="V12" s="89" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="157" t="s">
+    <row r="13" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="155" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="158"/>
-      <c r="C13" s="92" t="s">
+      <c r="B13" s="156"/>
+      <c r="C13" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="159" t="s">
+      <c r="D13" s="157" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="160" t="s">
+      <c r="E13" s="158" t="s">
         <v>109</v>
       </c>
-      <c r="F13" s="161">
+      <c r="F13" s="159">
         <v>7.9</v>
       </c>
-      <c r="G13" s="64">
+      <c r="G13" s="63">
         <v>152965.07008999999</v>
       </c>
-      <c r="H13" s="156">
-        <v>0</v>
-      </c>
-      <c r="I13" s="64">
+      <c r="H13" s="154">
+        <v>0</v>
+      </c>
+      <c r="I13" s="63">
         <f t="shared" si="0"/>
         <v>152965.07008999999</v>
       </c>
-      <c r="J13" s="156" t="e">
+      <c r="J13" s="154" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="156">
+      <c r="K13" s="154">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L13" s="156"/>
-      <c r="M13" s="162">
+      <c r="L13" s="154"/>
+      <c r="M13" s="160">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="160">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="162">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="156">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P13" s="63">
         <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P13" s="64">
+        <v>27650</v>
+      </c>
+      <c r="Q13" s="63">
         <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q13" s="64">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R13" s="247">
         <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R13" s="162">
-        <f t="shared" si="3"/>
-        <v>150475.56047000003</v>
-      </c>
-      <c r="U13" s="91" t="s">
+        <v>150476.03</v>
+      </c>
+      <c r="S13" s="189">
+        <f t="shared" si="8"/>
+        <v>154990.03</v>
+      </c>
+      <c r="T13" s="40">
+        <f t="shared" si="9"/>
+        <v>0.03</v>
+      </c>
+      <c r="V13" s="89" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="107" t="s">
+    <row r="14" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="91" t="s">
+      <c r="B14" s="71"/>
+      <c r="C14" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="153" t="s">
+      <c r="D14" s="151" t="s">
         <v>102</v>
       </c>
-      <c r="E14" s="110"/>
-      <c r="F14" s="93">
+      <c r="E14" s="108"/>
+      <c r="F14" s="91">
         <v>7.9</v>
       </c>
-      <c r="G14" s="155">
+      <c r="G14" s="153">
         <v>152965.07008999999</v>
       </c>
-      <c r="H14" s="71"/>
-      <c r="I14" s="64">
+      <c r="H14" s="70"/>
+      <c r="I14" s="63">
         <f t="shared" si="0"/>
         <v>152965.07008999999</v>
       </c>
-      <c r="J14" s="62" t="e">
+      <c r="J14" s="61" t="e">
         <f>C8*F14/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K14" s="62">
+      <c r="K14" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L14" s="63"/>
-      <c r="M14" s="61">
+      <c r="L14" s="62"/>
+      <c r="M14" s="60">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="60">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="61">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="62">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P14" s="63">
         <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P14" s="64">
+        <v>27650</v>
+      </c>
+      <c r="Q14" s="63">
         <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q14" s="64">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R14" s="247">
         <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R14" s="61">
-        <f t="shared" si="3"/>
-        <v>150475.56047000003</v>
-      </c>
-      <c r="U14" s="91" t="s">
+        <v>150476.04</v>
+      </c>
+      <c r="S14" s="189">
+        <f t="shared" si="8"/>
+        <v>154990.04</v>
+      </c>
+      <c r="T14" s="40">
+        <f t="shared" si="9"/>
+        <v>0.04</v>
+      </c>
+      <c r="V14" s="89" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="107" t="s">
+    <row r="15" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="91" t="s">
+      <c r="B15" s="67"/>
+      <c r="C15" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="108" t="s">
+      <c r="D15" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="110"/>
-      <c r="F15" s="93">
+      <c r="E15" s="108"/>
+      <c r="F15" s="91">
         <v>7.9</v>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="68">
         <v>152965.07008999999</v>
       </c>
-      <c r="H15" s="71">
-        <v>0</v>
-      </c>
-      <c r="I15" s="64">
+      <c r="H15" s="70">
+        <v>0</v>
+      </c>
+      <c r="I15" s="63">
         <f>163345-I27</f>
         <v>152964.73843</v>
       </c>
-      <c r="J15" s="62" t="e">
+      <c r="J15" s="61" t="e">
         <f>C8*F15/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K15" s="62">
+      <c r="K15" s="61">
         <f t="shared" si="1"/>
         <v>0.33165999999619089</v>
       </c>
-      <c r="L15" s="62"/>
-      <c r="M15" s="61">
-        <f t="shared" si="4"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="60">
+        <f t="shared" si="3"/>
         <v>9.9497999998857268E-3</v>
       </c>
-      <c r="N15" s="61">
+      <c r="N15" s="60">
         <f t="shared" si="2"/>
         <v>0.3416097999960766</v>
       </c>
-      <c r="O15" s="62">
+      <c r="O15" s="61">
+        <f t="shared" si="4"/>
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P15" s="63">
         <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P15" s="64">
+        <v>27650</v>
+      </c>
+      <c r="Q15" s="63">
         <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q15" s="64">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R15" s="247">
         <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R15" s="61">
-        <f t="shared" si="3"/>
-        <v>150475.90207980003</v>
-      </c>
-      <c r="U15" s="91" t="s">
+        <v>150476.04999999999</v>
+      </c>
+      <c r="S15" s="189">
+        <f t="shared" si="8"/>
+        <v>154990.04999999999</v>
+      </c>
+      <c r="T15" s="40">
+        <f t="shared" si="9"/>
+        <v>0.05</v>
+      </c>
+      <c r="V15" s="89" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="157" t="s">
+    <row r="16" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="155" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="158"/>
-      <c r="C16" s="92" t="s">
+      <c r="B16" s="156"/>
+      <c r="C16" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="159" t="s">
+      <c r="D16" s="157" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="160" t="s">
+      <c r="E16" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="F16" s="161">
+      <c r="F16" s="159">
         <v>7.9</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="63">
         <v>152965.07008999999</v>
       </c>
-      <c r="H16" s="156">
-        <v>0</v>
-      </c>
-      <c r="I16" s="64">
+      <c r="H16" s="154">
+        <v>0</v>
+      </c>
+      <c r="I16" s="63">
         <f>163345-I28</f>
         <v>152964.73843</v>
       </c>
-      <c r="J16" s="156" t="e">
+      <c r="J16" s="154" t="e">
         <f>C8*F16/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="156">
+      <c r="K16" s="154">
         <f t="shared" si="1"/>
         <v>0.33165999999619089</v>
       </c>
-      <c r="L16" s="156"/>
-      <c r="M16" s="162">
-        <f t="shared" si="4"/>
+      <c r="L16" s="154"/>
+      <c r="M16" s="160">
+        <f t="shared" si="3"/>
         <v>9.9497999998857268E-3</v>
       </c>
-      <c r="N16" s="162">
+      <c r="N16" s="160">
         <f t="shared" si="2"/>
         <v>0.3416097999960766</v>
       </c>
-      <c r="O16" s="156">
+      <c r="O16" s="154">
+        <f t="shared" si="4"/>
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P16" s="63">
         <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P16" s="64">
+        <v>27650</v>
+      </c>
+      <c r="Q16" s="63">
         <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q16" s="64">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R16" s="247">
         <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R16" s="162">
-        <f t="shared" si="3"/>
-        <v>150475.90207980003</v>
-      </c>
-      <c r="U16" s="91" t="s">
+        <v>150476.06</v>
+      </c>
+      <c r="S16" s="189">
+        <f t="shared" si="8"/>
+        <v>154990.06</v>
+      </c>
+      <c r="T16" s="40">
+        <f t="shared" si="9"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="V16" s="89" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="107" t="s">
+    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="91" t="s">
+      <c r="B17" s="67"/>
+      <c r="C17" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="108" t="s">
+      <c r="D17" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="E17" s="110" t="s">
+      <c r="E17" s="108" t="s">
         <v>145</v>
       </c>
-      <c r="F17" s="93">
+      <c r="F17" s="91">
         <v>7.9</v>
       </c>
-      <c r="G17" s="69">
+      <c r="G17" s="68">
         <v>152965.07008999999</v>
       </c>
-      <c r="H17" s="62">
-        <v>0</v>
-      </c>
-      <c r="I17" s="64">
+      <c r="H17" s="61">
+        <v>0</v>
+      </c>
+      <c r="I17" s="63">
         <f>152965-I23</f>
         <v>142584.73843</v>
       </c>
-      <c r="J17" s="62" t="e">
+      <c r="J17" s="61" t="e">
         <f>C8*F17/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="62">
+      <c r="K17" s="61">
         <f t="shared" si="1"/>
         <v>10380.331659999996</v>
       </c>
-      <c r="L17" s="62"/>
-      <c r="M17" s="61">
-        <f t="shared" si="4"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="60">
+        <f t="shared" si="3"/>
         <v>311.40994979999988</v>
       </c>
-      <c r="N17" s="61">
+      <c r="N17" s="60">
         <f t="shared" si="2"/>
         <v>10691.741609799996</v>
       </c>
-      <c r="O17" s="62">
+      <c r="O17" s="61">
+        <f t="shared" si="4"/>
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P17" s="63">
         <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P17" s="64">
+        <v>27650</v>
+      </c>
+      <c r="Q17" s="63">
         <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q17" s="64">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R17" s="247">
         <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R17" s="61">
-        <f t="shared" si="3"/>
-        <v>161167.30207979999</v>
-      </c>
-      <c r="U17" s="91" t="s">
+        <v>161167.07</v>
+      </c>
+      <c r="S17" s="189">
+        <f t="shared" si="8"/>
+        <v>166002.07</v>
+      </c>
+      <c r="T17" s="40">
+        <f t="shared" si="9"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="V17" s="89" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="157" t="s">
+    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="155" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="158"/>
-      <c r="C18" s="92" t="s">
+      <c r="B18" s="156"/>
+      <c r="C18" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="159" t="s">
+      <c r="D18" s="157" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="160" t="s">
+      <c r="E18" s="158" t="s">
         <v>146</v>
       </c>
-      <c r="F18" s="161">
+      <c r="F18" s="159">
         <v>7.9</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="63">
         <v>152965.07008999999</v>
       </c>
-      <c r="H18" s="156">
-        <v>0</v>
-      </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="156" t="e">
+      <c r="H18" s="154">
+        <v>0</v>
+      </c>
+      <c r="I18" s="63"/>
+      <c r="J18" s="154" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="156">
+      <c r="K18" s="154">
         <f t="shared" si="1"/>
         <v>152965.07008999999</v>
       </c>
-      <c r="L18" s="156"/>
-      <c r="M18" s="162">
-        <f t="shared" si="4"/>
+      <c r="L18" s="154"/>
+      <c r="M18" s="160">
+        <f t="shared" si="3"/>
         <v>4588.9521027000001</v>
       </c>
-      <c r="N18" s="162">
+      <c r="N18" s="160">
         <f t="shared" si="2"/>
         <v>157554.02219269998</v>
       </c>
-      <c r="O18" s="156">
+      <c r="O18" s="154">
+        <f t="shared" si="4"/>
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P18" s="63">
         <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P18" s="64">
+        <v>27650</v>
+      </c>
+      <c r="Q18" s="63">
         <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q18" s="64">
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R18" s="247">
         <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R18" s="162">
-        <f t="shared" si="3"/>
-        <v>308029.58266269998</v>
-      </c>
-      <c r="U18" s="91" t="s">
+        <v>308030.08000000002</v>
+      </c>
+      <c r="S18" s="189">
+        <f t="shared" si="8"/>
+        <v>317271.08</v>
+      </c>
+      <c r="T18" s="40">
+        <f t="shared" si="9"/>
+        <v>0.08</v>
+      </c>
+      <c r="V18" s="89" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="157" t="s">
+    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="155" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="158"/>
-      <c r="C19" s="92" t="s">
+      <c r="B19" s="156"/>
+      <c r="C19" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="159" t="s">
+      <c r="D19" s="157" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="160"/>
-      <c r="F19" s="161">
+      <c r="E19" s="158"/>
+      <c r="F19" s="159">
         <v>7.9</v>
       </c>
-      <c r="G19" s="64">
+      <c r="G19" s="63">
         <v>152965.07008999999</v>
       </c>
-      <c r="H19" s="156">
-        <v>0</v>
-      </c>
-      <c r="I19" s="64">
+      <c r="H19" s="154">
+        <v>0</v>
+      </c>
+      <c r="I19" s="63">
         <f t="shared" si="0"/>
         <v>152965.07008999999</v>
       </c>
-      <c r="J19" s="156" t="e">
+      <c r="J19" s="154" t="e">
         <f>C8*F19/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="156">
-        <f t="shared" ref="K19:K29" si="8">G19-H19-I19</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="156">
+      <c r="K19" s="154">
+        <f t="shared" ref="K19:K29" si="10">G19-H19-I19</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="154">
         <f>G19-I19</f>
         <v>0</v>
       </c>
-      <c r="M19" s="162">
+      <c r="M19" s="160">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="160">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="154">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="162">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="156">
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P19" s="63">
         <f t="shared" si="5"/>
+        <v>27650</v>
+      </c>
+      <c r="Q19" s="63">
+        <f t="shared" si="6"/>
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R19" s="247">
+        <f t="shared" si="7"/>
+        <v>150476.09</v>
+      </c>
+      <c r="S19" s="189">
+        <f t="shared" si="8"/>
+        <v>154990.09</v>
+      </c>
+      <c r="T19" s="40">
+        <f t="shared" si="9"/>
+        <v>0.09</v>
+      </c>
+      <c r="V19" s="89" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="105" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="67"/>
+      <c r="C20" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="106" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="108"/>
+      <c r="F20" s="91">
+        <v>7.9</v>
+      </c>
+      <c r="G20" s="68">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="H20" s="61"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61">
+        <f t="shared" si="10"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="L20" s="61"/>
+      <c r="M20" s="60">
+        <f t="shared" si="3"/>
+        <v>4588.9521027000001</v>
+      </c>
+      <c r="N20" s="60">
+        <f t="shared" ref="N20:N29" si="11">K20+M20+L20</f>
+        <v>157554.02219269998</v>
+      </c>
+      <c r="O20" s="61">
+        <f t="shared" si="4"/>
         <v>85466.141310000006</v>
       </c>
-      <c r="P19" s="64">
+      <c r="P20" s="63">
+        <f t="shared" si="5"/>
+        <v>27650</v>
+      </c>
+      <c r="Q20" s="63">
         <f t="shared" si="6"/>
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R20" s="247">
+        <f t="shared" si="7"/>
+        <v>308030.09999999998</v>
+      </c>
+      <c r="S20" s="189">
+        <f t="shared" si="8"/>
+        <v>317271.09999999998</v>
+      </c>
+      <c r="T20" s="40">
+        <f t="shared" si="9"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="V20" s="89" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="155" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="156"/>
+      <c r="C21" s="90" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="157" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="158" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="159">
+        <v>7.9</v>
+      </c>
+      <c r="G21" s="63">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="H21" s="154"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="154"/>
+      <c r="K21" s="154">
+        <f t="shared" si="10"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="L21" s="154"/>
+      <c r="M21" s="160">
+        <f t="shared" si="3"/>
+        <v>4588.9521027000001</v>
+      </c>
+      <c r="N21" s="160">
+        <f t="shared" si="11"/>
+        <v>157554.02219269998</v>
+      </c>
+      <c r="O21" s="154">
+        <f t="shared" si="4"/>
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P21" s="63">
+        <f t="shared" si="5"/>
         <v>27650</v>
       </c>
-      <c r="Q19" s="64">
+      <c r="Q21" s="63">
+        <f t="shared" si="6"/>
+        <v>37359.419160000005</v>
+      </c>
+      <c r="R21" s="247">
         <f t="shared" si="7"/>
+        <v>308030.11</v>
+      </c>
+      <c r="S21" s="189">
+        <f t="shared" si="8"/>
+        <v>317271.11</v>
+      </c>
+      <c r="T21" s="40">
+        <f t="shared" si="9"/>
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="V21" s="89" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="155" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="156"/>
+      <c r="C22" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="157" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="158" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22" s="159">
+        <v>7.9</v>
+      </c>
+      <c r="G22" s="63">
+        <v>152965.07008999999</v>
+      </c>
+      <c r="H22" s="154"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="154"/>
+      <c r="K22" s="154">
+        <f t="shared" si="10"/>
+        <v>152965.07008999999</v>
+      </c>
+      <c r="L22" s="154"/>
+      <c r="M22" s="160">
+        <f t="shared" si="3"/>
+        <v>4588.9521027000001</v>
+      </c>
+      <c r="N22" s="160">
+        <f t="shared" si="11"/>
+        <v>157554.02219269998</v>
+      </c>
+      <c r="O22" s="154">
+        <f t="shared" si="4"/>
+        <v>85466.141310000006</v>
+      </c>
+      <c r="P22" s="63">
+        <f t="shared" si="5"/>
+        <v>27650</v>
+      </c>
+      <c r="Q22" s="63">
+        <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R19" s="162">
-        <f t="shared" si="3"/>
-        <v>150475.56047000003</v>
-      </c>
-      <c r="U19" s="91" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="107" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="108" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" s="110"/>
-      <c r="F20" s="93">
-        <v>7.9</v>
-      </c>
-      <c r="G20" s="69">
-        <v>152965.07008999999</v>
-      </c>
-      <c r="H20" s="62"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62">
+      <c r="R22" s="247">
+        <f t="shared" si="7"/>
+        <v>308030.12</v>
+      </c>
+      <c r="S22" s="189">
         <f t="shared" si="8"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="L20" s="62"/>
-      <c r="M20" s="61">
-        <f t="shared" si="4"/>
-        <v>4588.9521027000001</v>
-      </c>
-      <c r="N20" s="61">
-        <f t="shared" ref="N20:N29" si="9">K20+M20+L20</f>
-        <v>157554.02219269998</v>
-      </c>
-      <c r="O20" s="62">
-        <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P20" s="64">
-        <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q20" s="64">
-        <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R20" s="61">
-        <f t="shared" si="3"/>
-        <v>308029.58266269998</v>
-      </c>
-      <c r="U20" s="91" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="157" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="158"/>
-      <c r="C21" s="92" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="159" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" s="160" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="161">
-        <v>7.9</v>
-      </c>
-      <c r="G21" s="64">
-        <v>152965.07008999999</v>
-      </c>
-      <c r="H21" s="156"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="156"/>
-      <c r="K21" s="156">
-        <f t="shared" si="8"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="L21" s="156"/>
-      <c r="M21" s="162">
-        <f t="shared" si="4"/>
-        <v>4588.9521027000001</v>
-      </c>
-      <c r="N21" s="162">
+        <v>317271.12</v>
+      </c>
+      <c r="T22" s="40">
         <f t="shared" si="9"/>
-        <v>157554.02219269998</v>
-      </c>
-      <c r="O21" s="156">
-        <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P21" s="64">
-        <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q21" s="64">
-        <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R21" s="162">
-        <f t="shared" si="3"/>
-        <v>308029.58266269998</v>
-      </c>
-      <c r="U21" s="91" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="157" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="158"/>
-      <c r="C22" s="92" t="s">
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="V22" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="159" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" s="160" t="s">
-        <v>152</v>
-      </c>
-      <c r="F22" s="161">
-        <v>7.9</v>
-      </c>
-      <c r="G22" s="64">
-        <v>152965.07008999999</v>
-      </c>
-      <c r="H22" s="156"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="156"/>
-      <c r="K22" s="156">
-        <f t="shared" si="8"/>
-        <v>152965.07008999999</v>
-      </c>
-      <c r="L22" s="156"/>
-      <c r="M22" s="162">
-        <f t="shared" si="4"/>
-        <v>4588.9521027000001</v>
-      </c>
-      <c r="N22" s="162">
-        <f t="shared" si="9"/>
-        <v>157554.02219269998</v>
-      </c>
-      <c r="O22" s="156">
-        <f t="shared" si="5"/>
-        <v>85466.141310000006</v>
-      </c>
-      <c r="P22" s="64">
-        <f t="shared" si="6"/>
-        <v>27650</v>
-      </c>
-      <c r="Q22" s="64">
-        <f t="shared" si="7"/>
-        <v>37359.419160000005</v>
-      </c>
-      <c r="R22" s="162">
-        <f t="shared" si="3"/>
-        <v>308029.58266269998</v>
-      </c>
-      <c r="S22" s="177"/>
-      <c r="U22" s="91" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="107"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="91" t="s">
+    </row>
+    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="105"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="109" t="str">
+      <c r="D23" s="107" t="str">
         <f>D17</f>
         <v>Estevez Norberto Omar</v>
       </c>
-      <c r="E23" s="110" t="s">
+      <c r="E23" s="108" t="s">
         <v>145</v>
       </c>
-      <c r="F23" s="93">
+      <c r="F23" s="91">
         <v>0.74</v>
       </c>
-      <c r="G23" s="69">
+      <c r="G23" s="68">
         <v>10380.261569999999</v>
       </c>
-      <c r="H23" s="62"/>
-      <c r="I23" s="64">
+      <c r="H23" s="61"/>
+      <c r="I23" s="63">
         <f>G23</f>
         <v>10380.261569999999</v>
       </c>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62">
+      <c r="J23" s="61"/>
+      <c r="K23" s="61">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="61"/>
+      <c r="M23" s="60">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="60">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="61">
+        <f t="shared" si="4"/>
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P23" s="63">
+        <f t="shared" si="5"/>
+        <v>2590</v>
+      </c>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="247">
+        <f t="shared" si="7"/>
+        <v>10596.13</v>
+      </c>
+      <c r="S23" s="189">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="62"/>
-      <c r="M23" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="61">
+        <v>10914.13</v>
+      </c>
+      <c r="T23" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="62">
-        <f t="shared" si="5"/>
-        <v>8005.6891860000005</v>
-      </c>
-      <c r="P23" s="64">
-        <f t="shared" si="6"/>
-        <v>2590</v>
-      </c>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="61">
-        <f t="shared" si="3"/>
-        <v>10595.689186</v>
-      </c>
-      <c r="U23" s="91" t="s">
+        <v>0.12999999999999998</v>
+      </c>
+      <c r="V23" s="89" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="157"/>
-      <c r="B24" s="158"/>
-      <c r="C24" s="92" t="s">
+    <row r="24" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="155"/>
+      <c r="B24" s="156"/>
+      <c r="C24" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="163" t="str">
+      <c r="D24" s="161" t="str">
         <f>D21</f>
         <v>Moro Vanesa Yania / Juan Carlos Moro</v>
       </c>
-      <c r="E24" s="160" t="s">
+      <c r="E24" s="158" t="s">
         <v>110</v>
       </c>
-      <c r="F24" s="161">
+      <c r="F24" s="159">
         <v>0.74</v>
       </c>
-      <c r="G24" s="64">
+      <c r="G24" s="63">
         <v>10380.261569999999</v>
       </c>
-      <c r="H24" s="156"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="156"/>
-      <c r="K24" s="156">
+      <c r="H24" s="154"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="154">
+        <f t="shared" si="10"/>
+        <v>10380.261569999999</v>
+      </c>
+      <c r="L24" s="154"/>
+      <c r="M24" s="160">
+        <f t="shared" si="3"/>
+        <v>311.40784709999997</v>
+      </c>
+      <c r="N24" s="160">
+        <f t="shared" si="11"/>
+        <v>10691.669417099998</v>
+      </c>
+      <c r="O24" s="154">
+        <f t="shared" si="4"/>
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P24" s="63">
+        <f t="shared" si="5"/>
+        <v>2590</v>
+      </c>
+      <c r="Q24" s="154">
+        <f>'Calculo Servicios  (2)'!H22</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="247">
+        <f t="shared" si="7"/>
+        <v>21287.14</v>
+      </c>
+      <c r="S24" s="189">
         <f t="shared" si="8"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="L24" s="156"/>
-      <c r="M24" s="162">
-        <f t="shared" si="4"/>
-        <v>311.40784709999997</v>
-      </c>
-      <c r="N24" s="162">
+        <v>21926.14</v>
+      </c>
+      <c r="T24" s="40">
         <f t="shared" si="9"/>
-        <v>10691.669417099998</v>
-      </c>
-      <c r="O24" s="156">
-        <f t="shared" si="5"/>
-        <v>8005.6891860000005</v>
-      </c>
-      <c r="P24" s="64">
-        <f t="shared" si="6"/>
-        <v>2590</v>
-      </c>
-      <c r="Q24" s="156">
-        <f>'Calculo Servicios  (2)'!H22</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="162">
-        <f t="shared" si="3"/>
-        <v>21287.358603099998</v>
-      </c>
-      <c r="U24" s="91" t="s">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="V24" s="89" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="107"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="91" t="s">
+    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="105"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="109" t="str">
+      <c r="D25" s="107" t="str">
         <f>D20</f>
         <v>Scarlercio Jorge Omar</v>
       </c>
-      <c r="E25" s="109"/>
-      <c r="F25" s="93">
+      <c r="E25" s="107"/>
+      <c r="F25" s="91">
         <v>0.74</v>
       </c>
-      <c r="G25" s="69">
+      <c r="G25" s="68">
         <v>10380.261569999999</v>
       </c>
-      <c r="H25" s="62"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62">
+      <c r="H25" s="61"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61">
+        <f t="shared" si="10"/>
+        <v>10380.261569999999</v>
+      </c>
+      <c r="L25" s="61"/>
+      <c r="M25" s="60">
+        <f t="shared" si="3"/>
+        <v>311.40784709999997</v>
+      </c>
+      <c r="N25" s="60">
+        <f t="shared" si="11"/>
+        <v>10691.669417099998</v>
+      </c>
+      <c r="O25" s="61">
+        <f t="shared" si="4"/>
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P25" s="63">
+        <f t="shared" si="5"/>
+        <v>2590</v>
+      </c>
+      <c r="Q25" s="61">
+        <f>'Calculo Servicios  (2)'!H23</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="247">
+        <f t="shared" si="7"/>
+        <v>21287.15</v>
+      </c>
+      <c r="S25" s="189">
         <f t="shared" si="8"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="L25" s="62"/>
-      <c r="M25" s="61">
-        <f t="shared" si="4"/>
-        <v>311.40784709999997</v>
-      </c>
-      <c r="N25" s="61">
+        <v>21926.15</v>
+      </c>
+      <c r="T25" s="40">
         <f t="shared" si="9"/>
-        <v>10691.669417099998</v>
-      </c>
-      <c r="O25" s="62">
-        <f t="shared" si="5"/>
-        <v>8005.6891860000005</v>
-      </c>
-      <c r="P25" s="64">
-        <f t="shared" si="6"/>
-        <v>2590</v>
-      </c>
-      <c r="Q25" s="62">
-        <f>'Calculo Servicios  (2)'!H23</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="61">
-        <f t="shared" si="3"/>
-        <v>21287.358603099998</v>
-      </c>
-      <c r="U25" s="91" t="s">
+        <v>0.15</v>
+      </c>
+      <c r="V25" s="89" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="157"/>
-      <c r="B26" s="154"/>
-      <c r="C26" s="92" t="s">
+    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="155"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="D26" s="163" t="str">
+      <c r="D26" s="161" t="str">
         <f>D18</f>
         <v>Lopez Gabriela</v>
       </c>
-      <c r="E26" s="160" t="s">
+      <c r="E26" s="158" t="s">
         <v>146</v>
       </c>
-      <c r="F26" s="161">
+      <c r="F26" s="159">
         <v>0.74</v>
       </c>
-      <c r="G26" s="64">
+      <c r="G26" s="63">
         <v>10380.261569999999</v>
       </c>
-      <c r="H26" s="156">
-        <v>0</v>
-      </c>
-      <c r="I26" s="64"/>
-      <c r="J26" s="156" t="e">
+      <c r="H26" s="154">
+        <v>0</v>
+      </c>
+      <c r="I26" s="63"/>
+      <c r="J26" s="154" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="156">
+      <c r="K26" s="154">
+        <f t="shared" si="10"/>
+        <v>10380.261569999999</v>
+      </c>
+      <c r="L26" s="154"/>
+      <c r="M26" s="160">
+        <f t="shared" si="3"/>
+        <v>311.40784709999997</v>
+      </c>
+      <c r="N26" s="160">
+        <f t="shared" si="11"/>
+        <v>10691.669417099998</v>
+      </c>
+      <c r="O26" s="154">
+        <f t="shared" si="4"/>
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P26" s="63">
+        <f t="shared" si="5"/>
+        <v>2590</v>
+      </c>
+      <c r="Q26" s="154">
+        <f>'Calculo Servicios  (2)'!H24</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="247">
+        <f t="shared" si="7"/>
+        <v>21287.16</v>
+      </c>
+      <c r="S26" s="189">
         <f t="shared" si="8"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="L26" s="156"/>
-      <c r="M26" s="162">
-        <f t="shared" si="4"/>
-        <v>311.40784709999997</v>
-      </c>
-      <c r="N26" s="162">
+        <v>21926.16</v>
+      </c>
+      <c r="T26" s="40">
         <f t="shared" si="9"/>
-        <v>10691.669417099998</v>
-      </c>
-      <c r="O26" s="156">
-        <f t="shared" si="5"/>
-        <v>8005.6891860000005</v>
-      </c>
-      <c r="P26" s="64">
-        <f t="shared" si="6"/>
-        <v>2590</v>
-      </c>
-      <c r="Q26" s="156">
-        <f>'Calculo Servicios  (2)'!H24</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="162">
-        <f t="shared" si="3"/>
-        <v>21287.358603099998</v>
-      </c>
-      <c r="U26" s="91" t="s">
+        <v>0.16</v>
+      </c>
+      <c r="V26" s="89" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="107"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="91" t="s">
+    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="105"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="109" t="str">
+      <c r="D27" s="107" t="str">
         <f>D15</f>
         <v>Cecilia Mariel Cassettari</v>
       </c>
-      <c r="E27" s="109"/>
-      <c r="F27" s="93">
+      <c r="E27" s="107"/>
+      <c r="F27" s="91">
         <v>0.74</v>
       </c>
-      <c r="G27" s="69">
+      <c r="G27" s="68">
         <v>10380.261569999999</v>
       </c>
-      <c r="H27" s="62">
-        <v>0</v>
-      </c>
-      <c r="I27" s="64">
+      <c r="H27" s="61">
+        <v>0</v>
+      </c>
+      <c r="I27" s="63">
         <f>G27</f>
         <v>10380.261569999999</v>
       </c>
-      <c r="J27" s="62" t="e">
+      <c r="J27" s="61" t="e">
         <f>C8*F27/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K27" s="62">
+      <c r="K27" s="61">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="61"/>
+      <c r="M27" s="60">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="60">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="61">
+        <f t="shared" si="4"/>
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P27" s="63">
+        <f t="shared" si="5"/>
+        <v>2590</v>
+      </c>
+      <c r="Q27" s="61">
+        <f>'Calculo Servicios  (2)'!H25</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="247">
+        <f t="shared" si="7"/>
+        <v>10596.17</v>
+      </c>
+      <c r="S27" s="189">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="62"/>
-      <c r="M27" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N27" s="61">
+        <v>10914.17</v>
+      </c>
+      <c r="T27" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="62">
-        <f t="shared" si="5"/>
-        <v>8005.6891860000005</v>
-      </c>
-      <c r="P27" s="64">
-        <f t="shared" si="6"/>
-        <v>2590</v>
-      </c>
-      <c r="Q27" s="62">
-        <f>'Calculo Servicios  (2)'!H25</f>
-        <v>0</v>
-      </c>
-      <c r="R27" s="61">
-        <f t="shared" si="3"/>
-        <v>10595.689186</v>
-      </c>
-      <c r="U27" s="91" t="s">
+        <v>0.17</v>
+      </c>
+      <c r="V27" s="89" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="181"/>
-      <c r="B28" s="182"/>
-      <c r="C28" s="92" t="s">
+    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="178"/>
+      <c r="B28" s="179"/>
+      <c r="C28" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="163" t="str">
+      <c r="D28" s="161" t="str">
         <f>D16</f>
         <v>Perez Sebastian</v>
       </c>
-      <c r="E28" s="160" t="s">
+      <c r="E28" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="F28" s="183">
+      <c r="F28" s="180">
         <v>0.74</v>
       </c>
-      <c r="G28" s="64">
+      <c r="G28" s="63">
         <v>10380.261569999999</v>
       </c>
-      <c r="H28" s="64">
-        <v>0</v>
-      </c>
-      <c r="I28" s="64">
+      <c r="H28" s="63">
+        <v>0</v>
+      </c>
+      <c r="I28" s="63">
         <f>G28</f>
         <v>10380.261569999999</v>
       </c>
-      <c r="J28" s="64">
-        <v>0</v>
-      </c>
-      <c r="K28" s="64">
+      <c r="J28" s="63">
+        <v>0</v>
+      </c>
+      <c r="K28" s="63">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="63"/>
+      <c r="M28" s="174">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="174">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="63">
+        <f t="shared" si="4"/>
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P28" s="63">
+        <f t="shared" si="5"/>
+        <v>2590</v>
+      </c>
+      <c r="Q28" s="63">
+        <f>'Calculo Servicios  (2)'!H26</f>
+        <v>0</v>
+      </c>
+      <c r="R28" s="247">
+        <f t="shared" si="7"/>
+        <v>10596.18</v>
+      </c>
+      <c r="S28" s="189">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="64"/>
-      <c r="M28" s="176">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="176">
+        <v>10914.18</v>
+      </c>
+      <c r="T28" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="64">
-        <f t="shared" si="5"/>
-        <v>8005.6891860000005</v>
-      </c>
-      <c r="P28" s="64">
-        <f t="shared" si="6"/>
-        <v>2590</v>
-      </c>
-      <c r="Q28" s="64">
-        <f>'Calculo Servicios  (2)'!H26</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="176">
-        <f t="shared" si="3"/>
-        <v>10595.689186</v>
-      </c>
-      <c r="U28" s="91" t="s">
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="V28" s="89" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="157"/>
-      <c r="B29" s="170"/>
-      <c r="C29" s="92" t="s">
+    <row r="29" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="155"/>
+      <c r="B29" s="168"/>
+      <c r="C29" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="163" t="str">
+      <c r="D29" s="161" t="str">
         <f>D22</f>
         <v>Rodriguez Flavio/Rodriguez Mauro</v>
       </c>
-      <c r="E29" s="160" t="s">
+      <c r="E29" s="158" t="s">
         <v>152</v>
       </c>
-      <c r="F29" s="179">
+      <c r="F29" s="176">
         <v>0.74</v>
       </c>
-      <c r="G29" s="64">
+      <c r="G29" s="63">
         <v>10380.261569999999</v>
       </c>
-      <c r="H29" s="156">
-        <v>0</v>
-      </c>
-      <c r="I29" s="64"/>
-      <c r="J29" s="156" t="e">
+      <c r="H29" s="154">
+        <v>0</v>
+      </c>
+      <c r="I29" s="63"/>
+      <c r="J29" s="154" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="156">
+      <c r="K29" s="154">
+        <f t="shared" si="10"/>
+        <v>10380.261569999999</v>
+      </c>
+      <c r="L29" s="154"/>
+      <c r="M29" s="160">
+        <f t="shared" si="3"/>
+        <v>311.40784709999997</v>
+      </c>
+      <c r="N29" s="160">
+        <f t="shared" si="11"/>
+        <v>10691.669417099998</v>
+      </c>
+      <c r="O29" s="154">
+        <f t="shared" si="4"/>
+        <v>8005.6891860000005</v>
+      </c>
+      <c r="P29" s="63">
+        <f t="shared" si="5"/>
+        <v>2590</v>
+      </c>
+      <c r="Q29" s="154">
+        <f>'Calculo Servicios  (2)'!H27</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="247">
+        <f t="shared" si="7"/>
+        <v>21287.19</v>
+      </c>
+      <c r="S29" s="189">
         <f t="shared" si="8"/>
-        <v>10380.261569999999</v>
-      </c>
-      <c r="L29" s="156"/>
-      <c r="M29" s="162">
-        <f t="shared" si="4"/>
-        <v>311.40784709999997</v>
-      </c>
-      <c r="N29" s="162">
+        <v>21926.19</v>
+      </c>
+      <c r="T29" s="40">
         <f t="shared" si="9"/>
-        <v>10691.669417099998</v>
-      </c>
-      <c r="O29" s="156">
-        <f t="shared" si="5"/>
-        <v>8005.6891860000005</v>
-      </c>
-      <c r="P29" s="64">
-        <f t="shared" si="6"/>
-        <v>2590</v>
-      </c>
-      <c r="Q29" s="156">
-        <f>'Calculo Servicios  (2)'!H27</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="162">
-        <f t="shared" si="3"/>
-        <v>21287.358603099998</v>
-      </c>
-      <c r="U29" s="92" t="s">
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="V29" s="90" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="70"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="62">
-        <v>0</v>
-      </c>
-      <c r="I30" s="64"/>
-      <c r="J30" s="63"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="63"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="62"/>
-      <c r="P30" s="62" t="e">
+    <row r="30" spans="1:22" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="69"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="61">
+        <v>0</v>
+      </c>
+      <c r="I30" s="63"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61" t="e">
         <f>#REF!*F30/100</f>
         <v>#REF!</v>
       </c>
-      <c r="Q30" s="62"/>
-      <c r="R30" s="106"/>
-      <c r="U30" s="91" t="s">
+      <c r="Q30" s="61"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="104"/>
+      <c r="V30" s="89" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="55" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="226"/>
-      <c r="B31" s="227"/>
-      <c r="C31" s="227"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="94"/>
-      <c r="G31" s="58">
+    <row r="31" spans="1:22" s="54" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="197"/>
+      <c r="B31" s="198"/>
+      <c r="C31" s="198"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="57">
         <f>SUM(G11:G30)</f>
         <v>1908242.672070001</v>
       </c>
-      <c r="H31" s="58">
+      <c r="H31" s="57">
         <f>SUM(H11:H30)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="59">
+      <c r="I31" s="58">
         <f>SUM(I11:I30)</f>
         <v>1244480.3504500003</v>
       </c>
-      <c r="J31" s="58"/>
-      <c r="K31" s="59">
+      <c r="J31" s="57"/>
+      <c r="K31" s="58">
         <f>SUM(K11:K30)</f>
         <v>663762.32161999983</v>
       </c>
-      <c r="L31" s="58"/>
-      <c r="M31" s="57"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="59">
+      <c r="L31" s="57"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="58">
         <f>SUM(O11:O30)</f>
         <v>1081633.520022</v>
       </c>
-      <c r="P31" s="59">
+      <c r="P31" s="58">
         <f>SUM(P11:P29)</f>
         <v>349930</v>
       </c>
-      <c r="Q31" s="59">
+      <c r="Q31" s="58">
         <f>SUM(Q11:Q29)</f>
         <v>448313.02991999994</v>
       </c>
-      <c r="R31" s="59">
+      <c r="R31" s="58">
         <f>SUM(R11:R29)</f>
-        <v>2563551.741210599</v>
-      </c>
-      <c r="U31" s="91" t="s">
+        <v>2563556.9000000004</v>
+      </c>
+      <c r="S31" s="58">
+        <f>SUM(S11:S29)</f>
+        <v>2640463.9000000004</v>
+      </c>
+      <c r="V31" s="89" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="223" t="s">
+    <row r="32" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="194" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="224"/>
-      <c r="D32" s="224"/>
-      <c r="E32" s="224"/>
-      <c r="F32" s="224"/>
-      <c r="G32" s="224"/>
-      <c r="H32" s="224"/>
-      <c r="I32" s="224"/>
-      <c r="J32" s="224"/>
-      <c r="K32" s="224"/>
-      <c r="L32" s="224"/>
-      <c r="M32" s="224"/>
-      <c r="N32" s="224"/>
-      <c r="O32" s="224"/>
-      <c r="P32" s="224"/>
-      <c r="Q32" s="224"/>
-      <c r="R32" s="225"/>
-      <c r="U32" s="91" t="s">
+      <c r="C32" s="195"/>
+      <c r="D32" s="195"/>
+      <c r="E32" s="195"/>
+      <c r="F32" s="195"/>
+      <c r="G32" s="195"/>
+      <c r="H32" s="195"/>
+      <c r="I32" s="195"/>
+      <c r="J32" s="195"/>
+      <c r="K32" s="195"/>
+      <c r="L32" s="195"/>
+      <c r="M32" s="195"/>
+      <c r="N32" s="195"/>
+      <c r="O32" s="195"/>
+      <c r="P32" s="195"/>
+      <c r="Q32" s="195"/>
+      <c r="R32" s="195"/>
+      <c r="S32" s="196"/>
+      <c r="V32" s="89" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="F33" s="54"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53" t="s">
+    <row r="33" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="F33" s="53"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="L33" s="53"/>
-      <c r="U33" s="91" t="s">
+      <c r="L33" s="52"/>
+      <c r="V33" s="89" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
-      <c r="J34" s="218"/>
-      <c r="K34" s="218"/>
-      <c r="L34" s="218"/>
-      <c r="M34" s="218"/>
-      <c r="N34" s="218"/>
-      <c r="O34" s="218"/>
-    </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C35" s="218"/>
-      <c r="D35" s="218"/>
-      <c r="E35" s="218"/>
-      <c r="F35" s="218"/>
-      <c r="G35" s="218"/>
-      <c r="H35" s="218"/>
-      <c r="I35" s="218"/>
-      <c r="J35" s="218"/>
-      <c r="K35" s="218"/>
-      <c r="L35" s="218"/>
-      <c r="M35" s="218"/>
-      <c r="N35" s="218"/>
-      <c r="O35" s="218"/>
-    </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="218"/>
-      <c r="J36" s="218"/>
-      <c r="K36" s="218"/>
-      <c r="L36" s="218"/>
-      <c r="M36" s="218"/>
-      <c r="N36" s="218"/>
-      <c r="O36" s="218"/>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C37" s="218"/>
-      <c r="D37" s="218"/>
-      <c r="E37" s="218"/>
-      <c r="F37" s="218"/>
-      <c r="G37" s="218"/>
-      <c r="H37" s="218"/>
-      <c r="I37" s="218"/>
-      <c r="J37" s="218"/>
-      <c r="K37" s="218"/>
-      <c r="L37" s="218"/>
-      <c r="M37" s="218"/>
-      <c r="N37" s="218"/>
-      <c r="O37" s="218"/>
-    </row>
-    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="218"/>
-      <c r="D38" s="218"/>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
-      <c r="H38" s="218"/>
-      <c r="I38" s="218"/>
-      <c r="J38" s="218"/>
-      <c r="K38" s="218"/>
-      <c r="L38" s="218"/>
-      <c r="M38" s="218"/>
-      <c r="N38" s="218"/>
-      <c r="O38" s="218"/>
+    <row r="34" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C34" s="190"/>
+      <c r="D34" s="190"/>
+      <c r="E34" s="190"/>
+      <c r="F34" s="190"/>
+      <c r="G34" s="190"/>
+      <c r="H34" s="190"/>
+      <c r="I34" s="190"/>
+      <c r="J34" s="190"/>
+      <c r="K34" s="190"/>
+      <c r="L34" s="190"/>
+      <c r="M34" s="190"/>
+      <c r="N34" s="190"/>
+      <c r="O34" s="190"/>
+    </row>
+    <row r="35" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C35" s="190"/>
+      <c r="D35" s="190"/>
+      <c r="E35" s="190"/>
+      <c r="F35" s="190"/>
+      <c r="G35" s="190"/>
+      <c r="H35" s="190"/>
+      <c r="I35" s="190"/>
+      <c r="J35" s="190"/>
+      <c r="K35" s="190"/>
+      <c r="L35" s="190"/>
+      <c r="M35" s="190"/>
+      <c r="N35" s="190"/>
+      <c r="O35" s="190"/>
+    </row>
+    <row r="36" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C36" s="190"/>
+      <c r="D36" s="190"/>
+      <c r="E36" s="190"/>
+      <c r="F36" s="190"/>
+      <c r="G36" s="190"/>
+      <c r="H36" s="190"/>
+      <c r="I36" s="190"/>
+      <c r="J36" s="190"/>
+      <c r="K36" s="190"/>
+      <c r="L36" s="190"/>
+      <c r="M36" s="190"/>
+      <c r="N36" s="190"/>
+      <c r="O36" s="190"/>
+    </row>
+    <row r="37" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C37" s="190"/>
+      <c r="D37" s="190"/>
+      <c r="E37" s="190"/>
+      <c r="F37" s="190"/>
+      <c r="G37" s="190"/>
+      <c r="H37" s="190"/>
+      <c r="I37" s="190"/>
+      <c r="J37" s="190"/>
+      <c r="K37" s="190"/>
+      <c r="L37" s="190"/>
+      <c r="M37" s="190"/>
+      <c r="N37" s="190"/>
+      <c r="O37" s="190"/>
+    </row>
+    <row r="38" spans="3:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="190"/>
+      <c r="D38" s="190"/>
+      <c r="E38" s="190"/>
+      <c r="F38" s="190"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="190"/>
+      <c r="K38" s="190"/>
+      <c r="L38" s="190"/>
+      <c r="M38" s="190"/>
+      <c r="N38" s="190"/>
+      <c r="O38" s="190"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="C34:O38"/>
-    <mergeCell ref="M4:R4"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="B32:R32"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="B32:S32"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M2:S9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="69" fitToWidth="0" orientation="landscape" r:id="rId1"/>
@@ -3817,7 +4108,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
@@ -3828,21 +4119,21 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="190">
+      <c r="E2" s="210">
         <v>1153202676</v>
       </c>
-      <c r="F2" s="190"/>
+      <c r="F2" s="210"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>112</v>
       </c>
       <c r="H3" s="6"/>
@@ -3853,33 +4144,33 @@
         <v>17</v>
       </c>
       <c r="H4" s="6"/>
-      <c r="J4" s="189"/>
+      <c r="J4" s="186"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="D5" s="191" t="s">
+      <c r="D5" s="211" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="191"/>
-      <c r="F5" s="191"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="192"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="212"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="D6" s="191"/>
-      <c r="E6" s="191"/>
-      <c r="F6" s="191"/>
-      <c r="G6" s="191"/>
-      <c r="H6" s="192"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="211"/>
+      <c r="F6" s="211"/>
+      <c r="G6" s="211"/>
+      <c r="H6" s="212"/>
     </row>
     <row r="7" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="D7" s="191"/>
-      <c r="E7" s="191"/>
-      <c r="F7" s="191"/>
-      <c r="G7" s="191"/>
-      <c r="H7" s="192"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+      <c r="F7" s="211"/>
+      <c r="G7" s="211"/>
+      <c r="H7" s="212"/>
     </row>
     <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
@@ -3893,7 +4184,9 @@
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="12"/>
+      <c r="H8" s="248" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
@@ -3929,567 +4222,567 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="204" t="s">
+      <c r="A13" s="224" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="204"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="204"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="204"/>
-      <c r="H13" s="204"/>
+      <c r="B13" s="224"/>
+      <c r="C13" s="224"/>
+      <c r="D13" s="224"/>
+      <c r="E13" s="224"/>
+      <c r="F13" s="224"/>
+      <c r="G13" s="224"/>
+      <c r="H13" s="224"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="239"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="187"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="186">
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="183">
         <f>392270+392270*2%</f>
         <v>400115.4</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="186">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="183">
         <v>4030.28</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="178">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="175">
         <f>SUM(H14:H16)</f>
         <v>404145.68000000005</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="40"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="39"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="205" t="s">
+      <c r="A19" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="206"/>
-      <c r="C19" s="206"/>
-      <c r="D19" s="206"/>
-      <c r="E19" s="206"/>
-      <c r="F19" s="206"/>
-      <c r="G19" s="206"/>
-      <c r="H19" s="207"/>
+      <c r="B19" s="226"/>
+      <c r="C19" s="226"/>
+      <c r="D19" s="226"/>
+      <c r="E19" s="226"/>
+      <c r="F19" s="226"/>
+      <c r="G19" s="226"/>
+      <c r="H19" s="227"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="25">
+      <c r="B20" s="18"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="24">
         <f>17878.5*2</f>
         <v>35757</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="25">
+      <c r="B21" s="18"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="24">
         <v>472904.04</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="26">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="25">
         <f>SUM(H20:H21)</f>
         <v>508661.04</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="208" t="s">
+      <c r="A23" s="228" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="208"/>
-      <c r="C23" s="208"/>
-      <c r="D23" s="208"/>
-      <c r="E23" s="208"/>
-      <c r="F23" s="208"/>
-      <c r="G23" s="208"/>
-      <c r="H23" s="208"/>
-      <c r="J23" s="25"/>
+      <c r="B23" s="228"/>
+      <c r="C23" s="228"/>
+      <c r="D23" s="228"/>
+      <c r="E23" s="228"/>
+      <c r="F23" s="228"/>
+      <c r="G23" s="228"/>
+      <c r="H23" s="228"/>
+      <c r="J23" s="24"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="93" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="25">
+      <c r="B24" s="18"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="24">
         <v>46638</v>
       </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="95" t="s">
+      <c r="A25" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="25">
+      <c r="B25" s="18"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="24">
         <v>26600</v>
       </c>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="95" t="s">
+      <c r="A26" s="93" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="25">
+      <c r="B26" s="18"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="24">
         <v>224969.09</v>
       </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="95" t="s">
+      <c r="A27" s="93" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="25">
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="24">
         <v>75000</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="26">
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="25">
         <f>SUM(H24:H27)</f>
         <v>373207.08999999997</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="205" t="s">
+      <c r="A29" s="225" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="206"/>
-      <c r="C29" s="206"/>
-      <c r="D29" s="206"/>
-      <c r="E29" s="206"/>
-      <c r="F29" s="206"/>
-      <c r="G29" s="206"/>
-      <c r="H29" s="207"/>
+      <c r="B29" s="226"/>
+      <c r="C29" s="226"/>
+      <c r="D29" s="226"/>
+      <c r="E29" s="226"/>
+      <c r="F29" s="226"/>
+      <c r="G29" s="226"/>
+      <c r="H29" s="227"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19" t="s">
+      <c r="B30" s="18"/>
+      <c r="C30" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="240">
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="188">
         <v>90000</v>
       </c>
-      <c r="I30" s="41"/>
+      <c r="I30" s="40"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="240">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="188">
         <v>45000</v>
       </c>
-      <c r="I31" s="41"/>
+      <c r="I31" s="40"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="240">
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="188">
         <v>120000</v>
       </c>
-      <c r="I32" s="41"/>
+      <c r="I32" s="40"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="187">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="184">
         <f>SUM(H30:H32)</f>
         <v>255000</v>
       </c>
-      <c r="I33" s="41"/>
+      <c r="I33" s="40"/>
       <c r="N33" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="27"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="205" t="s">
+      <c r="A35" s="225" t="s">
         <v>169</v>
       </c>
-      <c r="B35" s="206"/>
-      <c r="C35" s="206"/>
-      <c r="D35" s="206"/>
-      <c r="E35" s="206"/>
-      <c r="F35" s="206"/>
-      <c r="G35" s="206"/>
-      <c r="H35" s="207"/>
+      <c r="B35" s="226"/>
+      <c r="C35" s="226"/>
+      <c r="D35" s="226"/>
+      <c r="E35" s="226"/>
+      <c r="F35" s="226"/>
+      <c r="G35" s="226"/>
+      <c r="H35" s="227"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="47" t="s">
+      <c r="A36" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="49">
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="48">
         <v>13740.12</v>
       </c>
-      <c r="J36" s="15"/>
-    </row>
-    <row r="37" spans="1:14" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="28" t="s">
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:14" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="30">
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="29">
         <f>H17+H22+H28+H33+H36</f>
         <v>1554753.9300000002</v>
       </c>
     </row>
-    <row r="38" spans="1:14" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="43" t="s">
+    <row r="38" spans="1:14" s="13" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="B38" s="44"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="45"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="44"/>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="195" t="s">
+      <c r="A39" s="215" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="196"/>
-      <c r="C39" s="196"/>
-      <c r="D39" s="196"/>
-      <c r="E39" s="196"/>
-      <c r="F39" s="196"/>
-      <c r="G39" s="196"/>
-      <c r="H39" s="197"/>
-      <c r="I39" s="164"/>
-      <c r="K39" s="164"/>
+      <c r="B39" s="216"/>
+      <c r="C39" s="216"/>
+      <c r="D39" s="216"/>
+      <c r="E39" s="216"/>
+      <c r="F39" s="216"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="217"/>
+      <c r="I39" s="162"/>
+      <c r="K39" s="162"/>
     </row>
     <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="198"/>
-      <c r="B40" s="199"/>
-      <c r="C40" s="199"/>
-      <c r="D40" s="199"/>
-      <c r="E40" s="199"/>
-      <c r="F40" s="199"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="200"/>
+      <c r="A40" s="218"/>
+      <c r="B40" s="219"/>
+      <c r="C40" s="219"/>
+      <c r="D40" s="219"/>
+      <c r="E40" s="219"/>
+      <c r="F40" s="219"/>
+      <c r="G40" s="219"/>
+      <c r="H40" s="220"/>
     </row>
     <row r="41" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="209" t="s">
+      <c r="A41" s="235" t="s">
         <v>168</v>
       </c>
-      <c r="B41" s="210"/>
-      <c r="C41" s="210"/>
-      <c r="D41" s="210"/>
-      <c r="E41" s="210"/>
-      <c r="F41" s="210"/>
-      <c r="G41" s="211"/>
-      <c r="H41" s="188">
+      <c r="B41" s="236"/>
+      <c r="C41" s="236"/>
+      <c r="D41" s="236"/>
+      <c r="E41" s="236"/>
+      <c r="F41" s="236"/>
+      <c r="G41" s="237"/>
+      <c r="H41" s="185">
         <v>350000</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="212"/>
-      <c r="B42" s="213"/>
-      <c r="C42" s="213"/>
-      <c r="D42" s="213"/>
-      <c r="E42" s="213"/>
-      <c r="F42" s="213"/>
-      <c r="G42" s="214"/>
-      <c r="H42" s="31"/>
-    </row>
-    <row r="43" spans="1:14" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="215" t="s">
+      <c r="A42" s="229"/>
+      <c r="B42" s="230"/>
+      <c r="C42" s="230"/>
+      <c r="D42" s="230"/>
+      <c r="E42" s="230"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="30"/>
+    </row>
+    <row r="43" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="232" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="216"/>
-      <c r="C43" s="216"/>
-      <c r="D43" s="216"/>
-      <c r="E43" s="216"/>
-      <c r="F43" s="216"/>
-      <c r="G43" s="217"/>
-      <c r="H43" s="32">
+      <c r="B43" s="233"/>
+      <c r="C43" s="233"/>
+      <c r="D43" s="233"/>
+      <c r="E43" s="233"/>
+      <c r="F43" s="233"/>
+      <c r="G43" s="234"/>
+      <c r="H43" s="31">
         <f>SUM(H41:H42)</f>
         <v>350000</v>
       </c>
     </row>
-    <row r="44" spans="1:14" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="184"/>
-      <c r="B44" s="184"/>
-      <c r="C44" s="184"/>
-      <c r="D44" s="184"/>
-      <c r="E44" s="184"/>
-      <c r="F44" s="184"/>
-      <c r="G44" s="184"/>
-      <c r="H44" s="185"/>
+    <row r="44" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="181"/>
+      <c r="B44" s="181"/>
+      <c r="C44" s="181"/>
+      <c r="D44" s="181"/>
+      <c r="E44" s="181"/>
+      <c r="F44" s="181"/>
+      <c r="G44" s="181"/>
+      <c r="H44" s="182"/>
     </row>
     <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H45" s="19"/>
-      <c r="J45" s="15"/>
+      <c r="H45" s="18"/>
+      <c r="J45" s="14"/>
     </row>
     <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="193" t="s">
+      <c r="A46" s="213" t="s">
         <v>144</v>
       </c>
-      <c r="B46" s="193"/>
-      <c r="C46" s="193"/>
-      <c r="D46" s="193"/>
-      <c r="E46" s="193"/>
-      <c r="F46" s="193"/>
-      <c r="G46" s="193"/>
-      <c r="H46" s="30">
+      <c r="B46" s="213"/>
+      <c r="C46" s="213"/>
+      <c r="D46" s="213"/>
+      <c r="E46" s="213"/>
+      <c r="F46" s="213"/>
+      <c r="G46" s="213"/>
+      <c r="H46" s="29">
         <f>+H37+H38</f>
         <v>1554753.9300000002</v>
       </c>
-      <c r="J46" s="164"/>
+      <c r="J46" s="162"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
     </row>
     <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="33">
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="32">
         <f>H43</f>
         <v>350000</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="19"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="201" t="s">
+      <c r="A50" s="221" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="202"/>
-      <c r="C50" s="202"/>
-      <c r="D50" s="202"/>
-      <c r="E50" s="202"/>
-      <c r="F50" s="202"/>
-      <c r="G50" s="202"/>
-      <c r="H50" s="203"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
+      <c r="D50" s="222"/>
+      <c r="E50" s="222"/>
+      <c r="F50" s="222"/>
+      <c r="G50" s="222"/>
+      <c r="H50" s="223"/>
     </row>
     <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="194" t="s">
+      <c r="A51" s="214" t="s">
         <v>151</v>
       </c>
-      <c r="B51" s="194"/>
-      <c r="C51" s="194"/>
-      <c r="D51" s="194"/>
-      <c r="E51" s="194"/>
-      <c r="F51" s="194"/>
-      <c r="G51" s="194"/>
-      <c r="H51" s="39">
+      <c r="B51" s="214"/>
+      <c r="C51" s="214"/>
+      <c r="D51" s="214"/>
+      <c r="E51" s="214"/>
+      <c r="F51" s="214"/>
+      <c r="G51" s="214"/>
+      <c r="H51" s="38">
         <v>2287941.4208707316</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="42">
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="41">
         <f>Planilla!I31</f>
         <v>1244480.3504500003</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="34" t="s">
+      <c r="A53" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="36">
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="35">
         <f>-(H37+H43)</f>
         <v>-1904753.9300000002</v>
       </c>
-      <c r="J53" s="15"/>
+      <c r="J53" s="14"/>
     </row>
     <row r="54" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A54" s="37" t="s">
+      <c r="A54" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="46">
+      <c r="B54" s="37"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="45">
         <f>SUM(H51:H53)</f>
         <v>1627667.8413207317</v>
       </c>
@@ -4522,1007 +4815,1007 @@
   <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="111" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="111" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="111" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="111" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="111" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="111" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="111" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.42578125" style="111"/>
-    <col min="13" max="13" width="14.7109375" style="111" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="111" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="111"/>
+    <col min="1" max="1" width="12.140625" style="109" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="109" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="109" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="109" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="109" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="109" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="109" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.42578125" style="109"/>
+    <col min="13" max="13" width="14.7109375" style="109" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="109" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="109"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="230" t="s">
+      <c r="A1" s="238" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="231"/>
-      <c r="C1" s="231"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="232"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="240"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="152"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="151" t="s">
+      <c r="A2" s="150"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="149" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="148"/>
+      <c r="E2" s="146"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="150">
+      <c r="A3" s="148">
         <f>13+28+19</f>
         <v>60</v>
       </c>
-      <c r="B3" s="105">
+      <c r="B3" s="103">
         <v>10531.71</v>
       </c>
-      <c r="C3" s="149">
+      <c r="C3" s="147">
         <f>+B3/A3</f>
         <v>175.52849999999998</v>
       </c>
-      <c r="D3" s="149">
+      <c r="D3" s="147">
         <v>4863.8999999999996</v>
       </c>
-      <c r="E3" s="148" t="s">
+      <c r="E3" s="146" t="s">
         <v>139</v>
       </c>
-      <c r="I3" s="111" t="s">
+      <c r="I3" s="109" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="147"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="145"/>
+      <c r="A4" s="145"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="143"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="144"/>
-      <c r="B5" s="144"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
+      <c r="A5" s="142"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
     </row>
     <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144"/>
-      <c r="B6" s="144"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="144"/>
-      <c r="E6" s="144"/>
+      <c r="A6" s="142"/>
+      <c r="B6" s="142"/>
+      <c r="C6" s="142"/>
+      <c r="D6" s="142"/>
+      <c r="E6" s="142"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="233" t="s">
+      <c r="A7" s="241" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="234"/>
-      <c r="C7" s="234"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="234"/>
-      <c r="H7" s="235"/>
-      <c r="L7" s="111" t="s">
+      <c r="B7" s="242"/>
+      <c r="C7" s="242"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="242"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="243"/>
+      <c r="L7" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="111" t="s">
+      <c r="M7" s="109" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="104">
+      <c r="A8" s="102">
         <v>400523.88</v>
       </c>
-      <c r="B8" s="142" t="s">
+      <c r="B8" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="142" t="s">
+      <c r="C8" s="140" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="142" t="s">
+      <c r="D8" s="140" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="143">
+      <c r="E8" s="141">
         <f>3935/2</f>
         <v>1967.5</v>
       </c>
-      <c r="F8" s="142" t="s">
+      <c r="F8" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="142" t="s">
+      <c r="G8" s="140" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="141" t="s">
+      <c r="H8" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="137">
+      <c r="K8" s="135">
         <v>19</v>
       </c>
-      <c r="L8" s="123">
+      <c r="L8" s="121">
         <v>7502.93</v>
       </c>
-      <c r="M8" s="123">
+      <c r="M8" s="121">
         <v>2365.2600000000002</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="140" t="s">
+      <c r="A9" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="137">
+      <c r="B9" s="135">
         <v>1617</v>
       </c>
-      <c r="C9" s="137">
+      <c r="C9" s="135">
         <f>B9+J25</f>
         <v>1689</v>
       </c>
-      <c r="D9" s="137">
+      <c r="D9" s="135">
         <f t="shared" ref="D9:D20" si="0">+C9-B9</f>
         <v>72</v>
       </c>
-      <c r="E9" s="101">
+      <c r="E9" s="99">
         <f>+D9/E8</f>
         <v>3.6594663278271919E-2</v>
       </c>
-      <c r="F9" s="100">
+      <c r="F9" s="98">
         <f>+A8*E9</f>
         <v>14657.036523506989</v>
       </c>
-      <c r="G9" s="100">
+      <c r="G9" s="98">
         <f>+(A8*A23)/12</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H9" s="99">
+      <c r="H9" s="97">
         <f>+G9+F9</f>
         <v>24606.517913595933</v>
       </c>
-      <c r="K9" s="111">
+      <c r="K9" s="109">
         <v>106</v>
       </c>
-      <c r="L9" s="123">
+      <c r="L9" s="121">
         <f>+L8*O9</f>
         <v>1575.6152999999999</v>
       </c>
-      <c r="M9" s="111">
+      <c r="M9" s="109">
         <f>M8*21%</f>
         <v>496.70460000000003</v>
       </c>
-      <c r="N9" s="111" t="s">
+      <c r="N9" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="O9" s="103">
+      <c r="O9" s="101">
         <v>0.21</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="138" t="s">
+      <c r="A10" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="137">
+      <c r="B10" s="135">
         <v>4104</v>
       </c>
-      <c r="C10" s="137">
+      <c r="C10" s="135">
         <f t="shared" ref="C10:C20" si="1">B10+J26</f>
         <v>4195</v>
       </c>
-      <c r="D10" s="137">
+      <c r="D10" s="135">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="E10" s="101">
+      <c r="E10" s="99">
         <f>+D10/E8</f>
         <v>4.6251588310038116E-2</v>
       </c>
-      <c r="F10" s="100">
+      <c r="F10" s="98">
         <f>+A8*E10</f>
         <v>18524.865606099109</v>
       </c>
-      <c r="G10" s="100">
+      <c r="G10" s="98">
         <f>+G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H10" s="99">
+      <c r="H10" s="97">
         <f>+G10+F10</f>
         <v>28474.346996188055</v>
       </c>
-      <c r="K10" s="111">
+      <c r="K10" s="109">
         <v>60</v>
       </c>
-      <c r="L10" s="123">
+      <c r="L10" s="121">
         <f>+L8*O10</f>
         <v>481.98822320000005</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="109">
         <f>+M8*6.424%</f>
         <v>151.94430240000003</v>
       </c>
-      <c r="N10" s="111" t="s">
+      <c r="N10" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="O10" s="102">
+      <c r="O10" s="100">
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="138" t="s">
+      <c r="A11" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="137">
+      <c r="B11" s="135">
         <v>7644</v>
       </c>
-      <c r="C11" s="137">
+      <c r="C11" s="135">
         <f t="shared" si="1"/>
         <v>7807</v>
       </c>
-      <c r="D11" s="137">
+      <c r="D11" s="135">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="E11" s="101">
+      <c r="E11" s="99">
         <f>+D11/E8</f>
         <v>8.2846251588310035E-2</v>
       </c>
-      <c r="F11" s="100">
+      <c r="F11" s="98">
         <f>+A8*E11</f>
         <v>33181.902129606096</v>
       </c>
-      <c r="G11" s="100">
+      <c r="G11" s="98">
         <f>G10</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H11" s="99">
+      <c r="H11" s="97">
         <f>+G11+F11</f>
         <v>43131.383519695039</v>
       </c>
-      <c r="K11" s="111">
+      <c r="K11" s="109">
         <v>79</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="121">
         <f>+L8*0.001%</f>
         <v>7.5029300000000007E-2</v>
       </c>
-      <c r="M11" s="111">
+      <c r="M11" s="109">
         <v>0.03</v>
       </c>
-      <c r="N11" s="111" t="s">
+      <c r="N11" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="O11" s="123">
+      <c r="O11" s="121">
         <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="138" t="s">
+      <c r="A12" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="137">
+      <c r="B12" s="135">
         <v>6554</v>
       </c>
-      <c r="C12" s="137">
+      <c r="C12" s="135">
         <f t="shared" si="1"/>
         <v>6730</v>
       </c>
-      <c r="D12" s="137">
+      <c r="D12" s="135">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="E12" s="101">
+      <c r="E12" s="99">
         <f>+D12/E8</f>
         <v>8.9453621346886919E-2</v>
       </c>
-      <c r="F12" s="100">
+      <c r="F12" s="98">
         <f>+A8*E12</f>
         <v>35828.311501905977</v>
       </c>
-      <c r="G12" s="100">
+      <c r="G12" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H12" s="99">
+      <c r="H12" s="97">
         <f t="shared" ref="H12:H20" si="2">SUM(F12:G12)</f>
         <v>45777.792891994919</v>
       </c>
-      <c r="K12" s="111">
+      <c r="K12" s="109">
         <v>89</v>
       </c>
-      <c r="L12" s="123">
+      <c r="L12" s="121">
         <v>400</v>
       </c>
-      <c r="M12" s="111">
+      <c r="M12" s="109">
         <v>253</v>
       </c>
-      <c r="N12" s="111" t="s">
+      <c r="N12" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="O12" s="111">
+      <c r="O12" s="109">
         <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="138" t="s">
+      <c r="A13" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="137">
+      <c r="B13" s="135">
         <v>7564</v>
       </c>
-      <c r="C13" s="137">
+      <c r="C13" s="135">
         <f t="shared" si="1"/>
         <v>7767</v>
       </c>
-      <c r="D13" s="137">
+      <c r="D13" s="135">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="E13" s="101">
+      <c r="E13" s="99">
         <f>+D13/E8</f>
         <v>0.10317662007623889</v>
       </c>
-      <c r="F13" s="100">
+      <c r="F13" s="98">
         <f>+A8*E13</f>
         <v>41324.700198221093</v>
       </c>
-      <c r="G13" s="100">
+      <c r="G13" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H13" s="99">
+      <c r="H13" s="97">
         <f t="shared" si="2"/>
         <v>51274.181588310035</v>
       </c>
-      <c r="K13" s="111">
+      <c r="K13" s="109">
         <v>140</v>
       </c>
-      <c r="L13" s="139">
+      <c r="L13" s="137">
         <f>SUM(L8:L12)-0.45</f>
         <v>9960.1585524999991</v>
       </c>
-      <c r="M13" s="111">
+      <c r="M13" s="109">
         <f>SUM(M8:M12)</f>
         <v>3266.9389024000006</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="138" t="s">
+      <c r="A14" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="137">
+      <c r="B14" s="135">
         <v>10119</v>
       </c>
-      <c r="C14" s="137">
+      <c r="C14" s="135">
         <f t="shared" si="1"/>
         <v>10334</v>
       </c>
-      <c r="D14" s="137">
+      <c r="D14" s="135">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
-      <c r="E14" s="101">
+      <c r="E14" s="99">
         <f>+D14/E8</f>
         <v>0.10927573062261753</v>
       </c>
-      <c r="F14" s="100">
+      <c r="F14" s="98">
         <f>+A8*E14</f>
         <v>43767.539618805589</v>
       </c>
-      <c r="G14" s="100">
+      <c r="G14" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H14" s="99">
+      <c r="H14" s="97">
         <f t="shared" si="2"/>
         <v>53717.021008894531</v>
       </c>
-      <c r="K14" s="111">
+      <c r="K14" s="109">
         <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="138" t="s">
+      <c r="A15" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="137">
+      <c r="B15" s="135">
         <v>8986</v>
       </c>
-      <c r="C15" s="137">
+      <c r="C15" s="135">
         <f t="shared" si="1"/>
         <v>9068</v>
       </c>
-      <c r="D15" s="137">
+      <c r="D15" s="135">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="E15" s="101">
+      <c r="E15" s="99">
         <f>+D15/E8</f>
         <v>4.1677255400254132E-2</v>
       </c>
-      <c r="F15" s="100">
+      <c r="F15" s="98">
         <f>+A8*E15</f>
         <v>16692.736040660737</v>
       </c>
-      <c r="G15" s="100">
+      <c r="G15" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H15" s="99">
+      <c r="H15" s="97">
         <f t="shared" si="2"/>
         <v>26642.217430749683</v>
       </c>
-      <c r="K15" s="111">
+      <c r="K15" s="109">
         <v>221</v>
       </c>
-      <c r="L15" s="111">
+      <c r="L15" s="109">
         <f>+L13+M13</f>
         <v>13227.0974549</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="138" t="s">
+      <c r="A16" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="137">
+      <c r="B16" s="135">
         <v>7032</v>
       </c>
-      <c r="C16" s="137">
+      <c r="C16" s="135">
         <f t="shared" si="1"/>
         <v>7034</v>
       </c>
-      <c r="D16" s="137">
+      <c r="D16" s="135">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E16" s="101">
+      <c r="E16" s="99">
         <f>+D16/E8</f>
         <v>1.0165184243964421E-3</v>
       </c>
-      <c r="F16" s="100">
+      <c r="F16" s="98">
         <f>+A8*E16</f>
         <v>407.13990343074965</v>
       </c>
-      <c r="G16" s="100">
+      <c r="G16" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H16" s="99">
+      <c r="H16" s="97">
         <f t="shared" si="2"/>
         <v>10356.621293519693</v>
       </c>
-      <c r="K16" s="111">
+      <c r="K16" s="109">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="138" t="s">
+      <c r="A17" s="136" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="137">
+      <c r="B17" s="135">
         <v>1623</v>
       </c>
-      <c r="C17" s="137">
+      <c r="C17" s="135">
         <f t="shared" si="1"/>
         <v>1668</v>
       </c>
-      <c r="D17" s="137">
+      <c r="D17" s="135">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="E17" s="101">
+      <c r="E17" s="99">
         <f>+D17/E8</f>
         <v>2.2871664548919948E-2</v>
       </c>
-      <c r="F17" s="100">
+      <c r="F17" s="98">
         <f>+A8*E17</f>
         <v>9160.6478271918677</v>
       </c>
-      <c r="G17" s="100">
+      <c r="G17" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H17" s="99">
+      <c r="H17" s="97">
         <f t="shared" si="2"/>
         <v>19110.12921728081</v>
       </c>
-      <c r="K17" s="111">
+      <c r="K17" s="109">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="138" t="s">
+      <c r="A18" s="136" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="137">
+      <c r="B18" s="135">
         <v>3932</v>
       </c>
-      <c r="C18" s="137">
+      <c r="C18" s="135">
         <f t="shared" si="1"/>
         <v>4021</v>
       </c>
-      <c r="D18" s="137">
+      <c r="D18" s="135">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="E18" s="101">
+      <c r="E18" s="99">
         <f>+D18/E8</f>
         <v>4.5235069885641674E-2</v>
       </c>
-      <c r="F18" s="100">
+      <c r="F18" s="98">
         <f>+A8*E18</f>
         <v>18117.725702668358</v>
       </c>
-      <c r="G18" s="100">
+      <c r="G18" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H18" s="99">
+      <c r="H18" s="97">
         <f t="shared" si="2"/>
         <v>28067.2070927573</v>
       </c>
-      <c r="K18" s="111">
+      <c r="K18" s="109">
         <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="138" t="s">
+      <c r="A19" s="136" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="137">
+      <c r="B19" s="135">
         <v>6887</v>
       </c>
-      <c r="C19" s="137">
+      <c r="C19" s="135">
         <f t="shared" si="1"/>
         <v>6994</v>
       </c>
-      <c r="D19" s="137">
+      <c r="D19" s="135">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="E19" s="101">
+      <c r="E19" s="99">
         <f>+D19/E8</f>
         <v>5.4383735705209657E-2</v>
       </c>
-      <c r="F19" s="100">
+      <c r="F19" s="98">
         <f>+A8*E19</f>
         <v>21781.98483354511</v>
       </c>
-      <c r="G19" s="100">
+      <c r="G19" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H19" s="99">
+      <c r="H19" s="97">
         <f t="shared" si="2"/>
         <v>31731.466223634052</v>
       </c>
-      <c r="K19" s="111">
+      <c r="K19" s="109">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="138" t="s">
+      <c r="A20" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="137">
+      <c r="B20" s="135">
         <v>1884</v>
       </c>
-      <c r="C20" s="137">
+      <c r="C20" s="135">
         <f t="shared" si="1"/>
         <v>2020</v>
       </c>
-      <c r="D20" s="137">
+      <c r="D20" s="135">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="E20" s="101">
+      <c r="E20" s="99">
         <f>+D20/E8</f>
         <v>6.9123252858958067E-2</v>
       </c>
-      <c r="F20" s="100">
+      <c r="F20" s="98">
         <f>+A8*E20</f>
         <v>27685.513433290977</v>
       </c>
-      <c r="G20" s="100">
+      <c r="G20" s="98">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H20" s="99">
+      <c r="H20" s="97">
         <f t="shared" si="2"/>
         <v>37634.994823379922</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="136" t="s">
+      <c r="A21" s="134" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="135"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="134">
+      <c r="B21" s="133"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="132">
         <f>SUM(D9:D20)</f>
         <v>1381</v>
       </c>
-      <c r="E21" s="133"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="98">
+      <c r="E21" s="131"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="96">
         <f>SUM(H9:H20)</f>
         <v>400523.88</v>
       </c>
-      <c r="J21" s="123">
+      <c r="J21" s="121">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="97">
+      <c r="A22" s="95">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
       </c>
-      <c r="B22" s="132" t="s">
+      <c r="B22" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="L22" s="131"/>
+      <c r="L22" s="129"/>
     </row>
     <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="96">
+      <c r="A23" s="94">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
       </c>
-      <c r="B23" s="130" t="s">
+      <c r="B23" s="128" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="129"/>
-      <c r="J25" s="111">
+      <c r="A25" s="127"/>
+      <c r="J25" s="109">
         <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="J26" s="111">
+      <c r="J26" s="109">
         <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="111">
+      <c r="J27" s="109">
         <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="236" t="s">
+      <c r="B28" s="244" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="237"/>
-      <c r="D28" s="237"/>
-      <c r="E28" s="237"/>
-      <c r="F28" s="238"/>
-      <c r="J28" s="111">
+      <c r="C28" s="245"/>
+      <c r="D28" s="245"/>
+      <c r="E28" s="245"/>
+      <c r="F28" s="246"/>
+      <c r="J28" s="109">
         <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B29" s="128" t="s">
+      <c r="B29" s="126" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="127" t="s">
+      <c r="C29" s="125" t="s">
         <v>135</v>
       </c>
-      <c r="D29" s="127" t="s">
+      <c r="D29" s="125" t="s">
         <v>134</v>
       </c>
-      <c r="E29" s="127" t="s">
+      <c r="E29" s="125" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="126" t="s">
+      <c r="F29" s="124" t="s">
         <v>132</v>
       </c>
-      <c r="J29" s="111">
+      <c r="J29" s="109">
         <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="122" t="s">
+      <c r="B30" s="120" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="100">
+      <c r="C30" s="98">
         <v>4000</v>
       </c>
-      <c r="D30" s="100">
-        <v>0</v>
-      </c>
-      <c r="E30" s="120"/>
-      <c r="F30" s="99">
+      <c r="D30" s="98">
+        <v>0</v>
+      </c>
+      <c r="E30" s="118"/>
+      <c r="F30" s="97">
         <f>+C30</f>
         <v>4000</v>
       </c>
-      <c r="J30" s="125">
+      <c r="J30" s="123">
         <v>215</v>
       </c>
-      <c r="M30" s="111">
+      <c r="M30" s="109">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="122" t="s">
+      <c r="B31" s="120" t="s">
         <v>130</v>
       </c>
-      <c r="C31" s="100">
+      <c r="C31" s="98">
         <v>4000</v>
       </c>
-      <c r="D31" s="100">
-        <v>0</v>
-      </c>
-      <c r="E31" s="120"/>
-      <c r="F31" s="99">
+      <c r="D31" s="98">
+        <v>0</v>
+      </c>
+      <c r="E31" s="118"/>
+      <c r="F31" s="97">
         <f t="shared" ref="F31:F44" si="3">+F30+C31-D31</f>
         <v>8000</v>
       </c>
-      <c r="J31" s="111">
+      <c r="J31" s="109">
         <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="122" t="s">
+      <c r="B32" s="120" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="100">
+      <c r="C32" s="98">
         <v>4000</v>
       </c>
-      <c r="D32" s="100">
-        <v>0</v>
-      </c>
-      <c r="E32" s="120"/>
-      <c r="F32" s="99">
+      <c r="D32" s="98">
+        <v>0</v>
+      </c>
+      <c r="E32" s="118"/>
+      <c r="F32" s="97">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="J32" s="111">
+      <c r="J32" s="109">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="122" t="s">
+      <c r="B33" s="120" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="100">
+      <c r="C33" s="98">
         <v>4000</v>
       </c>
-      <c r="D33" s="100">
-        <v>0</v>
-      </c>
-      <c r="E33" s="120"/>
-      <c r="F33" s="99">
+      <c r="D33" s="98">
+        <v>0</v>
+      </c>
+      <c r="E33" s="118"/>
+      <c r="F33" s="97">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="J33" s="111">
+      <c r="J33" s="109">
         <v>45</v>
       </c>
-      <c r="K33" s="124">
+      <c r="K33" s="122">
         <f>11934.02-11933.71</f>
         <v>0.31000000000130967</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="122" t="s">
+      <c r="B34" s="120" t="s">
         <v>127</v>
       </c>
-      <c r="C34" s="100">
+      <c r="C34" s="98">
         <v>4000</v>
       </c>
-      <c r="D34" s="100">
-        <v>0</v>
-      </c>
-      <c r="E34" s="120"/>
-      <c r="F34" s="99">
+      <c r="D34" s="98">
+        <v>0</v>
+      </c>
+      <c r="E34" s="118"/>
+      <c r="F34" s="97">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="J34" s="111">
+      <c r="J34" s="109">
         <v>89</v>
       </c>
     </row>
     <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="122" t="s">
+      <c r="B35" s="120" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="100">
+      <c r="C35" s="98">
         <v>4000</v>
       </c>
-      <c r="D35" s="100">
-        <v>0</v>
-      </c>
-      <c r="E35" s="120"/>
-      <c r="F35" s="99">
+      <c r="D35" s="98">
+        <v>0</v>
+      </c>
+      <c r="E35" s="118"/>
+      <c r="F35" s="97">
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="J35" s="111">
+      <c r="J35" s="109">
         <v>107</v>
       </c>
     </row>
     <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="122" t="s">
+      <c r="B36" s="120" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="100">
+      <c r="C36" s="98">
         <v>4000</v>
       </c>
-      <c r="D36" s="100">
-        <v>0</v>
-      </c>
-      <c r="E36" s="120"/>
-      <c r="F36" s="99">
+      <c r="D36" s="98">
+        <v>0</v>
+      </c>
+      <c r="E36" s="118"/>
+      <c r="F36" s="97">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
-      <c r="J36" s="111">
+      <c r="J36" s="109">
         <v>136</v>
       </c>
     </row>
     <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="122" t="s">
+      <c r="B37" s="120" t="s">
         <v>124</v>
       </c>
-      <c r="C37" s="121">
+      <c r="C37" s="119">
         <v>4000</v>
       </c>
-      <c r="D37" s="100">
-        <v>0</v>
-      </c>
-      <c r="E37" s="120"/>
-      <c r="F37" s="99">
+      <c r="D37" s="98">
+        <v>0</v>
+      </c>
+      <c r="E37" s="118"/>
+      <c r="F37" s="97">
         <f t="shared" si="3"/>
         <v>32000</v>
       </c>
     </row>
     <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="122" t="s">
+      <c r="B38" s="120" t="s">
         <v>123</v>
       </c>
-      <c r="C38" s="121">
+      <c r="C38" s="119">
         <v>4000</v>
       </c>
-      <c r="D38" s="121">
+      <c r="D38" s="119">
         <v>3500</v>
       </c>
-      <c r="E38" s="120" t="s">
+      <c r="E38" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="F38" s="99">
+      <c r="F38" s="97">
         <f t="shared" si="3"/>
         <v>32500</v>
       </c>
-      <c r="M38" s="123">
+      <c r="M38" s="121">
         <f>88.05-100</f>
         <v>-11.950000000000003</v>
       </c>
     </row>
     <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="122" t="s">
+      <c r="B39" s="120" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="121">
+      <c r="C39" s="119">
         <v>4000</v>
       </c>
-      <c r="D39" s="120"/>
-      <c r="E39" s="120"/>
-      <c r="F39" s="99">
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="97">
         <f t="shared" si="3"/>
         <v>36500</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="122" t="s">
+      <c r="B40" s="120" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="121">
+      <c r="C40" s="119">
         <v>4000</v>
       </c>
-      <c r="D40" s="120"/>
-      <c r="E40" s="120"/>
-      <c r="F40" s="99">
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="97">
         <f t="shared" si="3"/>
         <v>40500</v>
       </c>
     </row>
     <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="122" t="s">
+      <c r="B41" s="120" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="121">
+      <c r="C41" s="119">
         <v>4000</v>
       </c>
-      <c r="D41" s="120"/>
-      <c r="E41" s="120"/>
-      <c r="F41" s="99">
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="97">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="122" t="s">
+      <c r="B42" s="120" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="121">
-        <v>0</v>
-      </c>
-      <c r="D42" s="120"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="99">
+      <c r="C42" s="119">
+        <v>0</v>
+      </c>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="97">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="122" t="s">
+      <c r="B43" s="120" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="121">
-        <v>0</v>
-      </c>
-      <c r="D43" s="120"/>
-      <c r="E43" s="120"/>
-      <c r="F43" s="99">
+      <c r="C43" s="119">
+        <v>0</v>
+      </c>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="97">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="119" t="s">
+      <c r="B44" s="117" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="118">
-        <v>0</v>
-      </c>
-      <c r="D44" s="117"/>
-      <c r="E44" s="117"/>
-      <c r="F44" s="116">
+      <c r="C44" s="116">
+        <v>0</v>
+      </c>
+      <c r="D44" s="115"/>
+      <c r="E44" s="115"/>
+      <c r="F44" s="114">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="119" t="s">
+      <c r="B45" s="117" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="118">
-        <v>0</v>
-      </c>
-      <c r="D45" s="117"/>
-      <c r="E45" s="117"/>
-      <c r="F45" s="116">
+      <c r="C45" s="116">
+        <v>0</v>
+      </c>
+      <c r="D45" s="115"/>
+      <c r="E45" s="115"/>
+      <c r="F45" s="114">
         <f>+F43+C45-D45</f>
         <v>44500</v>
       </c>
     </row>
     <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="119" t="s">
+      <c r="B46" s="117" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="118">
-        <v>0</v>
-      </c>
-      <c r="D46" s="117"/>
-      <c r="E46" s="117"/>
-      <c r="F46" s="116">
+      <c r="C46" s="116">
+        <v>0</v>
+      </c>
+      <c r="D46" s="115"/>
+      <c r="E46" s="115"/>
+      <c r="F46" s="114">
         <f>+F44+C46-D46</f>
         <v>44500</v>
       </c>
     </row>
     <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="115" t="s">
+      <c r="B47" s="113" t="s">
         <v>113</v>
       </c>
-      <c r="C47" s="114">
+      <c r="C47" s="112">
         <f>-A47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="113"/>
-      <c r="E47" s="113"/>
-      <c r="F47" s="112">
+      <c r="D47" s="111"/>
+      <c r="E47" s="111"/>
+      <c r="F47" s="110">
         <f>+F45+C47-D47</f>
         <v>44500</v>
       </c>

--- a/TUCUMAN 1061/Octubre/tucuman Octubre.xlsx
+++ b/TUCUMAN 1061/Octubre/tucuman Octubre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DDA536-A67F-442B-BF0C-B17FB27757C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32992551-F71B-4ACF-9116-27179381B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="176">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -597,6 +597,9 @@
   </si>
   <si>
     <t>VTO: 14/11</t>
+  </si>
+  <si>
+    <t>A JORGE EL MES PASADO LO PUSIMOS IMPAGO Y EL PAGO</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1434,7 @@
     <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1728,6 +1731,8 @@
     <xf numFmtId="6" fontId="35" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1788,6 +1793,18 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1899,20 +1916,22 @@
     <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2340,28 +2359,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="191" t="str">
+      <c r="A1" s="193" t="str">
         <f>Gastos!E8</f>
         <v xml:space="preserve">PERIODO: OCTUBRE </v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="193"/>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="195"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -2374,15 +2393,15 @@
       <c r="J2" s="52"/>
       <c r="K2" s="52"/>
       <c r="L2" s="12"/>
-      <c r="M2" s="201" t="s">
+      <c r="M2" s="203" t="s">
         <v>172</v>
       </c>
-      <c r="N2" s="202"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="202"/>
-      <c r="Q2" s="202"/>
-      <c r="R2" s="202"/>
-      <c r="S2" s="203"/>
+      <c r="N2" s="204"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="204"/>
+      <c r="Q2" s="204"/>
+      <c r="R2" s="204"/>
+      <c r="S2" s="205"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="83"/>
@@ -2394,54 +2413,54 @@
       <c r="I3" s="52"/>
       <c r="J3" s="52"/>
       <c r="L3" s="85"/>
-      <c r="M3" s="204"/>
-      <c r="N3" s="205"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="205"/>
-      <c r="Q3" s="205"/>
-      <c r="R3" s="205"/>
-      <c r="S3" s="206"/>
+      <c r="M3" s="206"/>
+      <c r="N3" s="207"/>
+      <c r="O3" s="207"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="207"/>
+      <c r="S3" s="208"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="83"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="215" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="252"/>
+      <c r="D4" s="215"/>
       <c r="G4" s="52"/>
       <c r="H4" s="52"/>
       <c r="I4" s="52"/>
       <c r="J4" s="52"/>
       <c r="L4" s="85"/>
-      <c r="M4" s="204"/>
-      <c r="N4" s="205"/>
-      <c r="O4" s="205"/>
-      <c r="P4" s="205"/>
-      <c r="Q4" s="205"/>
-      <c r="R4" s="205"/>
-      <c r="S4" s="206"/>
+      <c r="M4" s="206"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="208"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="83"/>
       <c r="B5" s="86"/>
-      <c r="C5" s="199">
+      <c r="C5" s="201">
         <f>D3</f>
         <v>472904.04</v>
       </c>
-      <c r="D5" s="199"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="12"/>
       <c r="G5" s="52"/>
       <c r="H5" s="52"/>
       <c r="I5" s="52"/>
       <c r="J5" s="52"/>
       <c r="L5" s="85"/>
-      <c r="M5" s="204"/>
-      <c r="N5" s="205"/>
-      <c r="O5" s="205"/>
-      <c r="P5" s="205"/>
-      <c r="Q5" s="205"/>
-      <c r="R5" s="205"/>
-      <c r="S5" s="206"/>
+      <c r="M5" s="206"/>
+      <c r="N5" s="207"/>
+      <c r="O5" s="207"/>
+      <c r="P5" s="207"/>
+      <c r="Q5" s="207"/>
+      <c r="R5" s="207"/>
+      <c r="S5" s="208"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="83"/>
@@ -2456,22 +2475,22 @@
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="52"/>
-      <c r="M6" s="204"/>
-      <c r="N6" s="205"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="205"/>
-      <c r="Q6" s="205"/>
-      <c r="R6" s="205"/>
-      <c r="S6" s="206"/>
+      <c r="M6" s="206"/>
+      <c r="N6" s="207"/>
+      <c r="O6" s="207"/>
+      <c r="P6" s="207"/>
+      <c r="Q6" s="207"/>
+      <c r="R6" s="207"/>
+      <c r="S6" s="208"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="83"/>
       <c r="B7" s="82"/>
-      <c r="C7" s="199">
+      <c r="C7" s="201">
         <f>C2-D3</f>
         <v>1081849.8900000001</v>
       </c>
-      <c r="D7" s="199"/>
+      <c r="D7" s="201"/>
       <c r="E7" s="84"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
@@ -2479,13 +2498,13 @@
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="52"/>
-      <c r="M7" s="204"/>
-      <c r="N7" s="205"/>
-      <c r="O7" s="205"/>
-      <c r="P7" s="205"/>
-      <c r="Q7" s="205"/>
-      <c r="R7" s="205"/>
-      <c r="S7" s="206"/>
+      <c r="M7" s="206"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
+      <c r="P7" s="207"/>
+      <c r="Q7" s="207"/>
+      <c r="R7" s="207"/>
+      <c r="S7" s="208"/>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="83"/>
@@ -2501,39 +2520,39 @@
       <c r="J8" s="52"/>
       <c r="K8" s="52"/>
       <c r="L8" s="52"/>
-      <c r="M8" s="204"/>
-      <c r="N8" s="205"/>
-      <c r="O8" s="205"/>
-      <c r="P8" s="205"/>
-      <c r="Q8" s="205"/>
-      <c r="R8" s="205"/>
-      <c r="S8" s="206"/>
+      <c r="M8" s="206"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
+      <c r="P8" s="207"/>
+      <c r="Q8" s="207"/>
+      <c r="R8" s="207"/>
+      <c r="S8" s="208"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81"/>
       <c r="B9" s="80"/>
-      <c r="C9" s="200">
+      <c r="C9" s="202">
         <v>350000</v>
       </c>
-      <c r="D9" s="200"/>
+      <c r="D9" s="202"/>
       <c r="E9" s="79"/>
       <c r="F9" s="78"/>
-      <c r="G9" s="249" t="str">
+      <c r="G9" s="212" t="str">
         <f>Gastos!H8</f>
         <v>VTO: 14/11</v>
       </c>
-      <c r="H9" s="250"/>
-      <c r="I9" s="250"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="251"/>
+      <c r="H9" s="213"/>
+      <c r="I9" s="213"/>
+      <c r="J9" s="213"/>
+      <c r="K9" s="214"/>
       <c r="L9" s="77"/>
-      <c r="M9" s="207"/>
-      <c r="N9" s="208"/>
-      <c r="O9" s="208"/>
-      <c r="P9" s="208"/>
-      <c r="Q9" s="208"/>
-      <c r="R9" s="208"/>
-      <c r="S9" s="209"/>
+      <c r="M9" s="209"/>
+      <c r="N9" s="210"/>
+      <c r="O9" s="210"/>
+      <c r="P9" s="210"/>
+      <c r="Q9" s="210"/>
+      <c r="R9" s="210"/>
+      <c r="S9" s="211"/>
     </row>
     <row r="10" spans="1:22" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="76" t="s">
@@ -2648,7 +2667,7 @@
         <f>C$5*F11/100</f>
         <v>37359.419160000005</v>
       </c>
-      <c r="R11" s="247">
+      <c r="R11" s="190">
         <f>ROUND(O11+N11+P11+Q11,0) + T11</f>
         <v>150476.01</v>
       </c>
@@ -2717,7 +2736,7 @@
         <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
         <v>37359.419160000005</v>
       </c>
-      <c r="R12" s="247">
+      <c r="R12" s="190">
         <f t="shared" ref="R12:R29" si="7">ROUND(O12+N12+P12+Q12,0) + T12</f>
         <v>150476.01999999999</v>
       </c>
@@ -2789,7 +2808,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R13" s="247">
+      <c r="R13" s="190">
         <f t="shared" si="7"/>
         <v>150476.03</v>
       </c>
@@ -2857,7 +2876,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R14" s="247">
+      <c r="R14" s="190">
         <f t="shared" si="7"/>
         <v>150476.04</v>
       </c>
@@ -2927,7 +2946,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R15" s="247">
+      <c r="R15" s="190">
         <f t="shared" si="7"/>
         <v>150476.04999999999</v>
       </c>
@@ -2999,7 +3018,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R16" s="247">
+      <c r="R16" s="190">
         <f t="shared" si="7"/>
         <v>150476.06</v>
       </c>
@@ -3071,7 +3090,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R17" s="247">
+      <c r="R17" s="190">
         <f t="shared" si="7"/>
         <v>161167.07</v>
       </c>
@@ -3140,7 +3159,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R18" s="247">
+      <c r="R18" s="190">
         <f t="shared" si="7"/>
         <v>308030.08000000002</v>
       </c>
@@ -3213,7 +3232,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R19" s="247">
+      <c r="R19" s="190">
         <f t="shared" si="7"/>
         <v>150476.09</v>
       </c>
@@ -3230,62 +3249,65 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="105" t="s">
+      <c r="A20" s="253" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="89" t="s">
+      <c r="B20" s="152"/>
+      <c r="C20" s="254" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="106" t="s">
+      <c r="D20" s="255" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="108"/>
-      <c r="F20" s="91">
+      <c r="E20" s="256"/>
+      <c r="F20" s="257">
         <v>7.9</v>
       </c>
-      <c r="G20" s="68">
+      <c r="G20" s="258">
         <v>152965.07008999999</v>
       </c>
-      <c r="H20" s="61"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61">
+      <c r="H20" s="259"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="259"/>
+      <c r="K20" s="259">
         <f t="shared" si="10"/>
         <v>152965.07008999999</v>
       </c>
-      <c r="L20" s="61"/>
-      <c r="M20" s="60">
+      <c r="L20" s="259"/>
+      <c r="M20" s="260">
         <f t="shared" si="3"/>
         <v>4588.9521027000001</v>
       </c>
-      <c r="N20" s="60">
+      <c r="N20" s="260">
         <f t="shared" ref="N20:N29" si="11">K20+M20+L20</f>
         <v>157554.02219269998</v>
       </c>
-      <c r="O20" s="61">
+      <c r="O20" s="259">
         <f t="shared" si="4"/>
         <v>85466.141310000006</v>
       </c>
-      <c r="P20" s="63">
+      <c r="P20" s="258">
         <f t="shared" si="5"/>
         <v>27650</v>
       </c>
-      <c r="Q20" s="63">
+      <c r="Q20" s="258">
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R20" s="247">
+      <c r="R20" s="261">
         <f t="shared" si="7"/>
         <v>308030.09999999998</v>
       </c>
-      <c r="S20" s="189">
+      <c r="S20" s="262">
         <f t="shared" si="8"/>
         <v>317271.09999999998</v>
       </c>
-      <c r="T20" s="40">
+      <c r="T20" s="263">
         <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="U20" s="264" t="s">
+        <v>175</v>
       </c>
       <c r="V20" s="89" t="s">
         <v>43</v>
@@ -3339,7 +3361,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R21" s="247">
+      <c r="R21" s="190">
         <f t="shared" si="7"/>
         <v>308030.11</v>
       </c>
@@ -3403,7 +3425,7 @@
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R22" s="247">
+      <c r="R22" s="190">
         <f t="shared" si="7"/>
         <v>308030.12</v>
       </c>
@@ -3466,7 +3488,7 @@
         <v>2590</v>
       </c>
       <c r="Q23" s="61"/>
-      <c r="R23" s="247">
+      <c r="R23" s="190">
         <f t="shared" si="7"/>
         <v>10596.13</v>
       </c>
@@ -3529,7 +3551,7 @@
         <f>'Calculo Servicios  (2)'!H22</f>
         <v>0</v>
       </c>
-      <c r="R24" s="247">
+      <c r="R24" s="190">
         <f t="shared" si="7"/>
         <v>21287.14</v>
       </c>
@@ -3590,7 +3612,7 @@
         <f>'Calculo Servicios  (2)'!H23</f>
         <v>0</v>
       </c>
-      <c r="R25" s="247">
+      <c r="R25" s="190">
         <f t="shared" si="7"/>
         <v>21287.15</v>
       </c>
@@ -3658,7 +3680,7 @@
         <f>'Calculo Servicios  (2)'!H24</f>
         <v>0</v>
       </c>
-      <c r="R26" s="247">
+      <c r="R26" s="190">
         <f t="shared" si="7"/>
         <v>21287.16</v>
       </c>
@@ -3727,7 +3749,7 @@
         <f>'Calculo Servicios  (2)'!H25</f>
         <v>0</v>
       </c>
-      <c r="R27" s="247">
+      <c r="R27" s="190">
         <f t="shared" si="7"/>
         <v>10596.17</v>
       </c>
@@ -3797,7 +3819,7 @@
         <f>'Calculo Servicios  (2)'!H26</f>
         <v>0</v>
       </c>
-      <c r="R28" s="247">
+      <c r="R28" s="190">
         <f t="shared" si="7"/>
         <v>10596.18</v>
       </c>
@@ -3865,7 +3887,7 @@
         <f>'Calculo Servicios  (2)'!H27</f>
         <v>0</v>
       </c>
-      <c r="R29" s="247">
+      <c r="R29" s="190">
         <f t="shared" si="7"/>
         <v>21287.19</v>
       </c>
@@ -3911,9 +3933,9 @@
       </c>
     </row>
     <row r="31" spans="1:22" s="54" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="197"/>
-      <c r="B31" s="198"/>
-      <c r="C31" s="198"/>
+      <c r="A31" s="199"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="200"/>
       <c r="D31" s="59"/>
       <c r="E31" s="59"/>
       <c r="F31" s="92"/>
@@ -3962,26 +3984,26 @@
       </c>
     </row>
     <row r="32" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="194" t="s">
+      <c r="B32" s="196" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="195"/>
-      <c r="D32" s="195"/>
-      <c r="E32" s="195"/>
-      <c r="F32" s="195"/>
-      <c r="G32" s="195"/>
-      <c r="H32" s="195"/>
-      <c r="I32" s="195"/>
-      <c r="J32" s="195"/>
-      <c r="K32" s="195"/>
-      <c r="L32" s="195"/>
-      <c r="M32" s="195"/>
-      <c r="N32" s="195"/>
-      <c r="O32" s="195"/>
-      <c r="P32" s="195"/>
-      <c r="Q32" s="195"/>
-      <c r="R32" s="195"/>
-      <c r="S32" s="196"/>
+      <c r="C32" s="197"/>
+      <c r="D32" s="197"/>
+      <c r="E32" s="197"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="197"/>
+      <c r="H32" s="197"/>
+      <c r="I32" s="197"/>
+      <c r="J32" s="197"/>
+      <c r="K32" s="197"/>
+      <c r="L32" s="197"/>
+      <c r="M32" s="197"/>
+      <c r="N32" s="197"/>
+      <c r="O32" s="197"/>
+      <c r="P32" s="197"/>
+      <c r="Q32" s="197"/>
+      <c r="R32" s="197"/>
+      <c r="S32" s="198"/>
       <c r="V32" s="89" t="s">
         <v>55</v>
       </c>
@@ -4001,79 +4023,79 @@
       </c>
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C34" s="190"/>
-      <c r="D34" s="190"/>
-      <c r="E34" s="190"/>
-      <c r="F34" s="190"/>
-      <c r="G34" s="190"/>
-      <c r="H34" s="190"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="190"/>
-      <c r="K34" s="190"/>
-      <c r="L34" s="190"/>
-      <c r="M34" s="190"/>
-      <c r="N34" s="190"/>
-      <c r="O34" s="190"/>
+      <c r="C34" s="192"/>
+      <c r="D34" s="192"/>
+      <c r="E34" s="192"/>
+      <c r="F34" s="192"/>
+      <c r="G34" s="192"/>
+      <c r="H34" s="192"/>
+      <c r="I34" s="192"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="192"/>
+      <c r="L34" s="192"/>
+      <c r="M34" s="192"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="192"/>
     </row>
     <row r="35" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C35" s="190"/>
-      <c r="D35" s="190"/>
-      <c r="E35" s="190"/>
-      <c r="F35" s="190"/>
-      <c r="G35" s="190"/>
-      <c r="H35" s="190"/>
-      <c r="I35" s="190"/>
-      <c r="J35" s="190"/>
-      <c r="K35" s="190"/>
-      <c r="L35" s="190"/>
-      <c r="M35" s="190"/>
-      <c r="N35" s="190"/>
-      <c r="O35" s="190"/>
+      <c r="C35" s="192"/>
+      <c r="D35" s="192"/>
+      <c r="E35" s="192"/>
+      <c r="F35" s="192"/>
+      <c r="G35" s="192"/>
+      <c r="H35" s="192"/>
+      <c r="I35" s="192"/>
+      <c r="J35" s="192"/>
+      <c r="K35" s="192"/>
+      <c r="L35" s="192"/>
+      <c r="M35" s="192"/>
+      <c r="N35" s="192"/>
+      <c r="O35" s="192"/>
     </row>
     <row r="36" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C36" s="190"/>
-      <c r="D36" s="190"/>
-      <c r="E36" s="190"/>
-      <c r="F36" s="190"/>
-      <c r="G36" s="190"/>
-      <c r="H36" s="190"/>
-      <c r="I36" s="190"/>
-      <c r="J36" s="190"/>
-      <c r="K36" s="190"/>
-      <c r="L36" s="190"/>
-      <c r="M36" s="190"/>
-      <c r="N36" s="190"/>
-      <c r="O36" s="190"/>
+      <c r="C36" s="192"/>
+      <c r="D36" s="192"/>
+      <c r="E36" s="192"/>
+      <c r="F36" s="192"/>
+      <c r="G36" s="192"/>
+      <c r="H36" s="192"/>
+      <c r="I36" s="192"/>
+      <c r="J36" s="192"/>
+      <c r="K36" s="192"/>
+      <c r="L36" s="192"/>
+      <c r="M36" s="192"/>
+      <c r="N36" s="192"/>
+      <c r="O36" s="192"/>
     </row>
     <row r="37" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C37" s="190"/>
-      <c r="D37" s="190"/>
-      <c r="E37" s="190"/>
-      <c r="F37" s="190"/>
-      <c r="G37" s="190"/>
-      <c r="H37" s="190"/>
-      <c r="I37" s="190"/>
-      <c r="J37" s="190"/>
-      <c r="K37" s="190"/>
-      <c r="L37" s="190"/>
-      <c r="M37" s="190"/>
-      <c r="N37" s="190"/>
-      <c r="O37" s="190"/>
+      <c r="C37" s="192"/>
+      <c r="D37" s="192"/>
+      <c r="E37" s="192"/>
+      <c r="F37" s="192"/>
+      <c r="G37" s="192"/>
+      <c r="H37" s="192"/>
+      <c r="I37" s="192"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="192"/>
+      <c r="L37" s="192"/>
+      <c r="M37" s="192"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="192"/>
     </row>
     <row r="38" spans="3:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="190"/>
-      <c r="D38" s="190"/>
-      <c r="E38" s="190"/>
-      <c r="F38" s="190"/>
-      <c r="G38" s="190"/>
-      <c r="H38" s="190"/>
-      <c r="I38" s="190"/>
-      <c r="J38" s="190"/>
-      <c r="K38" s="190"/>
-      <c r="L38" s="190"/>
-      <c r="M38" s="190"/>
-      <c r="N38" s="190"/>
-      <c r="O38" s="190"/>
+      <c r="C38" s="192"/>
+      <c r="D38" s="192"/>
+      <c r="E38" s="192"/>
+      <c r="F38" s="192"/>
+      <c r="G38" s="192"/>
+      <c r="H38" s="192"/>
+      <c r="I38" s="192"/>
+      <c r="J38" s="192"/>
+      <c r="K38" s="192"/>
+      <c r="L38" s="192"/>
+      <c r="M38" s="192"/>
+      <c r="N38" s="192"/>
+      <c r="O38" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4122,10 +4144,10 @@
       <c r="D2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="210">
+      <c r="E2" s="216">
         <v>1153202676</v>
       </c>
-      <c r="F2" s="210"/>
+      <c r="F2" s="216"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -4148,29 +4170,29 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="D5" s="211" t="s">
+      <c r="D5" s="217" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="212"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="218"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="D6" s="211"/>
-      <c r="E6" s="211"/>
-      <c r="F6" s="211"/>
-      <c r="G6" s="211"/>
-      <c r="H6" s="212"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="218"/>
     </row>
     <row r="7" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-      <c r="F7" s="211"/>
-      <c r="G7" s="211"/>
-      <c r="H7" s="212"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="218"/>
     </row>
     <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
@@ -4184,7 +4206,7 @@
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="248" t="s">
+      <c r="H8" s="191" t="s">
         <v>174</v>
       </c>
     </row>
@@ -4222,16 +4244,16 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="224" t="s">
+      <c r="A13" s="230" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="224"/>
-      <c r="C13" s="224"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="224"/>
-      <c r="F13" s="224"/>
-      <c r="G13" s="224"/>
-      <c r="H13" s="224"/>
+      <c r="B13" s="230"/>
+      <c r="C13" s="230"/>
+      <c r="D13" s="230"/>
+      <c r="E13" s="230"/>
+      <c r="F13" s="230"/>
+      <c r="G13" s="230"/>
+      <c r="H13" s="230"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
@@ -4300,16 +4322,16 @@
       <c r="H18" s="39"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="225" t="s">
+      <c r="A19" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="226"/>
-      <c r="C19" s="226"/>
-      <c r="D19" s="226"/>
-      <c r="E19" s="226"/>
-      <c r="F19" s="226"/>
-      <c r="G19" s="226"/>
-      <c r="H19" s="227"/>
+      <c r="B19" s="232"/>
+      <c r="C19" s="232"/>
+      <c r="D19" s="232"/>
+      <c r="E19" s="232"/>
+      <c r="F19" s="232"/>
+      <c r="G19" s="232"/>
+      <c r="H19" s="233"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -4356,16 +4378,16 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="228" t="s">
+      <c r="A23" s="234" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="228"/>
-      <c r="C23" s="228"/>
-      <c r="D23" s="228"/>
-      <c r="E23" s="228"/>
-      <c r="F23" s="228"/>
-      <c r="G23" s="228"/>
-      <c r="H23" s="228"/>
+      <c r="B23" s="234"/>
+      <c r="C23" s="234"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="234"/>
+      <c r="G23" s="234"/>
+      <c r="H23" s="234"/>
       <c r="J23" s="24"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -4446,16 +4468,16 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="225" t="s">
+      <c r="A29" s="231" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="226"/>
-      <c r="C29" s="226"/>
-      <c r="D29" s="226"/>
-      <c r="E29" s="226"/>
-      <c r="F29" s="226"/>
-      <c r="G29" s="226"/>
-      <c r="H29" s="227"/>
+      <c r="B29" s="232"/>
+      <c r="C29" s="232"/>
+      <c r="D29" s="232"/>
+      <c r="E29" s="232"/>
+      <c r="F29" s="232"/>
+      <c r="G29" s="232"/>
+      <c r="H29" s="233"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
@@ -4534,16 +4556,16 @@
       <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="225" t="s">
+      <c r="A35" s="231" t="s">
         <v>169</v>
       </c>
-      <c r="B35" s="226"/>
-      <c r="C35" s="226"/>
-      <c r="D35" s="226"/>
-      <c r="E35" s="226"/>
-      <c r="F35" s="226"/>
-      <c r="G35" s="226"/>
-      <c r="H35" s="227"/>
+      <c r="B35" s="232"/>
+      <c r="C35" s="232"/>
+      <c r="D35" s="232"/>
+      <c r="E35" s="232"/>
+      <c r="F35" s="232"/>
+      <c r="G35" s="232"/>
+      <c r="H35" s="233"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="46" t="s">
@@ -4588,63 +4610,63 @@
       <c r="H38" s="44"/>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="215" t="s">
+      <c r="A39" s="221" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="216"/>
-      <c r="C39" s="216"/>
-      <c r="D39" s="216"/>
-      <c r="E39" s="216"/>
-      <c r="F39" s="216"/>
-      <c r="G39" s="216"/>
-      <c r="H39" s="217"/>
+      <c r="B39" s="222"/>
+      <c r="C39" s="222"/>
+      <c r="D39" s="222"/>
+      <c r="E39" s="222"/>
+      <c r="F39" s="222"/>
+      <c r="G39" s="222"/>
+      <c r="H39" s="223"/>
       <c r="I39" s="162"/>
       <c r="K39" s="162"/>
     </row>
     <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="218"/>
-      <c r="B40" s="219"/>
-      <c r="C40" s="219"/>
-      <c r="D40" s="219"/>
-      <c r="E40" s="219"/>
-      <c r="F40" s="219"/>
-      <c r="G40" s="219"/>
-      <c r="H40" s="220"/>
+      <c r="A40" s="224"/>
+      <c r="B40" s="225"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
     </row>
     <row r="41" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="235" t="s">
+      <c r="A41" s="241" t="s">
         <v>168</v>
       </c>
-      <c r="B41" s="236"/>
-      <c r="C41" s="236"/>
-      <c r="D41" s="236"/>
-      <c r="E41" s="236"/>
-      <c r="F41" s="236"/>
-      <c r="G41" s="237"/>
+      <c r="B41" s="242"/>
+      <c r="C41" s="242"/>
+      <c r="D41" s="242"/>
+      <c r="E41" s="242"/>
+      <c r="F41" s="242"/>
+      <c r="G41" s="243"/>
       <c r="H41" s="185">
         <v>350000</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="229"/>
-      <c r="B42" s="230"/>
-      <c r="C42" s="230"/>
-      <c r="D42" s="230"/>
-      <c r="E42" s="230"/>
-      <c r="F42" s="230"/>
-      <c r="G42" s="231"/>
+      <c r="A42" s="235"/>
+      <c r="B42" s="236"/>
+      <c r="C42" s="236"/>
+      <c r="D42" s="236"/>
+      <c r="E42" s="236"/>
+      <c r="F42" s="236"/>
+      <c r="G42" s="237"/>
       <c r="H42" s="30"/>
     </row>
     <row r="43" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="232" t="s">
+      <c r="A43" s="238" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="233"/>
-      <c r="C43" s="233"/>
-      <c r="D43" s="233"/>
-      <c r="E43" s="233"/>
-      <c r="F43" s="233"/>
-      <c r="G43" s="234"/>
+      <c r="B43" s="239"/>
+      <c r="C43" s="239"/>
+      <c r="D43" s="239"/>
+      <c r="E43" s="239"/>
+      <c r="F43" s="239"/>
+      <c r="G43" s="240"/>
       <c r="H43" s="31">
         <f>SUM(H41:H42)</f>
         <v>350000</v>
@@ -4665,15 +4687,15 @@
       <c r="J45" s="14"/>
     </row>
     <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="213" t="s">
+      <c r="A46" s="219" t="s">
         <v>144</v>
       </c>
-      <c r="B46" s="213"/>
-      <c r="C46" s="213"/>
-      <c r="D46" s="213"/>
-      <c r="E46" s="213"/>
-      <c r="F46" s="213"/>
-      <c r="G46" s="213"/>
+      <c r="B46" s="219"/>
+      <c r="C46" s="219"/>
+      <c r="D46" s="219"/>
+      <c r="E46" s="219"/>
+      <c r="F46" s="219"/>
+      <c r="G46" s="219"/>
       <c r="H46" s="29">
         <f>+H37+H38</f>
         <v>1554753.9300000002</v>
@@ -4716,27 +4738,27 @@
       <c r="H49" s="18"/>
     </row>
     <row r="50" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="221" t="s">
+      <c r="A50" s="227" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="222"/>
-      <c r="C50" s="222"/>
-      <c r="D50" s="222"/>
-      <c r="E50" s="222"/>
-      <c r="F50" s="222"/>
-      <c r="G50" s="222"/>
-      <c r="H50" s="223"/>
+      <c r="B50" s="228"/>
+      <c r="C50" s="228"/>
+      <c r="D50" s="228"/>
+      <c r="E50" s="228"/>
+      <c r="F50" s="228"/>
+      <c r="G50" s="228"/>
+      <c r="H50" s="229"/>
     </row>
     <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="214" t="s">
+      <c r="A51" s="220" t="s">
         <v>151</v>
       </c>
-      <c r="B51" s="214"/>
-      <c r="C51" s="214"/>
-      <c r="D51" s="214"/>
-      <c r="E51" s="214"/>
-      <c r="F51" s="214"/>
-      <c r="G51" s="214"/>
+      <c r="B51" s="220"/>
+      <c r="C51" s="220"/>
+      <c r="D51" s="220"/>
+      <c r="E51" s="220"/>
+      <c r="F51" s="220"/>
+      <c r="G51" s="220"/>
       <c r="H51" s="38">
         <v>2287941.4208707316</v>
       </c>
@@ -4829,13 +4851,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="244" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="240"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="246"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="150"/>
@@ -4890,16 +4912,16 @@
       <c r="E6" s="142"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="241" t="s">
+      <c r="A7" s="247" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="242"/>
-      <c r="C7" s="242"/>
-      <c r="D7" s="242"/>
-      <c r="E7" s="242"/>
-      <c r="F7" s="242"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="243"/>
+      <c r="B7" s="248"/>
+      <c r="C7" s="248"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="249"/>
       <c r="L7" s="109" t="s">
         <v>71</v>
       </c>
@@ -5483,13 +5505,13 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="244" t="s">
+      <c r="B28" s="250" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="245"/>
-      <c r="D28" s="245"/>
-      <c r="E28" s="245"/>
-      <c r="F28" s="246"/>
+      <c r="C28" s="251"/>
+      <c r="D28" s="251"/>
+      <c r="E28" s="251"/>
+      <c r="F28" s="252"/>
       <c r="J28" s="109">
         <v>176</v>
       </c>
